--- a/exports/excel/digimon_name_changes_applied.xlsx
+++ b/exports/excel/digimon_name_changes_applied.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="applied_changes" sheetId="1" r:id="R4975bc170b574abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="applied_changes" sheetId="1" r:id="R577f99d7f0e34017"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -147,75 +147,36 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="0"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
@@ -441,6416 +402,6416 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="58" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="56" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="56" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="22" t="str">
+      <x:c r="A1" s="21" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="22" t="str">
         <x:v>english_name</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="22" t="str">
         <x:v>before</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="22" t="str">
         <x:v>after</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="22" t="str">
         <x:v>source_type</x:v>
       </x:c>
-      <x:c r="F1" s="25" t="str">
+      <x:c r="F1" s="24" t="str">
         <x:v>source_url</x:v>
       </x:c>
-      <x:c r="G1" s="23" t="str">
+      <x:c r="G1" s="22" t="str">
         <x:v>confidence</x:v>
       </x:c>
-      <x:c r="H1" s="26" t="str">
+      <x:c r="H1" s="25" t="str">
         <x:v>note</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="7" t="str">
+      <x:c r="A2" s="6" t="str">
         <x:v>char_EX-TYRANOMON</x:v>
       </x:c>
-      <x:c r="B2" s="8" t="str">
+      <x:c r="B2" s="7" t="str">
         <x:v>ExTyrannomon</x:v>
       </x:c>
-      <x:c r="C2" s="8" t="str">
+      <x:c r="C2" s="7" t="str">
         <x:v>ЭксТиранномон</x:v>
       </x:c>
-      <x:c r="D2" s="8" t="str">
+      <x:c r="D2" s="7" t="str">
         <x:v>Экс-Тираномон</x:v>
       </x:c>
-      <x:c r="E2" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F2" s="8" t="str">
+      <x:c r="E2" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Ex-Tyranomon</x:v>
       </x:c>
-      <x:c r="G2" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H2" s="9" t="str">
+      <x:c r="G2" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="7" t="str">
+      <x:c r="A3" s="6" t="str">
         <x:v>char_LEKISMON</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Lekismon</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="7" t="str">
         <x:v>Лекисмон</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="7" t="str">
         <x:v>Лексимон</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="E3" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lekismon</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H3" s="9" t="str">
+      <x:c r="G3" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="7" t="str">
+      <x:c r="A4" s="6" t="str">
         <x:v>char_SKULLSATAMON</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="7" t="str">
         <x:v>SkullSatamon</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="7" t="str">
         <x:v>СкулСатамон</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="7" t="str">
         <x:v>Скалл Сатамон</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="E4" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Skull_Satamon</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H4" s="9" t="str">
+      <x:c r="G4" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H4" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="A5" s="6" t="str">
         <x:v>char_AIRDRAMON</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
+      <x:c r="B5" s="7" t="str">
         <x:v>Airdramon</x:v>
       </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="C5" s="7" t="str">
         <x:v>Аирдрамон</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D5" s="7" t="str">
         <x:v>Эйрдрамон</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="str">
+      <x:c r="E5" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Airdramon</x:v>
       </x:c>
-      <x:c r="G5" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H5" s="9" t="str">
+      <x:c r="G5" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="7" t="str">
+      <x:c r="A6" s="6" t="str">
         <x:v>char_BAKEMON</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="7" t="str">
         <x:v>Bakemon</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="7" t="str">
         <x:v>Бакемон</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="7" t="str">
         <x:v>Бакэмон</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="E6" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Bakemon</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H6" s="9" t="str">
+      <x:c r="G6" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H6" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="7" t="str">
+      <x:c r="A7" s="6" t="str">
         <x:v>char_DORUGORAMON</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="7" t="str">
         <x:v>Dorugoramon</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="7" t="str">
         <x:v>Доругорамон</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="7" t="str">
         <x:v>ДОРУгорамон</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="E7" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F7" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/DORUgoramon</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H7" s="9" t="str">
+      <x:c r="G7" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H7" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="7" t="str">
+      <x:c r="A8" s="6" t="str">
         <x:v>char_TYUMON</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="7" t="str">
         <x:v>Chuumon</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="7" t="str">
         <x:v>Чуумон</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="7" t="str">
         <x:v>Тюмон</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="str">
+      <x:c r="E8" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tyumon</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="str">
+      <x:c r="G8" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="7" t="str">
+      <x:c r="A9" s="6" t="str">
         <x:v>char_WHAMON</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B9" s="7" t="str">
         <x:v>Whamon</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="7" t="str">
         <x:v>Вамон</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="7" t="str">
         <x:v>Уэмон</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="str">
+      <x:c r="E9" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F9" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Whamon</x:v>
       </x:c>
-      <x:c r="G9" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H9" s="9" t="str">
+      <x:c r="G9" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H9" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="7" t="str">
+      <x:c r="A10" s="6" t="str">
         <x:v>char_WARGREYMON</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
+      <x:c r="B10" s="7" t="str">
         <x:v>WarGreymon</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="C10" s="7" t="str">
         <x:v>ВарГреймон</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="7" t="str">
         <x:v>Вор Греймон</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F10" s="8" t="str">
+      <x:c r="E10" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F10" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/War_Greymon</x:v>
       </x:c>
-      <x:c r="G10" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H10" s="9" t="str">
+      <x:c r="G10" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H10" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="7" t="str">
+      <x:c r="A11" s="6" t="str">
         <x:v>char_BIGMAMEMON</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
+      <x:c r="B11" s="7" t="str">
         <x:v>BigMamemon</x:v>
       </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="C11" s="7" t="str">
         <x:v>БигМамемон</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
+      <x:c r="D11" s="7" t="str">
         <x:v>Биг Мамемон</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F11" s="8" t="str">
+      <x:c r="E11" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Big_Mamemon</x:v>
       </x:c>
-      <x:c r="G11" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H11" s="9" t="str">
+      <x:c r="G11" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H11" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="7" t="str">
+      <x:c r="A12" s="6" t="str">
         <x:v>char_SANGLOUPMON</x:v>
       </x:c>
-      <x:c r="B12" s="8" t="str">
+      <x:c r="B12" s="7" t="str">
         <x:v>Sangloupmon</x:v>
       </x:c>
-      <x:c r="C12" s="8" t="str">
+      <x:c r="C12" s="7" t="str">
         <x:v>Санглупмон</x:v>
       </x:c>
-      <x:c r="D12" s="8" t="str">
+      <x:c r="D12" s="7" t="str">
         <x:v>Сулюпмон</x:v>
       </x:c>
-      <x:c r="E12" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F12" s="8" t="str">
+      <x:c r="E12" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Sangloupmon</x:v>
       </x:c>
-      <x:c r="G12" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H12" s="9" t="str">
+      <x:c r="G12" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H12" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="7" t="str">
+      <x:c r="A13" s="6" t="str">
         <x:v>char_GRANDDRACUMON</x:v>
       </x:c>
-      <x:c r="B13" s="8" t="str">
+      <x:c r="B13" s="7" t="str">
         <x:v>GranDracmon</x:v>
       </x:c>
-      <x:c r="C13" s="8" t="str">
+      <x:c r="C13" s="7" t="str">
         <x:v>ГрандДракмон</x:v>
       </x:c>
-      <x:c r="D13" s="8" t="str">
+      <x:c r="D13" s="7" t="str">
         <x:v>Гранд Дракумон</x:v>
       </x:c>
-      <x:c r="E13" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F13" s="8" t="str">
+      <x:c r="E13" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Grand_Dracumon</x:v>
       </x:c>
-      <x:c r="G13" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H13" s="9" t="str">
+      <x:c r="G13" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H13" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="7" t="str">
+      <x:c r="A14" s="6" t="str">
         <x:v>char_BEELZEBUMON</x:v>
       </x:c>
-      <x:c r="B14" s="8" t="str">
+      <x:c r="B14" s="7" t="str">
         <x:v>Beelzemon</x:v>
       </x:c>
-      <x:c r="C14" s="8" t="str">
+      <x:c r="C14" s="7" t="str">
         <x:v>Вельземон</x:v>
       </x:c>
-      <x:c r="D14" s="8" t="str">
+      <x:c r="D14" s="7" t="str">
         <x:v>Вельзевумон</x:v>
       </x:c>
-      <x:c r="E14" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F14" s="8" t="str">
+      <x:c r="E14" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Beelzebumon</x:v>
       </x:c>
-      <x:c r="G14" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H14" s="9" t="str">
+      <x:c r="G14" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H14" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="7" t="str">
+      <x:c r="A15" s="6" t="str">
         <x:v>char_DEMON</x:v>
       </x:c>
-      <x:c r="B15" s="8" t="str">
+      <x:c r="B15" s="7" t="str">
         <x:v>Creepymon</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="str">
+      <x:c r="C15" s="7" t="str">
         <x:v>Крипимон</x:v>
       </x:c>
-      <x:c r="D15" s="8" t="str">
+      <x:c r="D15" s="7" t="str">
         <x:v>Демон</x:v>
       </x:c>
-      <x:c r="E15" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F15" s="8" t="str">
+      <x:c r="E15" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F15" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Demon</x:v>
       </x:c>
-      <x:c r="G15" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H15" s="9" t="str">
+      <x:c r="G15" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H15" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="7" t="str">
+      <x:c r="A16" s="6" t="str">
         <x:v>char_DEMON_BIG</x:v>
       </x:c>
-      <x:c r="B16" s="8" t="str">
+      <x:c r="B16" s="7" t="str">
         <x:v>Creepymon</x:v>
       </x:c>
-      <x:c r="C16" s="8" t="str">
+      <x:c r="C16" s="7" t="str">
         <x:v>Крипимон</x:v>
       </x:c>
-      <x:c r="D16" s="8" t="str">
+      <x:c r="D16" s="7" t="str">
         <x:v>Демон</x:v>
       </x:c>
-      <x:c r="E16" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F16" s="8" t="str">
+      <x:c r="E16" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Demon</x:v>
       </x:c>
-      <x:c r="G16" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H16" s="9" t="str">
+      <x:c r="G16" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="7" t="str">
+      <x:c r="A17" s="6" t="str">
         <x:v>char_LUCEMON_FM</x:v>
       </x:c>
-      <x:c r="B17" s="8" t="str">
+      <x:c r="B17" s="7" t="str">
         <x:v>Lucemon CM</x:v>
       </x:c>
-      <x:c r="C17" s="8" t="str">
+      <x:c r="C17" s="7" t="str">
         <x:v>Люцемон СМ</x:v>
       </x:c>
-      <x:c r="D17" s="8" t="str">
+      <x:c r="D17" s="7" t="str">
         <x:v>Люцимон: Падший режим</x:v>
       </x:c>
-      <x:c r="E17" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F17" s="8" t="str">
+      <x:c r="E17" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lucemon%3A_Falldown_Mode</x:v>
       </x:c>
-      <x:c r="G17" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H17" s="9" t="str">
+      <x:c r="G17" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H17" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="7" t="str">
+      <x:c r="A18" s="6" t="str">
         <x:v>char_FUNBEEMON</x:v>
       </x:c>
-      <x:c r="B18" s="8" t="str">
+      <x:c r="B18" s="7" t="str">
         <x:v>FunBeemon</x:v>
       </x:c>
-      <x:c r="C18" s="8" t="str">
+      <x:c r="C18" s="7" t="str">
         <x:v>ФанБиимон</x:v>
       </x:c>
-      <x:c r="D18" s="8" t="str">
+      <x:c r="D18" s="7" t="str">
         <x:v>Фанбимон</x:v>
       </x:c>
-      <x:c r="E18" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="str">
+      <x:c r="E18" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F18" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Funbeemon</x:v>
       </x:c>
-      <x:c r="G18" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H18" s="9" t="str">
+      <x:c r="G18" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H18" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="7" t="str">
+      <x:c r="A19" s="6" t="str">
         <x:v>char_BLACKTAILMON</x:v>
       </x:c>
-      <x:c r="B19" s="8" t="str">
+      <x:c r="B19" s="7" t="str">
         <x:v>BlackGatomon</x:v>
       </x:c>
-      <x:c r="C19" s="8" t="str">
+      <x:c r="C19" s="7" t="str">
         <x:v>БлэкГатомон</x:v>
       </x:c>
-      <x:c r="D19" s="8" t="str">
+      <x:c r="D19" s="7" t="str">
         <x:v>Блэк Теилмон</x:v>
       </x:c>
-      <x:c r="E19" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F19" s="8" t="str">
+      <x:c r="E19" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F19" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Black_Tailmon</x:v>
       </x:c>
-      <x:c r="G19" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H19" s="9" t="str">
+      <x:c r="G19" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H19" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="7" t="str">
+      <x:c r="A20" s="6" t="str">
         <x:v>char_CHRONOMON</x:v>
       </x:c>
-      <x:c r="B20" s="8" t="str">
+      <x:c r="B20" s="7" t="str">
         <x:v>Chronomon HM</x:v>
       </x:c>
-      <x:c r="C20" s="8" t="str">
+      <x:c r="C20" s="7" t="str">
         <x:v>Хрономон , ХМ</x:v>
       </x:c>
-      <x:c r="D20" s="8" t="str">
+      <x:c r="D20" s="7" t="str">
         <x:v>Хрономон в священном режиме</x:v>
       </x:c>
-      <x:c r="E20" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F20" s="8" t="str">
+      <x:c r="E20" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F20" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Chronomon_Holy_Mode</x:v>
       </x:c>
-      <x:c r="G20" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H20" s="9" t="str">
+      <x:c r="G20" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H20" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="7" t="str">
+      <x:c r="A21" s="6" t="str">
         <x:v>char_GODDRAMON</x:v>
       </x:c>
-      <x:c r="B21" s="8" t="str">
+      <x:c r="B21" s="7" t="str">
         <x:v>Goldramon</x:v>
       </x:c>
-      <x:c r="C21" s="8" t="str">
+      <x:c r="C21" s="7" t="str">
         <x:v>Голдрамон</x:v>
       </x:c>
-      <x:c r="D21" s="8" t="str">
+      <x:c r="D21" s="7" t="str">
         <x:v>Годдрамон</x:v>
       </x:c>
-      <x:c r="E21" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F21" s="8" t="str">
+      <x:c r="E21" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F21" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Goddramon</x:v>
       </x:c>
-      <x:c r="G21" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H21" s="9" t="str">
+      <x:c r="G21" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H21" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="7" t="str">
+      <x:c r="A22" s="6" t="str">
         <x:v>char_GEOGREYMON</x:v>
       </x:c>
-      <x:c r="B22" s="8" t="str">
+      <x:c r="B22" s="7" t="str">
         <x:v>GeoGreymon</x:v>
       </x:c>
-      <x:c r="C22" s="8" t="str">
+      <x:c r="C22" s="7" t="str">
         <x:v>ГеоГреймон</x:v>
       </x:c>
-      <x:c r="D22" s="8" t="str">
+      <x:c r="D22" s="7" t="str">
         <x:v>Гео Греймон</x:v>
       </x:c>
-      <x:c r="E22" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F22" s="8" t="str">
+      <x:c r="E22" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F22" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Geo_Greymon</x:v>
       </x:c>
-      <x:c r="G22" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H22" s="9" t="str">
+      <x:c r="G22" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H22" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="7" t="str">
+      <x:c r="A23" s="6" t="str">
         <x:v>char_SUNFLOWMON</x:v>
       </x:c>
-      <x:c r="B23" s="8" t="str">
+      <x:c r="B23" s="7" t="str">
         <x:v>Sunflowmon</x:v>
       </x:c>
-      <x:c r="C23" s="8" t="str">
+      <x:c r="C23" s="7" t="str">
         <x:v>Санфлоумон</x:v>
       </x:c>
-      <x:c r="D23" s="8" t="str">
+      <x:c r="D23" s="7" t="str">
         <x:v>Санфлаумон</x:v>
       </x:c>
-      <x:c r="E23" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F23" s="8" t="str">
+      <x:c r="E23" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F23" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Sunflowmon</x:v>
       </x:c>
-      <x:c r="G23" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H23" s="9" t="str">
+      <x:c r="G23" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H23" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="7" t="str">
+      <x:c r="A24" s="6" t="str">
         <x:v>char_MONZAEMON</x:v>
       </x:c>
-      <x:c r="B24" s="8" t="str">
+      <x:c r="B24" s="7" t="str">
         <x:v>Monzaemon</x:v>
       </x:c>
-      <x:c r="C24" s="8" t="str">
+      <x:c r="C24" s="7" t="str">
         <x:v>Монзаэмон</x:v>
       </x:c>
-      <x:c r="D24" s="8" t="str">
+      <x:c r="D24" s="7" t="str">
         <x:v>Мондзаэмон</x:v>
       </x:c>
-      <x:c r="E24" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F24" s="8" t="str">
+      <x:c r="E24" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F24" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Monzaemon</x:v>
       </x:c>
-      <x:c r="G24" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H24" s="9" t="str">
+      <x:c r="G24" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H24" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="7" t="str">
+      <x:c r="A25" s="6" t="str">
         <x:v>char_RIZEGREYMON</x:v>
       </x:c>
-      <x:c r="B25" s="8" t="str">
+      <x:c r="B25" s="7" t="str">
         <x:v>RizeGreymon</x:v>
       </x:c>
-      <x:c r="C25" s="8" t="str">
+      <x:c r="C25" s="7" t="str">
         <x:v>РайзГреймон</x:v>
       </x:c>
-      <x:c r="D25" s="8" t="str">
+      <x:c r="D25" s="7" t="str">
         <x:v>Райз Греймон</x:v>
       </x:c>
-      <x:c r="E25" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F25" s="8" t="str">
+      <x:c r="E25" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F25" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Rize_Greymon</x:v>
       </x:c>
-      <x:c r="G25" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H25" s="9" t="str">
+      <x:c r="G25" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H25" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="7" t="str">
+      <x:c r="A26" s="6" t="str">
         <x:v>char_MACHGAOGAMON</x:v>
       </x:c>
-      <x:c r="B26" s="8" t="str">
+      <x:c r="B26" s="7" t="str">
         <x:v>MachGaogamon</x:v>
       </x:c>
-      <x:c r="C26" s="8" t="str">
+      <x:c r="C26" s="7" t="str">
         <x:v>Мачгаогамон</x:v>
       </x:c>
-      <x:c r="D26" s="8" t="str">
+      <x:c r="D26" s="7" t="str">
         <x:v>Мах Гаогамон</x:v>
       </x:c>
-      <x:c r="E26" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F26" s="8" t="str">
+      <x:c r="E26" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F26" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mach_Gaogamon</x:v>
       </x:c>
-      <x:c r="G26" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H26" s="9" t="str">
+      <x:c r="G26" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H26" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="7" t="str">
+      <x:c r="A27" s="6" t="str">
         <x:v>char_NEPTUNEMON</x:v>
       </x:c>
-      <x:c r="B27" s="8" t="str">
+      <x:c r="B27" s="7" t="str">
         <x:v>Neptunemon</x:v>
       </x:c>
-      <x:c r="C27" s="8" t="str">
+      <x:c r="C27" s="7" t="str">
         <x:v>Нептунемон</x:v>
       </x:c>
-      <x:c r="D27" s="8" t="str">
+      <x:c r="D27" s="7" t="str">
         <x:v>Нептунмон</x:v>
       </x:c>
-      <x:c r="E27" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F27" s="8" t="str">
+      <x:c r="E27" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F27" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Neptunemon</x:v>
       </x:c>
-      <x:c r="G27" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H27" s="9" t="str">
+      <x:c r="G27" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H27" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="7" t="str">
+      <x:c r="A28" s="6" t="str">
         <x:v>char_GROWMON</x:v>
       </x:c>
-      <x:c r="B28" s="8" t="str">
+      <x:c r="B28" s="7" t="str">
         <x:v>Growlmon</x:v>
       </x:c>
-      <x:c r="C28" s="8" t="str">
+      <x:c r="C28" s="7" t="str">
         <x:v>Гроулмон</x:v>
       </x:c>
-      <x:c r="D28" s="8" t="str">
+      <x:c r="D28" s="7" t="str">
         <x:v>Граумон</x:v>
       </x:c>
-      <x:c r="E28" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F28" s="8" t="str">
+      <x:c r="E28" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F28" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Growmon</x:v>
       </x:c>
-      <x:c r="G28" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H28" s="9" t="str">
+      <x:c r="G28" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H28" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="7" t="str">
+      <x:c r="A29" s="6" t="str">
         <x:v>char_SUPERSTARMON</x:v>
       </x:c>
-      <x:c r="B29" s="8" t="str">
+      <x:c r="B29" s="7" t="str">
         <x:v>SuperStarmon</x:v>
       </x:c>
-      <x:c r="C29" s="8" t="str">
+      <x:c r="C29" s="7" t="str">
         <x:v>СуперСтармон</x:v>
       </x:c>
-      <x:c r="D29" s="8" t="str">
+      <x:c r="D29" s="7" t="str">
         <x:v>Суперстармон</x:v>
       </x:c>
-      <x:c r="E29" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F29" s="8" t="str">
+      <x:c r="E29" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F29" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Superstarmon</x:v>
       </x:c>
-      <x:c r="G29" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H29" s="9" t="str">
+      <x:c r="G29" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H29" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="7" t="str">
+      <x:c r="A30" s="6" t="str">
         <x:v>char_HIPPOGRIFFOMON</x:v>
       </x:c>
-      <x:c r="B30" s="8" t="str">
+      <x:c r="B30" s="7" t="str">
         <x:v>HippoGryphonmon</x:v>
       </x:c>
-      <x:c r="C30" s="8" t="str">
+      <x:c r="C30" s="7" t="str">
         <x:v>ГиппоГрифонмон</x:v>
       </x:c>
-      <x:c r="D30" s="8" t="str">
+      <x:c r="D30" s="7" t="str">
         <x:v>Гиппогрифомон</x:v>
       </x:c>
-      <x:c r="E30" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F30" s="8" t="str">
+      <x:c r="E30" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F30" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Hippogriffomon</x:v>
       </x:c>
-      <x:c r="G30" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H30" s="9" t="str">
+      <x:c r="G30" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H30" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="7" t="str">
+      <x:c r="A31" s="6" t="str">
         <x:v>char_GRIFFOMON</x:v>
       </x:c>
-      <x:c r="B31" s="8" t="str">
+      <x:c r="B31" s="7" t="str">
         <x:v>Gryphonmon</x:v>
       </x:c>
-      <x:c r="C31" s="8" t="str">
+      <x:c r="C31" s="7" t="str">
         <x:v>Грифонмон</x:v>
       </x:c>
-      <x:c r="D31" s="8" t="str">
+      <x:c r="D31" s="7" t="str">
         <x:v>Гриффомон</x:v>
       </x:c>
-      <x:c r="E31" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F31" s="8" t="str">
+      <x:c r="E31" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F31" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Griffomon</x:v>
       </x:c>
-      <x:c r="G31" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H31" s="9" t="str">
+      <x:c r="G31" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H31" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="7" t="str">
+      <x:c r="A32" s="6" t="str">
         <x:v>char_TYILINMON</x:v>
       </x:c>
-      <x:c r="B32" s="8" t="str">
+      <x:c r="B32" s="7" t="str">
         <x:v>Chirinmon</x:v>
       </x:c>
-      <x:c r="C32" s="8" t="str">
+      <x:c r="C32" s="7" t="str">
         <x:v>Чиринмон</x:v>
       </x:c>
-      <x:c r="D32" s="8" t="str">
+      <x:c r="D32" s="7" t="str">
         <x:v>Цилиньмон</x:v>
       </x:c>
-      <x:c r="E32" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F32" s="8" t="str">
+      <x:c r="E32" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tyilinmon</x:v>
       </x:c>
-      <x:c r="G32" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H32" s="9" t="str">
+      <x:c r="G32" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H32" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="7" t="str">
+      <x:c r="A33" s="6" t="str">
         <x:v>char_VAMDEMON</x:v>
       </x:c>
-      <x:c r="B33" s="8" t="str">
+      <x:c r="B33" s="7" t="str">
         <x:v>Myotismon</x:v>
       </x:c>
-      <x:c r="C33" s="8" t="str">
+      <x:c r="C33" s="7" t="str">
         <x:v>Миотизмон</x:v>
       </x:c>
-      <x:c r="D33" s="8" t="str">
+      <x:c r="D33" s="7" t="str">
         <x:v>Вамдемон</x:v>
       </x:c>
-      <x:c r="E33" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F33" s="8" t="str">
+      <x:c r="E33" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Vamdemon</x:v>
       </x:c>
-      <x:c r="G33" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H33" s="9" t="str">
+      <x:c r="G33" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H33" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="7" t="str">
+      <x:c r="A34" s="6" t="str">
         <x:v>char_SLEIPMON</x:v>
       </x:c>
-      <x:c r="B34" s="8" t="str">
+      <x:c r="B34" s="7" t="str">
         <x:v>Kentaurosmon</x:v>
       </x:c>
-      <x:c r="C34" s="8" t="str">
+      <x:c r="C34" s="7" t="str">
         <x:v>Кентауросмон</x:v>
       </x:c>
-      <x:c r="D34" s="8" t="str">
+      <x:c r="D34" s="7" t="str">
         <x:v>Слейпмон</x:v>
       </x:c>
-      <x:c r="E34" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F34" s="8" t="str">
+      <x:c r="E34" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Sleipmon</x:v>
       </x:c>
-      <x:c r="G34" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H34" s="9" t="str">
+      <x:c r="G34" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H34" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
-      <x:c r="A35" s="7" t="str">
+      <x:c r="A35" s="6" t="str">
         <x:v>char_SLEIPMON_BIG</x:v>
       </x:c>
-      <x:c r="B35" s="8" t="str">
+      <x:c r="B35" s="7" t="str">
         <x:v>Kentaurosmon</x:v>
       </x:c>
-      <x:c r="C35" s="8" t="str">
+      <x:c r="C35" s="7" t="str">
         <x:v>Кентауросмон</x:v>
       </x:c>
-      <x:c r="D35" s="8" t="str">
+      <x:c r="D35" s="7" t="str">
         <x:v>Слейпмон</x:v>
       </x:c>
-      <x:c r="E35" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F35" s="8" t="str">
+      <x:c r="E35" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F35" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Sleipmon</x:v>
       </x:c>
-      <x:c r="G35" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H35" s="9" t="str">
+      <x:c r="G35" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H35" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
-      <x:c r="A36" s="7" t="str">
+      <x:c r="A36" s="6" t="str">
         <x:v>char_OMEGAMON</x:v>
       </x:c>
-      <x:c r="B36" s="8" t="str">
+      <x:c r="B36" s="7" t="str">
         <x:v>Omnimon</x:v>
       </x:c>
-      <x:c r="C36" s="8" t="str">
+      <x:c r="C36" s="7" t="str">
         <x:v>Омнимон</x:v>
       </x:c>
-      <x:c r="D36" s="8" t="str">
+      <x:c r="D36" s="7" t="str">
         <x:v>Омегамон</x:v>
       </x:c>
-      <x:c r="E36" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F36" s="8" t="str">
+      <x:c r="E36" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F36" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Omegamon</x:v>
       </x:c>
-      <x:c r="G36" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H36" s="9" t="str">
+      <x:c r="G36" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H36" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
-      <x:c r="A37" s="7" t="str">
+      <x:c r="A37" s="6" t="str">
         <x:v>char_GUILMON</x:v>
       </x:c>
-      <x:c r="B37" s="8" t="str">
+      <x:c r="B37" s="7" t="str">
         <x:v>Guilmon</x:v>
       </x:c>
-      <x:c r="C37" s="8" t="str">
+      <x:c r="C37" s="7" t="str">
         <x:v>Гильмон</x:v>
       </x:c>
-      <x:c r="D37" s="8" t="str">
+      <x:c r="D37" s="7" t="str">
         <x:v>Гилмон</x:v>
       </x:c>
-      <x:c r="E37" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F37" s="8" t="str">
+      <x:c r="E37" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F37" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Guilmon</x:v>
       </x:c>
-      <x:c r="G37" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H37" s="9" t="str">
+      <x:c r="G37" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H37" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
-      <x:c r="A38" s="7" t="str">
+      <x:c r="A38" s="6" t="str">
         <x:v>char_TAILMON</x:v>
       </x:c>
-      <x:c r="B38" s="8" t="str">
+      <x:c r="B38" s="7" t="str">
         <x:v>Gatomon</x:v>
       </x:c>
-      <x:c r="C38" s="8" t="str">
+      <x:c r="C38" s="7" t="str">
         <x:v>Гатомон</x:v>
       </x:c>
-      <x:c r="D38" s="8" t="str">
+      <x:c r="D38" s="7" t="str">
         <x:v>Тейлмон</x:v>
       </x:c>
-      <x:c r="E38" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F38" s="8" t="str">
+      <x:c r="E38" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F38" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tailmon</x:v>
       </x:c>
-      <x:c r="G38" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H38" s="9" t="str">
+      <x:c r="G38" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H38" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="7" t="str">
+      <x:c r="A39" s="6" t="str">
         <x:v>char_SHINEGREYMON</x:v>
       </x:c>
-      <x:c r="B39" s="8" t="str">
+      <x:c r="B39" s="7" t="str">
         <x:v>ShineGreymon</x:v>
       </x:c>
-      <x:c r="C39" s="8" t="str">
+      <x:c r="C39" s="7" t="str">
         <x:v>ШайнГреймон</x:v>
       </x:c>
-      <x:c r="D39" s="8" t="str">
+      <x:c r="D39" s="7" t="str">
         <x:v>Шайн Греймон</x:v>
       </x:c>
-      <x:c r="E39" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F39" s="8" t="str">
+      <x:c r="E39" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F39" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Shine_Greymon</x:v>
       </x:c>
-      <x:c r="G39" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H39" s="9" t="str">
+      <x:c r="G39" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H39" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
-      <x:c r="A40" s="7" t="str">
+      <x:c r="A40" s="6" t="str">
         <x:v>char_SHINEGREYMON_BIG</x:v>
       </x:c>
-      <x:c r="B40" s="8" t="str">
+      <x:c r="B40" s="7" t="str">
         <x:v>ShineGreymon</x:v>
       </x:c>
-      <x:c r="C40" s="8" t="str">
+      <x:c r="C40" s="7" t="str">
         <x:v>ШайнГреймон</x:v>
       </x:c>
-      <x:c r="D40" s="8" t="str">
+      <x:c r="D40" s="7" t="str">
         <x:v>Шайн Греймон</x:v>
       </x:c>
-      <x:c r="E40" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F40" s="8" t="str">
+      <x:c r="E40" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F40" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Shine_Greymon</x:v>
       </x:c>
-      <x:c r="G40" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H40" s="9" t="str">
+      <x:c r="G40" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H40" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
-      <x:c r="A41" s="7" t="str">
+      <x:c r="A41" s="6" t="str">
         <x:v>char_MIRAGEGAOGAMON</x:v>
       </x:c>
-      <x:c r="B41" s="8" t="str">
+      <x:c r="B41" s="7" t="str">
         <x:v>MirageGaogamon</x:v>
       </x:c>
-      <x:c r="C41" s="8" t="str">
+      <x:c r="C41" s="7" t="str">
         <x:v>МиражГаогамон</x:v>
       </x:c>
-      <x:c r="D41" s="8" t="str">
+      <x:c r="D41" s="7" t="str">
         <x:v>Мираж Гаогамон</x:v>
       </x:c>
-      <x:c r="E41" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F41" s="8" t="str">
+      <x:c r="E41" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F41" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mirage_Gaogamon</x:v>
       </x:c>
-      <x:c r="G41" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H41" s="9" t="str">
+      <x:c r="G41" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H41" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
-      <x:c r="A42" s="7" t="str">
+      <x:c r="A42" s="6" t="str">
         <x:v>char_PICODEVIMON</x:v>
       </x:c>
-      <x:c r="B42" s="8" t="str">
+      <x:c r="B42" s="7" t="str">
         <x:v>DemiDevimon</x:v>
       </x:c>
-      <x:c r="C42" s="8" t="str">
+      <x:c r="C42" s="7" t="str">
         <x:v>ДемиДевимон</x:v>
       </x:c>
-      <x:c r="D42" s="8" t="str">
+      <x:c r="D42" s="7" t="str">
         <x:v>Пико Девимон</x:v>
       </x:c>
-      <x:c r="E42" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F42" s="8" t="str">
+      <x:c r="E42" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F42" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Pico_Devimon</x:v>
       </x:c>
-      <x:c r="G42" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H42" s="9" t="str">
+      <x:c r="G42" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H42" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
-      <x:c r="A43" s="7" t="str">
+      <x:c r="A43" s="6" t="str">
         <x:v>char_WENDIMON</x:v>
       </x:c>
-      <x:c r="B43" s="8" t="str">
+      <x:c r="B43" s="7" t="str">
         <x:v>Wendigomon</x:v>
       </x:c>
-      <x:c r="C43" s="8" t="str">
+      <x:c r="C43" s="7" t="str">
         <x:v>Вендигомон</x:v>
       </x:c>
-      <x:c r="D43" s="8" t="str">
+      <x:c r="D43" s="7" t="str">
         <x:v>Вендимон</x:v>
       </x:c>
-      <x:c r="E43" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F43" s="8" t="str">
+      <x:c r="E43" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F43" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Wendimon</x:v>
       </x:c>
-      <x:c r="G43" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H43" s="9" t="str">
+      <x:c r="G43" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H43" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="7" t="str">
+      <x:c r="A44" s="6" t="str">
         <x:v>char_HOLYANGEMON</x:v>
       </x:c>
-      <x:c r="B44" s="8" t="str">
+      <x:c r="B44" s="7" t="str">
         <x:v>MagnaAngemon</x:v>
       </x:c>
-      <x:c r="C44" s="8" t="str">
+      <x:c r="C44" s="7" t="str">
         <x:v>МагнаАнгемон</x:v>
       </x:c>
-      <x:c r="D44" s="8" t="str">
+      <x:c r="D44" s="7" t="str">
         <x:v>Холи Ангемон</x:v>
       </x:c>
-      <x:c r="E44" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F44" s="8" t="str">
+      <x:c r="E44" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F44" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Holy_Angemon</x:v>
       </x:c>
-      <x:c r="G44" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H44" s="9" t="str">
+      <x:c r="G44" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H44" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
-      <x:c r="A45" s="7" t="str">
+      <x:c r="A45" s="6" t="str">
         <x:v>char_GANIMON</x:v>
       </x:c>
-      <x:c r="B45" s="8" t="str">
+      <x:c r="B45" s="7" t="str">
         <x:v>Crabmon</x:v>
       </x:c>
-      <x:c r="C45" s="8" t="str">
+      <x:c r="C45" s="7" t="str">
         <x:v>Крабмон</x:v>
       </x:c>
-      <x:c r="D45" s="8" t="str">
+      <x:c r="D45" s="7" t="str">
         <x:v>Ганимон</x:v>
       </x:c>
-      <x:c r="E45" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F45" s="8" t="str">
+      <x:c r="E45" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F45" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Ganimon</x:v>
       </x:c>
-      <x:c r="G45" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H45" s="9" t="str">
+      <x:c r="G45" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H45" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
-      <x:c r="A46" s="7" t="str">
+      <x:c r="A46" s="6" t="str">
         <x:v>char_SUSANOOMON</x:v>
       </x:c>
-      <x:c r="B46" s="8" t="str">
+      <x:c r="B46" s="7" t="str">
         <x:v>Susanomon</x:v>
       </x:c>
-      <x:c r="C46" s="8" t="str">
+      <x:c r="C46" s="7" t="str">
         <x:v>Сусаномон</x:v>
       </x:c>
-      <x:c r="D46" s="8" t="str">
+      <x:c r="D46" s="7" t="str">
         <x:v>Сусаноомон</x:v>
       </x:c>
-      <x:c r="E46" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F46" s="8" t="str">
+      <x:c r="E46" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F46" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Susanoomon</x:v>
       </x:c>
-      <x:c r="G46" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H46" s="9" t="str">
+      <x:c r="G46" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H46" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
-      <x:c r="A47" s="7" t="str">
+      <x:c r="A47" s="6" t="str">
         <x:v>char_ARMAGEMON</x:v>
       </x:c>
-      <x:c r="B47" s="8" t="str">
+      <x:c r="B47" s="7" t="str">
         <x:v>Armageddemon</x:v>
       </x:c>
-      <x:c r="C47" s="8" t="str">
+      <x:c r="C47" s="7" t="str">
         <x:v>Армагеддемон</x:v>
       </x:c>
-      <x:c r="D47" s="8" t="str">
+      <x:c r="D47" s="7" t="str">
         <x:v>Армагемон</x:v>
       </x:c>
-      <x:c r="E47" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F47" s="8" t="str">
+      <x:c r="E47" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F47" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Armagemon</x:v>
       </x:c>
-      <x:c r="G47" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H47" s="9" t="str">
+      <x:c r="G47" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H47" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
-      <x:c r="A48" s="7" t="str">
+      <x:c r="A48" s="6" t="str">
         <x:v>char_LADYDEVIMON</x:v>
       </x:c>
-      <x:c r="B48" s="8" t="str">
+      <x:c r="B48" s="7" t="str">
         <x:v>LadyDevimon</x:v>
       </x:c>
-      <x:c r="C48" s="8" t="str">
+      <x:c r="C48" s="7" t="str">
         <x:v>ЛедиДэвимон</x:v>
       </x:c>
-      <x:c r="D48" s="8" t="str">
+      <x:c r="D48" s="7" t="str">
         <x:v>Леди Девимон</x:v>
       </x:c>
-      <x:c r="E48" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F48" s="8" t="str">
+      <x:c r="E48" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F48" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lady_Devimon</x:v>
       </x:c>
-      <x:c r="G48" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H48" s="9" t="str">
+      <x:c r="G48" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H48" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="7" t="str">
+      <x:c r="A49" s="6" t="str">
         <x:v>char_GOBURIMON</x:v>
       </x:c>
-      <x:c r="B49" s="8" t="str">
+      <x:c r="B49" s="7" t="str">
         <x:v>Goblimon</x:v>
       </x:c>
-      <x:c r="C49" s="8" t="str">
+      <x:c r="C49" s="7" t="str">
         <x:v>Гоблимон</x:v>
       </x:c>
-      <x:c r="D49" s="8" t="str">
+      <x:c r="D49" s="7" t="str">
         <x:v>Гобуримон</x:v>
       </x:c>
-      <x:c r="E49" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F49" s="8" t="str">
+      <x:c r="E49" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F49" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Goburimon</x:v>
       </x:c>
-      <x:c r="G49" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H49" s="9" t="str">
+      <x:c r="G49" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H49" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="7" t="str">
+      <x:c r="A50" s="6" t="str">
         <x:v>char_V-MON</x:v>
       </x:c>
-      <x:c r="B50" s="8" t="str">
+      <x:c r="B50" s="7" t="str">
         <x:v>Veemon</x:v>
       </x:c>
-      <x:c r="C50" s="8" t="str">
+      <x:c r="C50" s="7" t="str">
         <x:v>Веемон</x:v>
       </x:c>
-      <x:c r="D50" s="8" t="str">
+      <x:c r="D50" s="7" t="str">
         <x:v>Ви-мон</x:v>
       </x:c>
-      <x:c r="E50" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F50" s="8" t="str">
+      <x:c r="E50" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F50" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/V-mon</x:v>
       </x:c>
-      <x:c r="G50" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H50" s="9" t="str">
+      <x:c r="G50" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H50" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
-      <x:c r="A51" s="7" t="str">
+      <x:c r="A51" s="6" t="str">
         <x:v>char_BAOHUCKMON</x:v>
       </x:c>
-      <x:c r="B51" s="8" t="str">
+      <x:c r="B51" s="7" t="str">
         <x:v>BaoHuckmon</x:v>
       </x:c>
-      <x:c r="C51" s="8" t="str">
+      <x:c r="C51" s="7" t="str">
         <x:v>Баохакмон</x:v>
       </x:c>
-      <x:c r="D51" s="8" t="str">
+      <x:c r="D51" s="7" t="str">
         <x:v>Бао Хакмон</x:v>
       </x:c>
-      <x:c r="E51" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F51" s="8" t="str">
+      <x:c r="E51" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F51" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Bao_Huckmon</x:v>
       </x:c>
-      <x:c r="G51" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H51" s="9" t="str">
+      <x:c r="G51" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H51" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
-      <x:c r="A52" s="7" t="str">
+      <x:c r="A52" s="6" t="str">
         <x:v>char_SAVIORHUCKMON</x:v>
       </x:c>
-      <x:c r="B52" s="8" t="str">
+      <x:c r="B52" s="7" t="str">
         <x:v>SaviorHuckmon</x:v>
       </x:c>
-      <x:c r="C52" s="8" t="str">
+      <x:c r="C52" s="7" t="str">
         <x:v>СэйворХакмон</x:v>
       </x:c>
-      <x:c r="D52" s="8" t="str">
+      <x:c r="D52" s="7" t="str">
         <x:v>Сэйвиор Хакмон</x:v>
       </x:c>
-      <x:c r="E52" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F52" s="8" t="str">
+      <x:c r="E52" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F52" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Savior_Huckmon</x:v>
       </x:c>
-      <x:c r="G52" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H52" s="9" t="str">
+      <x:c r="G52" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H52" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
-      <x:c r="A53" s="7" t="str">
+      <x:c r="A53" s="6" t="str">
         <x:v>char_VALDURMON</x:v>
       </x:c>
-      <x:c r="B53" s="8" t="str">
+      <x:c r="B53" s="7" t="str">
         <x:v>Varodurumon</x:v>
       </x:c>
-      <x:c r="C53" s="8" t="str">
+      <x:c r="C53" s="7" t="str">
         <x:v>Вародурумон</x:v>
       </x:c>
-      <x:c r="D53" s="8" t="str">
+      <x:c r="D53" s="7" t="str">
         <x:v>Вальдурмон</x:v>
       </x:c>
-      <x:c r="E53" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F53" s="8" t="str">
+      <x:c r="E53" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F53" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Valdurmon</x:v>
       </x:c>
-      <x:c r="G53" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H53" s="9" t="str">
+      <x:c r="G53" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H53" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="7" t="str">
+      <x:c r="A54" s="6" t="str">
         <x:v>char_DUKEMON</x:v>
       </x:c>
-      <x:c r="B54" s="8" t="str">
+      <x:c r="B54" s="7" t="str">
         <x:v>Gallantmon</x:v>
       </x:c>
-      <x:c r="C54" s="8" t="str">
+      <x:c r="C54" s="7" t="str">
         <x:v>Галантмон</x:v>
       </x:c>
-      <x:c r="D54" s="8" t="str">
+      <x:c r="D54" s="7" t="str">
         <x:v>Дюкмон</x:v>
       </x:c>
-      <x:c r="E54" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F54" s="8" t="str">
+      <x:c r="E54" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F54" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dukemon</x:v>
       </x:c>
-      <x:c r="G54" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H54" s="9" t="str">
+      <x:c r="G54" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H54" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="7" t="str">
+      <x:c r="A55" s="6" t="str">
         <x:v>char_DUKEMON_BIG</x:v>
       </x:c>
-      <x:c r="B55" s="8" t="str">
+      <x:c r="B55" s="7" t="str">
         <x:v>Gallantmon</x:v>
       </x:c>
-      <x:c r="C55" s="8" t="str">
+      <x:c r="C55" s="7" t="str">
         <x:v>Галантмон</x:v>
       </x:c>
-      <x:c r="D55" s="8" t="str">
+      <x:c r="D55" s="7" t="str">
         <x:v>Дюкмон</x:v>
       </x:c>
-      <x:c r="E55" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F55" s="8" t="str">
+      <x:c r="E55" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F55" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dukemon</x:v>
       </x:c>
-      <x:c r="G55" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H55" s="9" t="str">
+      <x:c r="G55" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H55" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
-      <x:c r="A56" s="7" t="str">
+      <x:c r="A56" s="6" t="str">
         <x:v>char_TYRANTKABUTERIMON</x:v>
       </x:c>
-      <x:c r="B56" s="8" t="str">
+      <x:c r="B56" s="7" t="str">
         <x:v>TyrantKabuterimon</x:v>
       </x:c>
-      <x:c r="C56" s="8" t="str">
+      <x:c r="C56" s="7" t="str">
         <x:v>ТирантКабутеримон</x:v>
       </x:c>
-      <x:c r="D56" s="8" t="str">
+      <x:c r="D56" s="7" t="str">
         <x:v>Тиран Кабутеримон</x:v>
       </x:c>
-      <x:c r="E56" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F56" s="8" t="str">
+      <x:c r="E56" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F56" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tyrant_Kabuterimon</x:v>
       </x:c>
-      <x:c r="G56" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H56" s="9" t="str">
+      <x:c r="G56" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H56" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
-      <x:c r="A57" s="7" t="str">
+      <x:c r="A57" s="6" t="str">
         <x:v>char_TYRANTKABUTERIMON_BIG</x:v>
       </x:c>
-      <x:c r="B57" s="8" t="str">
+      <x:c r="B57" s="7" t="str">
         <x:v>TyrantKabuterimon</x:v>
       </x:c>
-      <x:c r="C57" s="8" t="str">
+      <x:c r="C57" s="7" t="str">
         <x:v>ТирантКабутеримон</x:v>
       </x:c>
-      <x:c r="D57" s="8" t="str">
+      <x:c r="D57" s="7" t="str">
         <x:v>Тиран Кабутеримон</x:v>
       </x:c>
-      <x:c r="E57" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F57" s="8" t="str">
+      <x:c r="E57" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F57" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tyrant_Kabuterimon</x:v>
       </x:c>
-      <x:c r="G57" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H57" s="9" t="str">
+      <x:c r="G57" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H57" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
-      <x:c r="A58" s="7" t="str">
+      <x:c r="A58" s="6" t="str">
         <x:v>char_DAGOMON</x:v>
       </x:c>
-      <x:c r="B58" s="8" t="str">
+      <x:c r="B58" s="7" t="str">
         <x:v>Dragomon</x:v>
       </x:c>
-      <x:c r="C58" s="8" t="str">
+      <x:c r="C58" s="7" t="str">
         <x:v>Драгомон</x:v>
       </x:c>
-      <x:c r="D58" s="8" t="str">
+      <x:c r="D58" s="7" t="str">
         <x:v>Дагомон</x:v>
       </x:c>
-      <x:c r="E58" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F58" s="8" t="str">
+      <x:c r="E58" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F58" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dagomon</x:v>
       </x:c>
-      <x:c r="G58" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H58" s="9" t="str">
+      <x:c r="G58" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H58" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
-      <x:c r="A59" s="7" t="str">
+      <x:c r="A59" s="6" t="str">
         <x:v>char_COELAMON</x:v>
       </x:c>
-      <x:c r="B59" s="8" t="str">
+      <x:c r="B59" s="7" t="str">
         <x:v>Coelamon</x:v>
       </x:c>
-      <x:c r="C59" s="8" t="str">
+      <x:c r="C59" s="7" t="str">
         <x:v>Селамон</x:v>
       </x:c>
-      <x:c r="D59" s="8" t="str">
+      <x:c r="D59" s="7" t="str">
         <x:v>Целамон</x:v>
       </x:c>
-      <x:c r="E59" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F59" s="8" t="str">
+      <x:c r="E59" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F59" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Coelamon</x:v>
       </x:c>
-      <x:c r="G59" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H59" s="9" t="str">
+      <x:c r="G59" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H59" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
-      <x:c r="A60" s="7" t="str">
+      <x:c r="A60" s="6" t="str">
         <x:v>char_MEGASEADRAMON</x:v>
       </x:c>
-      <x:c r="B60" s="8" t="str">
+      <x:c r="B60" s="7" t="str">
         <x:v>MegaSeadramon</x:v>
       </x:c>
-      <x:c r="C60" s="8" t="str">
+      <x:c r="C60" s="7" t="str">
         <x:v>МегаСидрамон</x:v>
       </x:c>
-      <x:c r="D60" s="8" t="str">
+      <x:c r="D60" s="7" t="str">
         <x:v>Мега Сидрамон</x:v>
       </x:c>
-      <x:c r="E60" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F60" s="8" t="str">
+      <x:c r="E60" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F60" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mega_Seadramon</x:v>
       </x:c>
-      <x:c r="G60" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H60" s="9" t="str">
+      <x:c r="G60" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H60" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
-      <x:c r="A61" s="7" t="str">
+      <x:c r="A61" s="6" t="str">
         <x:v>char_MEGAGROWLMON</x:v>
       </x:c>
-      <x:c r="B61" s="8" t="str">
+      <x:c r="B61" s="7" t="str">
         <x:v>WarGrowlmon</x:v>
       </x:c>
-      <x:c r="C61" s="8" t="str">
+      <x:c r="C61" s="7" t="str">
         <x:v>ВарГроулмон</x:v>
       </x:c>
-      <x:c r="D61" s="8" t="str">
+      <x:c r="D61" s="7" t="str">
         <x:v>Мегало Граумон</x:v>
       </x:c>
-      <x:c r="E61" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F61" s="8" t="str">
+      <x:c r="E61" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F61" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Megalo_Growmon</x:v>
       </x:c>
-      <x:c r="G61" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H61" s="9" t="str">
+      <x:c r="G61" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H61" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
-      <x:c r="A62" s="7" t="str">
+      <x:c r="A62" s="6" t="str">
         <x:v>char_METALGARURUMON</x:v>
       </x:c>
-      <x:c r="B62" s="8" t="str">
+      <x:c r="B62" s="7" t="str">
         <x:v>MetalGarurumon</x:v>
       </x:c>
-      <x:c r="C62" s="8" t="str">
+      <x:c r="C62" s="7" t="str">
         <x:v>МеталлГарурумон</x:v>
       </x:c>
-      <x:c r="D62" s="8" t="str">
+      <x:c r="D62" s="7" t="str">
         <x:v>Метал Гарурумон</x:v>
       </x:c>
-      <x:c r="E62" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F62" s="8" t="str">
+      <x:c r="E62" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F62" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Metal_Garurumon</x:v>
       </x:c>
-      <x:c r="G62" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H62" s="9" t="str">
+      <x:c r="G62" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H62" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
-      <x:c r="A63" s="7" t="str">
+      <x:c r="A63" s="6" t="str">
         <x:v>char_WEREGARURUMON</x:v>
       </x:c>
-      <x:c r="B63" s="8" t="str">
+      <x:c r="B63" s="7" t="str">
         <x:v>WereGarurumon</x:v>
       </x:c>
-      <x:c r="C63" s="8" t="str">
+      <x:c r="C63" s="7" t="str">
         <x:v>ВэрГарурумон</x:v>
       </x:c>
-      <x:c r="D63" s="8" t="str">
+      <x:c r="D63" s="7" t="str">
         <x:v>ВерГарурумон</x:v>
       </x:c>
-      <x:c r="E63" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F63" s="8" t="str">
+      <x:c r="E63" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F63" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Were_Garurumon</x:v>
       </x:c>
-      <x:c r="G63" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H63" s="9" t="str">
+      <x:c r="G63" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H63" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="7" t="str">
+      <x:c r="A64" s="6" t="str">
         <x:v>char_HOLSMON</x:v>
       </x:c>
-      <x:c r="B64" s="8" t="str">
+      <x:c r="B64" s="7" t="str">
         <x:v>Halsemon</x:v>
       </x:c>
-      <x:c r="C64" s="8" t="str">
+      <x:c r="C64" s="7" t="str">
         <x:v>Халсемон</x:v>
       </x:c>
-      <x:c r="D64" s="8" t="str">
+      <x:c r="D64" s="7" t="str">
         <x:v>Холсмон</x:v>
       </x:c>
-      <x:c r="E64" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F64" s="8" t="str">
+      <x:c r="E64" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F64" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Holsmon</x:v>
       </x:c>
-      <x:c r="G64" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H64" s="9" t="str">
+      <x:c r="G64" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H64" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
-      <x:c r="A65" s="7" t="str">
+      <x:c r="A65" s="6" t="str">
         <x:v>char_SHURIMON</x:v>
       </x:c>
-      <x:c r="B65" s="8" t="str">
+      <x:c r="B65" s="7" t="str">
         <x:v>Shurimon</x:v>
       </x:c>
-      <x:c r="C65" s="8" t="str">
+      <x:c r="C65" s="7" t="str">
         <x:v>Шуримон</x:v>
       </x:c>
-      <x:c r="D65" s="8" t="str">
+      <x:c r="D65" s="7" t="str">
         <x:v>Сюримон</x:v>
       </x:c>
-      <x:c r="E65" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F65" s="8" t="str">
+      <x:c r="E65" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F65" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Shurimon</x:v>
       </x:c>
-      <x:c r="G65" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H65" s="9" t="str">
+      <x:c r="G65" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H65" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
-      <x:c r="A66" s="7" t="str">
+      <x:c r="A66" s="6" t="str">
         <x:v>char_ANGEWOMON</x:v>
       </x:c>
-      <x:c r="B66" s="8" t="str">
+      <x:c r="B66" s="7" t="str">
         <x:v>Angewomon</x:v>
       </x:c>
-      <x:c r="C66" s="8" t="str">
+      <x:c r="C66" s="7" t="str">
         <x:v>Ангевомон</x:v>
       </x:c>
-      <x:c r="D66" s="8" t="str">
+      <x:c r="D66" s="7" t="str">
         <x:v>Ангевумон</x:v>
       </x:c>
-      <x:c r="E66" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F66" s="8" t="str">
+      <x:c r="E66" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F66" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Angewomon</x:v>
       </x:c>
-      <x:c r="G66" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H66" s="9" t="str">
+      <x:c r="G66" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H66" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
-      <x:c r="A67" s="7" t="str">
+      <x:c r="A67" s="6" t="str">
         <x:v>char_OROCHIMON</x:v>
       </x:c>
-      <x:c r="B67" s="8" t="str">
+      <x:c r="B67" s="7" t="str">
         <x:v>Orochimon</x:v>
       </x:c>
-      <x:c r="C67" s="8" t="str">
+      <x:c r="C67" s="7" t="str">
         <x:v>Орочимон</x:v>
       </x:c>
-      <x:c r="D67" s="8" t="str">
+      <x:c r="D67" s="7" t="str">
         <x:v>Оротимон</x:v>
       </x:c>
-      <x:c r="E67" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F67" s="8" t="str">
+      <x:c r="E67" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F67" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Orochimon</x:v>
       </x:c>
-      <x:c r="G67" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H67" s="9" t="str">
+      <x:c r="G67" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H67" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
-      <x:c r="A68" s="7" t="str">
+      <x:c r="A68" s="6" t="str">
         <x:v>char_RANAMON</x:v>
       </x:c>
-      <x:c r="B68" s="8" t="str">
+      <x:c r="B68" s="7" t="str">
         <x:v>Lanamon</x:v>
       </x:c>
-      <x:c r="C68" s="8" t="str">
+      <x:c r="C68" s="7" t="str">
         <x:v>Ланамон</x:v>
       </x:c>
-      <x:c r="D68" s="8" t="str">
+      <x:c r="D68" s="7" t="str">
         <x:v>Ранамон</x:v>
       </x:c>
-      <x:c r="E68" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F68" s="8" t="str">
+      <x:c r="E68" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F68" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Ranamon</x:v>
       </x:c>
-      <x:c r="G68" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H68" s="9" t="str">
+      <x:c r="G68" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H68" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
-      <x:c r="A69" s="7" t="str">
+      <x:c r="A69" s="6" t="str">
         <x:v>char_JUPITERMON_WRATHMODE</x:v>
       </x:c>
-      <x:c r="B69" s="8" t="str">
+      <x:c r="B69" s="7" t="str">
         <x:v>Jupitermon WM</x:v>
       </x:c>
-      <x:c r="C69" s="8" t="str">
+      <x:c r="C69" s="7" t="str">
         <x:v>Юпитермон WM</x:v>
       </x:c>
-      <x:c r="D69" s="8" t="str">
+      <x:c r="D69" s="7" t="str">
         <x:v>Юпитермон: Режим гнева</x:v>
       </x:c>
-      <x:c r="E69" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F69" s="8" t="str">
+      <x:c r="E69" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F69" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Jupitermon%3A_Wrath_Mode</x:v>
       </x:c>
-      <x:c r="G69" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H69" s="9" t="str">
+      <x:c r="G69" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H69" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
-      <x:c r="A70" s="7" t="str">
+      <x:c r="A70" s="6" t="str">
         <x:v>char_JUPITERMON_WRATHMODE_SUB</x:v>
       </x:c>
-      <x:c r="B70" s="8" t="str">
+      <x:c r="B70" s="7" t="str">
         <x:v>Jupitermon: Wrath Mode</x:v>
       </x:c>
-      <x:c r="C70" s="8" t="str">
+      <x:c r="C70" s="7" t="str">
         <x:v>Юпитермон: Режим Гнева</x:v>
       </x:c>
-      <x:c r="D70" s="8" t="str">
+      <x:c r="D70" s="7" t="str">
         <x:v>Юпитермон: Режим гнева</x:v>
       </x:c>
-      <x:c r="E70" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F70" s="8" t="str">
+      <x:c r="E70" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F70" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Jupitermon%3A_Wrath_Mode</x:v>
       </x:c>
-      <x:c r="G70" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H70" s="9" t="str">
+      <x:c r="G70" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H70" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
-      <x:c r="A71" s="7" t="str">
+      <x:c r="A71" s="6" t="str">
         <x:v>char_APOLLOMON_ADD</x:v>
       </x:c>
-      <x:c r="B71" s="8" t="str">
+      <x:c r="B71" s="7" t="str">
         <x:v>Apollomon (Flame Sphere)</x:v>
       </x:c>
-      <x:c r="C71" s="8" t="str">
+      <x:c r="C71" s="7" t="str">
         <x:v>Аполломон (Огненная Сфера)</x:v>
       </x:c>
-      <x:c r="D71" s="8" t="str">
+      <x:c r="D71" s="7" t="str">
         <x:v>Аполломон (огненная сфера)</x:v>
       </x:c>
-      <x:c r="E71" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F71" s="8" t="str">
+      <x:c r="E71" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F71" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Apollomon</x:v>
       </x:c>
-      <x:c r="G71" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H71" s="9" t="str">
+      <x:c r="G71" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H71" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
-      <x:c r="A72" s="7" t="str">
+      <x:c r="A72" s="6" t="str">
         <x:v>char_BLUEMERAMON</x:v>
       </x:c>
-      <x:c r="B72" s="8" t="str">
+      <x:c r="B72" s="7" t="str">
         <x:v>BlueMeramon</x:v>
       </x:c>
-      <x:c r="C72" s="8" t="str">
+      <x:c r="C72" s="7" t="str">
         <x:v>Блюмерамон</x:v>
       </x:c>
-      <x:c r="D72" s="8" t="str">
+      <x:c r="D72" s="7" t="str">
         <x:v>Блю Мерамон</x:v>
       </x:c>
-      <x:c r="E72" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F72" s="8" t="str">
+      <x:c r="E72" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F72" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Blue_Meramon</x:v>
       </x:c>
-      <x:c r="G72" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H72" s="9" t="str">
+      <x:c r="G72" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H72" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
-      <x:c r="A73" s="7" t="str">
+      <x:c r="A73" s="6" t="str">
         <x:v>char_BACCHUSMON</x:v>
       </x:c>
-      <x:c r="B73" s="8" t="str">
+      <x:c r="B73" s="7" t="str">
         <x:v>Bacchusmon</x:v>
       </x:c>
-      <x:c r="C73" s="8" t="str">
+      <x:c r="C73" s="7" t="str">
         <x:v>Вакхусмон</x:v>
       </x:c>
-      <x:c r="D73" s="8" t="str">
+      <x:c r="D73" s="7" t="str">
         <x:v>Вакхмон</x:v>
       </x:c>
-      <x:c r="E73" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F73" s="8" t="str">
+      <x:c r="E73" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F73" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Bacchusmon</x:v>
       </x:c>
-      <x:c r="G73" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H73" s="9" t="str">
+      <x:c r="G73" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H73" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
-      <x:c r="A74" s="7" t="str">
+      <x:c r="A74" s="6" t="str">
         <x:v>char_AEGIOMON_PLAIN_CLOTHES</x:v>
       </x:c>
-      <x:c r="B74" s="8" t="str">
+      <x:c r="B74" s="7" t="str">
         <x:v>Aegiomon (Street Clothes)</x:v>
       </x:c>
-      <x:c r="C74" s="8" t="str">
+      <x:c r="C74" s="7" t="str">
         <x:v>Эгиомон (Уличная Одежда)</x:v>
       </x:c>
-      <x:c r="D74" s="8" t="str">
+      <x:c r="D74" s="7" t="str">
         <x:v>Эгиомон (уличная одежда)</x:v>
       </x:c>
-      <x:c r="E74" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F74" s="8" t="str">
+      <x:c r="E74" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F74" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aegiomon</x:v>
       </x:c>
-      <x:c r="G74" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H74" s="9" t="str">
+      <x:c r="G74" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H74" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
-      <x:c r="A75" s="7" t="str">
+      <x:c r="A75" s="6" t="str">
         <x:v>char_AEGIOMON_NO_CAP</x:v>
       </x:c>
-      <x:c r="B75" s="8" t="str">
+      <x:c r="B75" s="7" t="str">
         <x:v>Aegiomon (Hatless Street Clothes)</x:v>
       </x:c>
-      <x:c r="C75" s="8" t="str">
+      <x:c r="C75" s="7" t="str">
         <x:v>Эгиомон (Уличная Одежда без головного убора)</x:v>
       </x:c>
-      <x:c r="D75" s="8" t="str">
+      <x:c r="D75" s="7" t="str">
         <x:v>Эгиомон (уличная одежда без головного убора)</x:v>
       </x:c>
-      <x:c r="E75" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F75" s="8" t="str">
+      <x:c r="E75" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F75" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aegiomon</x:v>
       </x:c>
-      <x:c r="G75" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H75" s="9" t="str">
+      <x:c r="G75" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H75" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
-      <x:c r="A76" s="7" t="str">
+      <x:c r="A76" s="6" t="str">
         <x:v>char_AEGIOCHUSMON</x:v>
       </x:c>
-      <x:c r="B76" s="8" t="str">
+      <x:c r="B76" s="7" t="str">
         <x:v>Aegiochusmon</x:v>
       </x:c>
-      <x:c r="C76" s="8" t="str">
+      <x:c r="C76" s="7" t="str">
         <x:v>Эгиохусмон</x:v>
       </x:c>
-      <x:c r="D76" s="8" t="str">
+      <x:c r="D76" s="7" t="str">
         <x:v>Эгиохмон</x:v>
       </x:c>
-      <x:c r="E76" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F76" s="8" t="str">
+      <x:c r="E76" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F76" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aegiochusmon</x:v>
       </x:c>
-      <x:c r="G76" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H76" s="9" t="str">
+      <x:c r="G76" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H76" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
-      <x:c r="A77" s="7" t="str">
+      <x:c r="A77" s="6" t="str">
         <x:v>char_AEGIOCHUSMON_DARK</x:v>
       </x:c>
-      <x:c r="B77" s="8" t="str">
+      <x:c r="B77" s="7" t="str">
         <x:v>Aegiochusmon: Dark</x:v>
       </x:c>
-      <x:c r="C77" s="8" t="str">
+      <x:c r="C77" s="7" t="str">
         <x:v>Эгиохусмон: Темный</x:v>
       </x:c>
-      <x:c r="D77" s="8" t="str">
+      <x:c r="D77" s="7" t="str">
         <x:v>Эгиохмон: Тёмный</x:v>
       </x:c>
-      <x:c r="E77" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F77" s="8" t="str">
+      <x:c r="E77" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F77" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aegiochusmon%3A_Dark</x:v>
       </x:c>
-      <x:c r="G77" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H77" s="9" t="str">
+      <x:c r="G77" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H77" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
-      <x:c r="A78" s="7" t="str">
+      <x:c r="A78" s="6" t="str">
         <x:v>char_AEGIOCHUSMON_HOLLY</x:v>
       </x:c>
-      <x:c r="B78" s="8" t="str">
+      <x:c r="B78" s="7" t="str">
         <x:v>Aegiochusmon: Holy</x:v>
       </x:c>
-      <x:c r="C78" s="8" t="str">
+      <x:c r="C78" s="7" t="str">
         <x:v>Эгиохусмон: Святой</x:v>
       </x:c>
-      <x:c r="D78" s="8" t="str">
+      <x:c r="D78" s="7" t="str">
         <x:v>Эгиохмон: Святой</x:v>
       </x:c>
-      <x:c r="E78" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F78" s="8" t="str">
+      <x:c r="E78" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F78" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aegiochusmon%3A_Holy</x:v>
       </x:c>
-      <x:c r="G78" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H78" s="9" t="str">
+      <x:c r="G78" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H78" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
-      <x:c r="A79" s="7" t="str">
+      <x:c r="A79" s="6" t="str">
         <x:v>char_AEGIOCHUSMON_BLUE</x:v>
       </x:c>
-      <x:c r="B79" s="8" t="str">
+      <x:c r="B79" s="7" t="str">
         <x:v>Aegiochusmon: Blue</x:v>
       </x:c>
-      <x:c r="C79" s="8" t="str">
+      <x:c r="C79" s="7" t="str">
         <x:v>Эгиохусмон: Синий</x:v>
       </x:c>
-      <x:c r="D79" s="8" t="str">
+      <x:c r="D79" s="7" t="str">
         <x:v>Эгиохмон: Синий</x:v>
       </x:c>
-      <x:c r="E79" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F79" s="8" t="str">
+      <x:c r="E79" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F79" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aegiochusmon%3A_Blue</x:v>
       </x:c>
-      <x:c r="G79" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H79" s="9" t="str">
+      <x:c r="G79" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H79" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
-      <x:c r="A80" s="7" t="str">
+      <x:c r="A80" s="6" t="str">
         <x:v>char_AEGIOCHUSMON_GREEN</x:v>
       </x:c>
-      <x:c r="B80" s="8" t="str">
+      <x:c r="B80" s="7" t="str">
         <x:v>Aegiochusmon: Green</x:v>
       </x:c>
-      <x:c r="C80" s="8" t="str">
+      <x:c r="C80" s="7" t="str">
         <x:v>Эгиохусмон: Зеленый</x:v>
       </x:c>
-      <x:c r="D80" s="8" t="str">
+      <x:c r="D80" s="7" t="str">
         <x:v>Эгиохмон: Зелёный</x:v>
       </x:c>
-      <x:c r="E80" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F80" s="8" t="str">
+      <x:c r="E80" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F80" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aegiochusmon%3A_Green</x:v>
       </x:c>
-      <x:c r="G80" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H80" s="9" t="str">
+      <x:c r="G80" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H80" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
-      <x:c r="A81" s="7" t="str">
+      <x:c r="A81" s="6" t="str">
         <x:v>char_GUNDRAMON</x:v>
       </x:c>
-      <x:c r="B81" s="8" t="str">
+      <x:c r="B81" s="7" t="str">
         <x:v>Gundramon</x:v>
       </x:c>
-      <x:c r="C81" s="8" t="str">
+      <x:c r="C81" s="7" t="str">
         <x:v>Гундрамон</x:v>
       </x:c>
-      <x:c r="D81" s="8" t="str">
+      <x:c r="D81" s="7" t="str">
         <x:v>Гандрамон</x:v>
       </x:c>
-      <x:c r="E81" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F81" s="8" t="str">
+      <x:c r="E81" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F81" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gundramon</x:v>
       </x:c>
-      <x:c r="G81" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H81" s="9" t="str">
+      <x:c r="G81" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H81" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
-      <x:c r="A82" s="7" t="str">
+      <x:c r="A82" s="6" t="str">
         <x:v>char_GUNDRAMON_BIG</x:v>
       </x:c>
-      <x:c r="B82" s="8" t="str">
+      <x:c r="B82" s="7" t="str">
         <x:v>Gundramon</x:v>
       </x:c>
-      <x:c r="C82" s="8" t="str">
+      <x:c r="C82" s="7" t="str">
         <x:v>Гундрамон</x:v>
       </x:c>
-      <x:c r="D82" s="8" t="str">
+      <x:c r="D82" s="7" t="str">
         <x:v>Гандрамон</x:v>
       </x:c>
-      <x:c r="E82" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F82" s="8" t="str">
+      <x:c r="E82" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F82" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gundramon</x:v>
       </x:c>
-      <x:c r="G82" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H82" s="9" t="str">
+      <x:c r="G82" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H82" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
-      <x:c r="A83" s="7" t="str">
+      <x:c r="A83" s="6" t="str">
         <x:v>char_BEELSTARMON</x:v>
       </x:c>
-      <x:c r="B83" s="8" t="str">
+      <x:c r="B83" s="7" t="str">
         <x:v>BeelStarmon</x:v>
       </x:c>
-      <x:c r="C83" s="8" t="str">
+      <x:c r="C83" s="7" t="str">
         <x:v>ВельСтармон</x:v>
       </x:c>
-      <x:c r="D83" s="8" t="str">
+      <x:c r="D83" s="7" t="str">
         <x:v>Вель Стармон</x:v>
       </x:c>
-      <x:c r="E83" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F83" s="8" t="str">
+      <x:c r="E83" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F83" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Beel_Starmon</x:v>
       </x:c>
-      <x:c r="G83" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H83" s="9" t="str">
+      <x:c r="G83" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H83" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
-      <x:c r="A84" s="7" t="str">
+      <x:c r="A84" s="6" t="str">
         <x:v>char_CROSSMON</x:v>
       </x:c>
-      <x:c r="B84" s="8" t="str">
+      <x:c r="B84" s="7" t="str">
         <x:v>Eaglemon</x:v>
       </x:c>
-      <x:c r="C84" s="8" t="str">
+      <x:c r="C84" s="7" t="str">
         <x:v>Иглемон</x:v>
       </x:c>
-      <x:c r="D84" s="8" t="str">
+      <x:c r="D84" s="7" t="str">
         <x:v>Кроссмон</x:v>
       </x:c>
-      <x:c r="E84" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F84" s="8" t="str">
+      <x:c r="E84" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F84" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Crossmon</x:v>
       </x:c>
-      <x:c r="G84" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H84" s="9" t="str">
+      <x:c r="G84" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H84" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
-      <x:c r="A85" s="7" t="str">
+      <x:c r="A85" s="6" t="str">
         <x:v>char_COREDRAMON_GR</x:v>
       </x:c>
-      <x:c r="B85" s="8" t="str">
+      <x:c r="B85" s="7" t="str">
         <x:v>Coredramon (Green)</x:v>
       </x:c>
-      <x:c r="C85" s="8" t="str">
+      <x:c r="C85" s="7" t="str">
         <x:v>Коредрамон (Зеленый)</x:v>
       </x:c>
-      <x:c r="D85" s="8" t="str">
+      <x:c r="D85" s="7" t="str">
         <x:v>Кордрамон (Зелёный)</x:v>
       </x:c>
-      <x:c r="E85" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F85" s="8" t="str">
+      <x:c r="E85" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F85" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Coredramon_%28Green%29</x:v>
       </x:c>
-      <x:c r="G85" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H85" s="9" t="str">
+      <x:c r="G85" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H85" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
-      <x:c r="A86" s="7" t="str">
+      <x:c r="A86" s="6" t="str">
         <x:v>char_SLAYERDRAMON</x:v>
       </x:c>
-      <x:c r="B86" s="8" t="str">
+      <x:c r="B86" s="7" t="str">
         <x:v>Slayerdramon</x:v>
       </x:c>
-      <x:c r="C86" s="8" t="str">
+      <x:c r="C86" s="7" t="str">
         <x:v>Убийца Драмон</x:v>
       </x:c>
-      <x:c r="D86" s="8" t="str">
+      <x:c r="D86" s="7" t="str">
         <x:v>Слейердрамон</x:v>
       </x:c>
-      <x:c r="E86" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F86" s="8" t="str">
+      <x:c r="E86" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F86" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Slayerdramon</x:v>
       </x:c>
-      <x:c r="G86" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H86" s="9" t="str">
+      <x:c r="G86" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H86" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
-      <x:c r="A87" s="7" t="str">
+      <x:c r="A87" s="6" t="str">
         <x:v>char_EXAMON</x:v>
       </x:c>
-      <x:c r="B87" s="8" t="str">
+      <x:c r="B87" s="7" t="str">
         <x:v>Examon</x:v>
       </x:c>
-      <x:c r="C87" s="8" t="str">
+      <x:c r="C87" s="7" t="str">
         <x:v>Экзамон</x:v>
       </x:c>
-      <x:c r="D87" s="8" t="str">
+      <x:c r="D87" s="7" t="str">
         <x:v>Эксамон</x:v>
       </x:c>
-      <x:c r="E87" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F87" s="8" t="str">
+      <x:c r="E87" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F87" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Examon</x:v>
       </x:c>
-      <x:c r="G87" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H87" s="9" t="str">
+      <x:c r="G87" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H87" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
-      <x:c r="A88" s="7" t="str">
+      <x:c r="A88" s="6" t="str">
         <x:v>char_EXAMON_SMALL</x:v>
       </x:c>
-      <x:c r="B88" s="8" t="str">
+      <x:c r="B88" s="7" t="str">
         <x:v>Examon</x:v>
       </x:c>
-      <x:c r="C88" s="8" t="str">
+      <x:c r="C88" s="7" t="str">
         <x:v>Экзамон</x:v>
       </x:c>
-      <x:c r="D88" s="8" t="str">
+      <x:c r="D88" s="7" t="str">
         <x:v>Эксамон</x:v>
       </x:c>
-      <x:c r="E88" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F88" s="8" t="str">
+      <x:c r="E88" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F88" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Examon</x:v>
       </x:c>
-      <x:c r="G88" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H88" s="9" t="str">
+      <x:c r="G88" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H88" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
-      <x:c r="A89" s="7" t="str">
+      <x:c r="A89" s="6" t="str">
         <x:v>char_EXAMON_BIG</x:v>
       </x:c>
-      <x:c r="B89" s="8" t="str">
+      <x:c r="B89" s="7" t="str">
         <x:v>Examon</x:v>
       </x:c>
-      <x:c r="C89" s="8" t="str">
+      <x:c r="C89" s="7" t="str">
         <x:v>Экзамон</x:v>
       </x:c>
-      <x:c r="D89" s="8" t="str">
+      <x:c r="D89" s="7" t="str">
         <x:v>Эксамон</x:v>
       </x:c>
-      <x:c r="E89" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F89" s="8" t="str">
+      <x:c r="E89" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F89" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Examon</x:v>
       </x:c>
-      <x:c r="G89" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H89" s="9" t="str">
+      <x:c r="G89" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H89" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
-      <x:c r="A90" s="7" t="str">
+      <x:c r="A90" s="6" t="str">
         <x:v>char_DARKSUPERSTARMON</x:v>
       </x:c>
-      <x:c r="B90" s="8" t="str">
+      <x:c r="B90" s="7" t="str">
         <x:v>DarkSuperStarmon</x:v>
       </x:c>
-      <x:c r="C90" s="8" t="str">
+      <x:c r="C90" s="7" t="str">
         <x:v>ДаркСуперСтармон</x:v>
       </x:c>
-      <x:c r="D90" s="8" t="str">
+      <x:c r="D90" s="7" t="str">
         <x:v>Дарк Суперстармон</x:v>
       </x:c>
-      <x:c r="E90" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F90" s="8" t="str">
+      <x:c r="E90" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F90" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dark_Superstarmon</x:v>
       </x:c>
-      <x:c r="G90" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H90" s="9" t="str">
+      <x:c r="G90" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H90" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
-      <x:c r="A91" s="7" t="str">
+      <x:c r="A91" s="6" t="str">
         <x:v>char_COREDRAMON_BL</x:v>
       </x:c>
-      <x:c r="B91" s="8" t="str">
+      <x:c r="B91" s="7" t="str">
         <x:v>Coredramon (Blue)</x:v>
       </x:c>
-      <x:c r="C91" s="8" t="str">
+      <x:c r="C91" s="7" t="str">
         <x:v>Коредрамон (Синий)</x:v>
       </x:c>
-      <x:c r="D91" s="8" t="str">
+      <x:c r="D91" s="7" t="str">
         <x:v>Кордрамон (Синий)</x:v>
       </x:c>
-      <x:c r="E91" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F91" s="8" t="str">
+      <x:c r="E91" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F91" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Coredramon_%28Blue%29</x:v>
       </x:c>
-      <x:c r="G91" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H91" s="9" t="str">
+      <x:c r="G91" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H91" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
-      <x:c r="A92" s="7" t="str">
+      <x:c r="A92" s="6" t="str">
         <x:v>char_KOTEMON</x:v>
       </x:c>
-      <x:c r="B92" s="8" t="str">
+      <x:c r="B92" s="7" t="str">
         <x:v>Kotemon</x:v>
       </x:c>
-      <x:c r="C92" s="8" t="str">
+      <x:c r="C92" s="7" t="str">
         <x:v>Котемон</x:v>
       </x:c>
-      <x:c r="D92" s="8" t="str">
+      <x:c r="D92" s="7" t="str">
         <x:v>Котэмон</x:v>
       </x:c>
-      <x:c r="E92" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F92" s="8" t="str">
+      <x:c r="E92" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F92" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Kotemon</x:v>
       </x:c>
-      <x:c r="G92" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H92" s="9" t="str">
+      <x:c r="G92" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H92" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
-      <x:c r="A93" s="7" t="str">
+      <x:c r="A93" s="6" t="str">
         <x:v>char_MUSYAMON</x:v>
       </x:c>
-      <x:c r="B93" s="8" t="str">
+      <x:c r="B93" s="7" t="str">
         <x:v>Musyamon</x:v>
       </x:c>
-      <x:c r="C93" s="8" t="str">
+      <x:c r="C93" s="7" t="str">
         <x:v>Мусьямон</x:v>
       </x:c>
-      <x:c r="D93" s="8" t="str">
+      <x:c r="D93" s="7" t="str">
         <x:v>Мусямон</x:v>
       </x:c>
-      <x:c r="E93" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F93" s="8" t="str">
+      <x:c r="E93" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F93" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Musyamon</x:v>
       </x:c>
-      <x:c r="G93" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H93" s="9" t="str">
+      <x:c r="G93" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H93" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
-      <x:c r="A94" s="7" t="str">
+      <x:c r="A94" s="6" t="str">
         <x:v>char_CERBERUMON</x:v>
       </x:c>
-      <x:c r="B94" s="8" t="str">
+      <x:c r="B94" s="7" t="str">
         <x:v>Cerberusmon</x:v>
       </x:c>
-      <x:c r="C94" s="8" t="str">
+      <x:c r="C94" s="7" t="str">
         <x:v>Церберусмон</x:v>
       </x:c>
-      <x:c r="D94" s="8" t="str">
+      <x:c r="D94" s="7" t="str">
         <x:v>Церберумон</x:v>
       </x:c>
-      <x:c r="E94" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F94" s="8" t="str">
+      <x:c r="E94" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F94" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Cerberumon</x:v>
       </x:c>
-      <x:c r="G94" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H94" s="9" t="str">
+      <x:c r="G94" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H94" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
-      <x:c r="A95" s="7" t="str">
+      <x:c r="A95" s="6" t="str">
         <x:v>char_CERBERUMON_WEREWOLFMODE</x:v>
       </x:c>
-      <x:c r="B95" s="8" t="str">
+      <x:c r="B95" s="7" t="str">
         <x:v>Cerberusmon WM</x:v>
       </x:c>
-      <x:c r="C95" s="8" t="str">
+      <x:c r="C95" s="7" t="str">
         <x:v>Церберусмон ВМ</x:v>
       </x:c>
-      <x:c r="D95" s="8" t="str">
+      <x:c r="D95" s="7" t="str">
         <x:v>Церберумон: режим оборотня</x:v>
       </x:c>
-      <x:c r="E95" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F95" s="8" t="str">
+      <x:c r="E95" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F95" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Cerberumon%3A_Werewolf_Mode</x:v>
       </x:c>
-      <x:c r="G95" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H95" s="9" t="str">
+      <x:c r="G95" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H95" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
-      <x:c r="A96" s="7" t="str">
+      <x:c r="A96" s="6" t="str">
         <x:v>char_ZANBAMON</x:v>
       </x:c>
-      <x:c r="B96" s="8" t="str">
+      <x:c r="B96" s="7" t="str">
         <x:v>Zanbamon</x:v>
       </x:c>
-      <x:c r="C96" s="8" t="str">
+      <x:c r="C96" s="7" t="str">
         <x:v>Занбамон</x:v>
       </x:c>
-      <x:c r="D96" s="8" t="str">
+      <x:c r="D96" s="7" t="str">
         <x:v>Дзанбамон</x:v>
       </x:c>
-      <x:c r="E96" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F96" s="8" t="str">
+      <x:c r="E96" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F96" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Zanbamon</x:v>
       </x:c>
-      <x:c r="G96" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H96" s="9" t="str">
+      <x:c r="G96" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H96" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
-      <x:c r="A97" s="7" t="str">
+      <x:c r="A97" s="6" t="str">
         <x:v>char_ZANBAMON_BIG</x:v>
       </x:c>
-      <x:c r="B97" s="8" t="str">
+      <x:c r="B97" s="7" t="str">
         <x:v>Zanbamon</x:v>
       </x:c>
-      <x:c r="C97" s="8" t="str">
+      <x:c r="C97" s="7" t="str">
         <x:v>Занбамон</x:v>
       </x:c>
-      <x:c r="D97" s="8" t="str">
+      <x:c r="D97" s="7" t="str">
         <x:v>Дзанбамон</x:v>
       </x:c>
-      <x:c r="E97" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F97" s="8" t="str">
+      <x:c r="E97" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F97" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Zanbamon</x:v>
       </x:c>
-      <x:c r="G97" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H97" s="9" t="str">
+      <x:c r="G97" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H97" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
-      <x:c r="A98" s="7" t="str">
+      <x:c r="A98" s="6" t="str">
         <x:v>char_CHIMAIRAMON</x:v>
       </x:c>
-      <x:c r="B98" s="8" t="str">
+      <x:c r="B98" s="7" t="str">
         <x:v>Kimeramon</x:v>
       </x:c>
-      <x:c r="C98" s="8" t="str">
+      <x:c r="C98" s="7" t="str">
         <x:v>Кимерамон</x:v>
       </x:c>
-      <x:c r="D98" s="8" t="str">
+      <x:c r="D98" s="7" t="str">
         <x:v>Химерамон</x:v>
       </x:c>
-      <x:c r="E98" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F98" s="8" t="str">
+      <x:c r="E98" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F98" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Chimairamon</x:v>
       </x:c>
-      <x:c r="G98" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H98" s="9" t="str">
+      <x:c r="G98" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H98" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
-      <x:c r="A99" s="7" t="str">
+      <x:c r="A99" s="6" t="str">
         <x:v>char_MILLENNIUMON</x:v>
       </x:c>
-      <x:c r="B99" s="8" t="str">
+      <x:c r="B99" s="7" t="str">
         <x:v>Millenniummon</x:v>
       </x:c>
-      <x:c r="C99" s="8" t="str">
+      <x:c r="C99" s="7" t="str">
         <x:v>Милениуммон</x:v>
       </x:c>
-      <x:c r="D99" s="8" t="str">
+      <x:c r="D99" s="7" t="str">
         <x:v>Милленниумон</x:v>
       </x:c>
-      <x:c r="E99" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F99" s="8" t="str">
+      <x:c r="E99" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F99" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Millenniumon</x:v>
       </x:c>
-      <x:c r="G99" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H99" s="9" t="str">
+      <x:c r="G99" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H99" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
-      <x:c r="A100" s="7" t="str">
+      <x:c r="A100" s="6" t="str">
         <x:v>char_MILLENNIUMON_BIG</x:v>
       </x:c>
-      <x:c r="B100" s="8" t="str">
+      <x:c r="B100" s="7" t="str">
         <x:v>Millenniummon</x:v>
       </x:c>
-      <x:c r="C100" s="8" t="str">
+      <x:c r="C100" s="7" t="str">
         <x:v>Милениуммон</x:v>
       </x:c>
-      <x:c r="D100" s="8" t="str">
+      <x:c r="D100" s="7" t="str">
         <x:v>Милленниумон</x:v>
       </x:c>
-      <x:c r="E100" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F100" s="8" t="str">
+      <x:c r="E100" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F100" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Millenniumon</x:v>
       </x:c>
-      <x:c r="G100" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H100" s="9" t="str">
+      <x:c r="G100" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H100" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
-      <x:c r="A101" s="7" t="str">
+      <x:c r="A101" s="6" t="str">
         <x:v>char_BAKUMON</x:v>
       </x:c>
-      <x:c r="B101" s="8" t="str">
+      <x:c r="B101" s="7" t="str">
         <x:v>Tapirmon</x:v>
       </x:c>
-      <x:c r="C101" s="8" t="str">
+      <x:c r="C101" s="7" t="str">
         <x:v>Тапирмон</x:v>
       </x:c>
-      <x:c r="D101" s="8" t="str">
+      <x:c r="D101" s="7" t="str">
         <x:v>Бакумон</x:v>
       </x:c>
-      <x:c r="E101" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F101" s="8" t="str">
+      <x:c r="E101" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F101" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Bakumon</x:v>
       </x:c>
-      <x:c r="G101" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H101" s="9" t="str">
+      <x:c r="G101" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H101" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
-      <x:c r="A102" s="7" t="str">
+      <x:c r="A102" s="6" t="str">
         <x:v>char_BEARMON</x:v>
       </x:c>
-      <x:c r="B102" s="8" t="str">
+      <x:c r="B102" s="7" t="str">
         <x:v>Bearmon</x:v>
       </x:c>
-      <x:c r="C102" s="8" t="str">
+      <x:c r="C102" s="7" t="str">
         <x:v>Бирмон</x:v>
       </x:c>
-      <x:c r="D102" s="8" t="str">
+      <x:c r="D102" s="7" t="str">
         <x:v>Бермон</x:v>
       </x:c>
-      <x:c r="E102" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F102" s="8" t="str">
+      <x:c r="E102" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F102" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Bearmon</x:v>
       </x:c>
-      <x:c r="G102" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H102" s="9" t="str">
+      <x:c r="G102" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H102" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
-      <x:c r="A103" s="7" t="str">
+      <x:c r="A103" s="6" t="str">
         <x:v>char_GRYZMON</x:v>
       </x:c>
-      <x:c r="B103" s="8" t="str">
+      <x:c r="B103" s="7" t="str">
         <x:v>Grizzlymon</x:v>
       </x:c>
-      <x:c r="C103" s="8" t="str">
+      <x:c r="C103" s="7" t="str">
         <x:v>Гризлимон</x:v>
       </x:c>
-      <x:c r="D103" s="8" t="str">
+      <x:c r="D103" s="7" t="str">
         <x:v>Гризмон</x:v>
       </x:c>
-      <x:c r="E103" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F103" s="8" t="str">
+      <x:c r="E103" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F103" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gryzmon</x:v>
       </x:c>
-      <x:c r="G103" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H103" s="9" t="str">
+      <x:c r="G103" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H103" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
-      <x:c r="A104" s="7" t="str">
+      <x:c r="A104" s="6" t="str">
         <x:v>char_SKULLBALUCHIMON</x:v>
       </x:c>
-      <x:c r="B104" s="8" t="str">
+      <x:c r="B104" s="7" t="str">
         <x:v>SkullBaluchimon</x:v>
       </x:c>
-      <x:c r="C104" s="8" t="str">
+      <x:c r="C104" s="7" t="str">
         <x:v>СкаллБалучимон</x:v>
       </x:c>
-      <x:c r="D104" s="8" t="str">
+      <x:c r="D104" s="7" t="str">
         <x:v>Скалл Балухимон</x:v>
       </x:c>
-      <x:c r="E104" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F104" s="8" t="str">
+      <x:c r="E104" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F104" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Skull_Baluchimon</x:v>
       </x:c>
-      <x:c r="G104" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H104" s="9" t="str">
+      <x:c r="G104" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H104" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
-      <x:c r="A105" s="7" t="str">
+      <x:c r="A105" s="6" t="str">
         <x:v>char_CHOROMON</x:v>
       </x:c>
-      <x:c r="B105" s="8" t="str">
+      <x:c r="B105" s="7" t="str">
         <x:v>Choromon</x:v>
       </x:c>
-      <x:c r="C105" s="8" t="str">
+      <x:c r="C105" s="7" t="str">
         <x:v>Хоромон</x:v>
       </x:c>
-      <x:c r="D105" s="8" t="str">
+      <x:c r="D105" s="7" t="str">
         <x:v>Торомон</x:v>
       </x:c>
-      <x:c r="E105" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F105" s="8" t="str">
+      <x:c r="E105" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F105" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Choromon</x:v>
       </x:c>
-      <x:c r="G105" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H105" s="9" t="str">
+      <x:c r="G105" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H105" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
-      <x:c r="A106" s="7" t="str">
+      <x:c r="A106" s="6" t="str">
         <x:v>char_CAPROMON</x:v>
       </x:c>
-      <x:c r="B106" s="8" t="str">
+      <x:c r="B106" s="7" t="str">
         <x:v>Kapurimon</x:v>
       </x:c>
-      <x:c r="C106" s="8" t="str">
+      <x:c r="C106" s="7" t="str">
         <x:v>Капуримон</x:v>
       </x:c>
-      <x:c r="D106" s="8" t="str">
+      <x:c r="D106" s="7" t="str">
         <x:v>Капримон</x:v>
       </x:c>
-      <x:c r="E106" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F106" s="8" t="str">
+      <x:c r="E106" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F106" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Caprimon</x:v>
       </x:c>
-      <x:c r="G106" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H106" s="9" t="str">
+      <x:c r="G106" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H106" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
-      <x:c r="A107" s="7" t="str">
+      <x:c r="A107" s="6" t="str">
         <x:v>char_METALGREYMON</x:v>
       </x:c>
-      <x:c r="B107" s="8" t="str">
+      <x:c r="B107" s="7" t="str">
         <x:v>MetalGreymon</x:v>
       </x:c>
-      <x:c r="C107" s="8" t="str">
+      <x:c r="C107" s="7" t="str">
         <x:v>МеталГреймон</x:v>
       </x:c>
-      <x:c r="D107" s="8" t="str">
+      <x:c r="D107" s="7" t="str">
         <x:v>Металл Греймон</x:v>
       </x:c>
-      <x:c r="E107" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F107" s="8" t="str">
+      <x:c r="E107" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F107" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Metal_Greymon</x:v>
       </x:c>
-      <x:c r="G107" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H107" s="9" t="str">
+      <x:c r="G107" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H107" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
-      <x:c r="A108" s="7" t="str">
+      <x:c r="A108" s="6" t="str">
         <x:v>char_PIYOMON</x:v>
       </x:c>
-      <x:c r="B108" s="8" t="str">
+      <x:c r="B108" s="7" t="str">
         <x:v>Biyomon</x:v>
       </x:c>
-      <x:c r="C108" s="8" t="str">
+      <x:c r="C108" s="7" t="str">
         <x:v>Бийомон</x:v>
       </x:c>
-      <x:c r="D108" s="8" t="str">
+      <x:c r="D108" s="7" t="str">
         <x:v>Пиёмон</x:v>
       </x:c>
-      <x:c r="E108" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F108" s="8" t="str">
+      <x:c r="E108" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F108" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Piyomon</x:v>
       </x:c>
-      <x:c r="G108" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H108" s="9" t="str">
+      <x:c r="G108" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H108" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
-      <x:c r="A109" s="7" t="str">
+      <x:c r="A109" s="6" t="str">
         <x:v>char_BIRDRAMON</x:v>
       </x:c>
-      <x:c r="B109" s="8" t="str">
+      <x:c r="B109" s="7" t="str">
         <x:v>Birdramon</x:v>
       </x:c>
-      <x:c r="C109" s="8" t="str">
+      <x:c r="C109" s="7" t="str">
         <x:v>Бирдрамон</x:v>
       </x:c>
-      <x:c r="D109" s="8" t="str">
+      <x:c r="D109" s="7" t="str">
         <x:v>Бёрдрамон</x:v>
       </x:c>
-      <x:c r="E109" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F109" s="8" t="str">
+      <x:c r="E109" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F109" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Birdramon</x:v>
       </x:c>
-      <x:c r="G109" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H109" s="9" t="str">
+      <x:c r="G109" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H109" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
-      <x:c r="A110" s="7" t="str">
+      <x:c r="A110" s="6" t="str">
         <x:v>char_METALETEMON</x:v>
       </x:c>
-      <x:c r="B110" s="8" t="str">
+      <x:c r="B110" s="7" t="str">
         <x:v>MetalEtemon</x:v>
       </x:c>
-      <x:c r="C110" s="8" t="str">
+      <x:c r="C110" s="7" t="str">
         <x:v>МеталлЭтемон</x:v>
       </x:c>
-      <x:c r="D110" s="8" t="str">
+      <x:c r="D110" s="7" t="str">
         <x:v>Металл Этемон</x:v>
       </x:c>
-      <x:c r="E110" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F110" s="8" t="str">
+      <x:c r="E110" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F110" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Metal_Etemon</x:v>
       </x:c>
-      <x:c r="G110" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H110" s="9" t="str">
+      <x:c r="G110" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H110" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
-      <x:c r="A111" s="7" t="str">
+      <x:c r="A111" s="6" t="str">
         <x:v>char_VEGIMON</x:v>
       </x:c>
-      <x:c r="B111" s="8" t="str">
+      <x:c r="B111" s="7" t="str">
         <x:v>Vegiemon</x:v>
       </x:c>
-      <x:c r="C111" s="8" t="str">
+      <x:c r="C111" s="7" t="str">
         <x:v>Вегиемон</x:v>
       </x:c>
-      <x:c r="D111" s="8" t="str">
+      <x:c r="D111" s="7" t="str">
         <x:v>Вегимон</x:v>
       </x:c>
-      <x:c r="E111" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F111" s="8" t="str">
+      <x:c r="E111" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F111" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Vegimon</x:v>
       </x:c>
-      <x:c r="G111" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H111" s="9" t="str">
+      <x:c r="G111" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H111" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
-      <x:c r="A112" s="7" t="str">
+      <x:c r="A112" s="6" t="str">
         <x:v>char_POYOMON</x:v>
       </x:c>
-      <x:c r="B112" s="8" t="str">
+      <x:c r="B112" s="7" t="str">
         <x:v>Poyomon</x:v>
       </x:c>
-      <x:c r="C112" s="8" t="str">
+      <x:c r="C112" s="7" t="str">
         <x:v>Поймон</x:v>
       </x:c>
-      <x:c r="D112" s="8" t="str">
+      <x:c r="D112" s="7" t="str">
         <x:v>Поёмон</x:v>
       </x:c>
-      <x:c r="E112" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F112" s="8" t="str">
+      <x:c r="E112" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F112" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Poyomon</x:v>
       </x:c>
-      <x:c r="G112" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H112" s="9" t="str">
+      <x:c r="G112" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H112" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
-      <x:c r="A113" s="7" t="str">
+      <x:c r="A113" s="6" t="str">
         <x:v>char_WANYAMON</x:v>
       </x:c>
-      <x:c r="B113" s="8" t="str">
+      <x:c r="B113" s="7" t="str">
         <x:v>Wanyamon</x:v>
       </x:c>
-      <x:c r="C113" s="8" t="str">
+      <x:c r="C113" s="7" t="str">
         <x:v>Ваньямон</x:v>
       </x:c>
-      <x:c r="D113" s="8" t="str">
+      <x:c r="D113" s="7" t="str">
         <x:v>Ванямон</x:v>
       </x:c>
-      <x:c r="E113" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F113" s="8" t="str">
+      <x:c r="E113" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F113" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Wanyamon</x:v>
       </x:c>
-      <x:c r="G113" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H113" s="9" t="str">
+      <x:c r="G113" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H113" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
-      <x:c r="A114" s="7" t="str">
+      <x:c r="A114" s="6" t="str">
         <x:v>char_ANCIENTWISETMON</x:v>
       </x:c>
-      <x:c r="B114" s="8" t="str">
+      <x:c r="B114" s="7" t="str">
         <x:v>AncientWisemon</x:v>
       </x:c>
-      <x:c r="C114" s="8" t="str">
+      <x:c r="C114" s="7" t="str">
         <x:v>ЭншиентВайсмон</x:v>
       </x:c>
-      <x:c r="D114" s="8" t="str">
+      <x:c r="D114" s="7" t="str">
         <x:v>Древний Вайзмон</x:v>
       </x:c>
-      <x:c r="E114" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F114" s="8" t="str">
+      <x:c r="E114" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F114" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Ancient_Wisemon</x:v>
       </x:c>
-      <x:c r="G114" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H114" s="9" t="str">
+      <x:c r="G114" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H114" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
-      <x:c r="A115" s="7" t="str">
+      <x:c r="A115" s="6" t="str">
         <x:v>char_GUARDROMON</x:v>
       </x:c>
-      <x:c r="B115" s="8" t="str">
+      <x:c r="B115" s="7" t="str">
         <x:v>Guardromon</x:v>
       </x:c>
-      <x:c r="C115" s="8" t="str">
+      <x:c r="C115" s="7" t="str">
         <x:v>Гвардромон</x:v>
       </x:c>
-      <x:c r="D115" s="8" t="str">
+      <x:c r="D115" s="7" t="str">
         <x:v>Гардромон</x:v>
       </x:c>
-      <x:c r="E115" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F115" s="8" t="str">
+      <x:c r="E115" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F115" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Guardromon</x:v>
       </x:c>
-      <x:c r="G115" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H115" s="9" t="str">
+      <x:c r="G115" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H115" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
-      <x:c r="A116" s="7" t="str">
+      <x:c r="A116" s="6" t="str">
         <x:v>char_TOGEMON</x:v>
       </x:c>
-      <x:c r="B116" s="8" t="str">
+      <x:c r="B116" s="7" t="str">
         <x:v>Togemon</x:v>
       </x:c>
-      <x:c r="C116" s="8" t="str">
+      <x:c r="C116" s="7" t="str">
         <x:v>Тогемон</x:v>
       </x:c>
-      <x:c r="D116" s="8" t="str">
+      <x:c r="D116" s="7" t="str">
         <x:v>Тогэмон</x:v>
       </x:c>
-      <x:c r="E116" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F116" s="8" t="str">
+      <x:c r="E116" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F116" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Togemon</x:v>
       </x:c>
-      <x:c r="G116" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H116" s="9" t="str">
+      <x:c r="G116" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H116" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
-      <x:c r="A117" s="7" t="str">
+      <x:c r="A117" s="6" t="str">
         <x:v>char_EXSAON_BOSS</x:v>
       </x:c>
-      <x:c r="B117" s="8" t="str">
+      <x:c r="B117" s="7" t="str">
         <x:v>Examon (Boss)</x:v>
       </x:c>
-      <x:c r="C117" s="8" t="str">
+      <x:c r="C117" s="7" t="str">
         <x:v>Экзамон (Босс)</x:v>
       </x:c>
-      <x:c r="D117" s="8" t="str">
+      <x:c r="D117" s="7" t="str">
         <x:v>Эксамон (босс)</x:v>
       </x:c>
-      <x:c r="E117" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F117" s="8" t="str">
+      <x:c r="E117" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F117" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Examon</x:v>
       </x:c>
-      <x:c r="G117" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H117" s="9" t="str">
+      <x:c r="G117" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H117" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
-      <x:c r="A118" s="7" t="str">
+      <x:c r="A118" s="6" t="str">
         <x:v>char_PLOTMON</x:v>
       </x:c>
-      <x:c r="B118" s="8" t="str">
+      <x:c r="B118" s="7" t="str">
         <x:v>Salamon</x:v>
       </x:c>
-      <x:c r="C118" s="8" t="str">
+      <x:c r="C118" s="7" t="str">
         <x:v>Саламон</x:v>
       </x:c>
-      <x:c r="D118" s="8" t="str">
+      <x:c r="D118" s="7" t="str">
         <x:v>Плотмон</x:v>
       </x:c>
-      <x:c r="E118" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F118" s="8" t="str">
+      <x:c r="E118" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F118" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Plotmon</x:v>
       </x:c>
-      <x:c r="G118" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H118" s="9" t="str">
+      <x:c r="G118" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H118" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
-      <x:c r="A119" s="7" t="str">
+      <x:c r="A119" s="6" t="str">
         <x:v>char_XV-MON</x:v>
       </x:c>
-      <x:c r="B119" s="8" t="str">
+      <x:c r="B119" s="7" t="str">
         <x:v>ExVeemon</x:v>
       </x:c>
-      <x:c r="C119" s="8" t="str">
+      <x:c r="C119" s="7" t="str">
         <x:v>ЭксВиимон</x:v>
       </x:c>
-      <x:c r="D119" s="8" t="str">
+      <x:c r="D119" s="7" t="str">
         <x:v>ИксВи-мон</x:v>
       </x:c>
-      <x:c r="E119" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F119" s="8" t="str">
+      <x:c r="E119" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F119" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/XV-mon</x:v>
       </x:c>
-      <x:c r="G119" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H119" s="9" t="str">
+      <x:c r="G119" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H119" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
-      <x:c r="A120" s="7" t="str">
+      <x:c r="A120" s="6" t="str">
         <x:v>char_SHELLMON</x:v>
       </x:c>
-      <x:c r="B120" s="8" t="str">
+      <x:c r="B120" s="7" t="str">
         <x:v>Shellmon</x:v>
       </x:c>
-      <x:c r="C120" s="8" t="str">
+      <x:c r="C120" s="7" t="str">
         <x:v>Шелмон</x:v>
       </x:c>
-      <x:c r="D120" s="8" t="str">
+      <x:c r="D120" s="7" t="str">
         <x:v>Шеллмон</x:v>
       </x:c>
-      <x:c r="E120" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F120" s="8" t="str">
+      <x:c r="E120" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F120" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Shellmon</x:v>
       </x:c>
-      <x:c r="G120" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H120" s="9" t="str">
+      <x:c r="G120" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H120" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
-      <x:c r="A121" s="7" t="str">
+      <x:c r="A121" s="6" t="str">
         <x:v>char_YUKIDARUMON</x:v>
       </x:c>
-      <x:c r="B121" s="8" t="str">
+      <x:c r="B121" s="7" t="str">
         <x:v>Frigimon</x:v>
       </x:c>
-      <x:c r="C121" s="8" t="str">
+      <x:c r="C121" s="7" t="str">
         <x:v>Фригимон</x:v>
       </x:c>
-      <x:c r="D121" s="8" t="str">
+      <x:c r="D121" s="7" t="str">
         <x:v>Юкидарумон</x:v>
       </x:c>
-      <x:c r="E121" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F121" s="8" t="str">
+      <x:c r="E121" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F121" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Yukidarumon</x:v>
       </x:c>
-      <x:c r="G121" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H121" s="9" t="str">
+      <x:c r="G121" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H121" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
-      <x:c r="A122" s="7" t="str">
+      <x:c r="A122" s="6" t="str">
         <x:v>char_CENTALMON</x:v>
       </x:c>
-      <x:c r="B122" s="8" t="str">
+      <x:c r="B122" s="7" t="str">
         <x:v>Centarumon</x:v>
       </x:c>
-      <x:c r="C122" s="8" t="str">
+      <x:c r="C122" s="7" t="str">
         <x:v>Центарумон</x:v>
       </x:c>
-      <x:c r="D122" s="8" t="str">
+      <x:c r="D122" s="7" t="str">
         <x:v>Кенталмон</x:v>
       </x:c>
-      <x:c r="E122" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F122" s="8" t="str">
+      <x:c r="E122" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F122" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Centalmon</x:v>
       </x:c>
-      <x:c r="G122" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H122" s="9" t="str">
+      <x:c r="G122" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H122" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
-      <x:c r="A123" s="7" t="str">
+      <x:c r="A123" s="6" t="str">
         <x:v>char_TONOSAMAGEKOMON</x:v>
       </x:c>
-      <x:c r="B123" s="8" t="str">
+      <x:c r="B123" s="7" t="str">
         <x:v>ShogunGekomon</x:v>
       </x:c>
-      <x:c r="C123" s="8" t="str">
+      <x:c r="C123" s="7" t="str">
         <x:v>СёгунГекомон</x:v>
       </x:c>
-      <x:c r="D123" s="8" t="str">
+      <x:c r="D123" s="7" t="str">
         <x:v>Тоносама Гэкомон</x:v>
       </x:c>
-      <x:c r="E123" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F123" s="8" t="str">
+      <x:c r="E123" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F123" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tonosama_Gekomon</x:v>
       </x:c>
-      <x:c r="G123" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H123" s="9" t="str">
+      <x:c r="G123" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H123" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
-      <x:c r="A124" s="7" t="str">
+      <x:c r="A124" s="6" t="str">
         <x:v>char_DELUMON</x:v>
       </x:c>
-      <x:c r="B124" s="8" t="str">
+      <x:c r="B124" s="7" t="str">
         <x:v>Deramon</x:v>
       </x:c>
-      <x:c r="C124" s="8" t="str">
+      <x:c r="C124" s="7" t="str">
         <x:v>Дерамон</x:v>
       </x:c>
-      <x:c r="D124" s="8" t="str">
+      <x:c r="D124" s="7" t="str">
         <x:v>Делюмон</x:v>
       </x:c>
-      <x:c r="E124" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F124" s="8" t="str">
+      <x:c r="E124" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F124" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Delumon</x:v>
       </x:c>
-      <x:c r="G124" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H124" s="9" t="str">
+      <x:c r="G124" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H124" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
-      <x:c r="A125" s="7" t="str">
+      <x:c r="A125" s="6" t="str">
         <x:v>char_GERBEMON</x:v>
       </x:c>
-      <x:c r="B125" s="8" t="str">
+      <x:c r="B125" s="7" t="str">
         <x:v>Garbagemon</x:v>
       </x:c>
-      <x:c r="C125" s="8" t="str">
+      <x:c r="C125" s="7" t="str">
         <x:v>Гарбэджмон</x:v>
       </x:c>
-      <x:c r="D125" s="8" t="str">
+      <x:c r="D125" s="7" t="str">
         <x:v>Гербемон</x:v>
       </x:c>
-      <x:c r="E125" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F125" s="8" t="str">
+      <x:c r="E125" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F125" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gerbemon</x:v>
       </x:c>
-      <x:c r="G125" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H125" s="9" t="str">
+      <x:c r="G125" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H125" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
-      <x:c r="A126" s="7" t="str">
+      <x:c r="A126" s="6" t="str">
         <x:v>char_MUGENDRAMON</x:v>
       </x:c>
-      <x:c r="B126" s="8" t="str">
+      <x:c r="B126" s="7" t="str">
         <x:v>Machinedramon</x:v>
       </x:c>
-      <x:c r="C126" s="8" t="str">
+      <x:c r="C126" s="7" t="str">
         <x:v>Машиндрамон</x:v>
       </x:c>
-      <x:c r="D126" s="8" t="str">
+      <x:c r="D126" s="7" t="str">
         <x:v>Мугендрамон</x:v>
       </x:c>
-      <x:c r="E126" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F126" s="8" t="str">
+      <x:c r="E126" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F126" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mugendramon</x:v>
       </x:c>
-      <x:c r="G126" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H126" s="9" t="str">
+      <x:c r="G126" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H126" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
-      <x:c r="A127" s="7" t="str">
+      <x:c r="A127" s="6" t="str">
         <x:v>char_MUGENDRAMON_BIG</x:v>
       </x:c>
-      <x:c r="B127" s="8" t="str">
+      <x:c r="B127" s="7" t="str">
         <x:v>Machinedramon</x:v>
       </x:c>
-      <x:c r="C127" s="8" t="str">
+      <x:c r="C127" s="7" t="str">
         <x:v>Машиндрамон</x:v>
       </x:c>
-      <x:c r="D127" s="8" t="str">
+      <x:c r="D127" s="7" t="str">
         <x:v>Мугендрамон</x:v>
       </x:c>
-      <x:c r="E127" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F127" s="8" t="str">
+      <x:c r="E127" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F127" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mugendramon</x:v>
       </x:c>
-      <x:c r="G127" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H127" s="9" t="str">
+      <x:c r="G127" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H127" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
-      <x:c r="A128" s="7" t="str">
+      <x:c r="A128" s="6" t="str">
         <x:v>char_BUBBMON</x:v>
       </x:c>
-      <x:c r="B128" s="8" t="str">
+      <x:c r="B128" s="7" t="str">
         <x:v>Pabumon</x:v>
       </x:c>
-      <x:c r="C128" s="8" t="str">
+      <x:c r="C128" s="7" t="str">
         <x:v>Пабумон</x:v>
       </x:c>
-      <x:c r="D128" s="8" t="str">
+      <x:c r="D128" s="7" t="str">
         <x:v>Баббмон</x:v>
       </x:c>
-      <x:c r="E128" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F128" s="8" t="str">
+      <x:c r="E128" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F128" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Bubbmon</x:v>
       </x:c>
-      <x:c r="G128" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H128" s="9" t="str">
+      <x:c r="G128" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H128" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
-      <x:c r="A129" s="7" t="str">
+      <x:c r="A129" s="6" t="str">
         <x:v>char_BETAMON</x:v>
       </x:c>
-      <x:c r="B129" s="8" t="str">
+      <x:c r="B129" s="7" t="str">
         <x:v>Betamon</x:v>
       </x:c>
-      <x:c r="C129" s="8" t="str">
+      <x:c r="C129" s="7" t="str">
         <x:v>Бетамон</x:v>
       </x:c>
-      <x:c r="D129" s="8" t="str">
+      <x:c r="D129" s="7" t="str">
         <x:v>Бэтамон</x:v>
       </x:c>
-      <x:c r="E129" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F129" s="8" t="str">
+      <x:c r="E129" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F129" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Betamon</x:v>
       </x:c>
-      <x:c r="G129" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H129" s="9" t="str">
+      <x:c r="G129" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H129" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
-      <x:c r="A130" s="7" t="str">
+      <x:c r="A130" s="6" t="str">
         <x:v>char_LUCEMON</x:v>
       </x:c>
-      <x:c r="B130" s="8" t="str">
+      <x:c r="B130" s="7" t="str">
         <x:v>Lucemon</x:v>
       </x:c>
-      <x:c r="C130" s="8" t="str">
+      <x:c r="C130" s="7" t="str">
         <x:v>Люцемон</x:v>
       </x:c>
-      <x:c r="D130" s="8" t="str">
+      <x:c r="D130" s="7" t="str">
         <x:v>Люцимон</x:v>
       </x:c>
-      <x:c r="E130" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F130" s="8" t="str">
+      <x:c r="E130" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F130" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lucemon</x:v>
       </x:c>
-      <x:c r="G130" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H130" s="9" t="str">
+      <x:c r="G130" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H130" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
-      <x:c r="A131" s="7" t="str">
+      <x:c r="A131" s="6" t="str">
         <x:v>char_ORGEMON</x:v>
       </x:c>
-      <x:c r="B131" s="8" t="str">
+      <x:c r="B131" s="7" t="str">
         <x:v>Ogremon</x:v>
       </x:c>
-      <x:c r="C131" s="8" t="str">
+      <x:c r="C131" s="7" t="str">
         <x:v>Огремон</x:v>
       </x:c>
-      <x:c r="D131" s="8" t="str">
+      <x:c r="D131" s="7" t="str">
         <x:v>Оргмон</x:v>
       </x:c>
-      <x:c r="E131" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F131" s="8" t="str">
+      <x:c r="E131" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F131" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Orgemon</x:v>
       </x:c>
-      <x:c r="G131" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H131" s="9" t="str">
+      <x:c r="G131" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H131" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
-      <x:c r="A132" s="7" t="str">
+      <x:c r="A132" s="6" t="str">
         <x:v>char_KYUBIMON</x:v>
       </x:c>
-      <x:c r="B132" s="8" t="str">
+      <x:c r="B132" s="7" t="str">
         <x:v>Kyubimon</x:v>
       </x:c>
-      <x:c r="C132" s="8" t="str">
+      <x:c r="C132" s="7" t="str">
         <x:v>Кюбимон</x:v>
       </x:c>
-      <x:c r="D132" s="8" t="str">
+      <x:c r="D132" s="7" t="str">
         <x:v>Кьюбимон</x:v>
       </x:c>
-      <x:c r="E132" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F132" s="8" t="str">
+      <x:c r="E132" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F132" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Kyubimon</x:v>
       </x:c>
-      <x:c r="G132" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H132" s="9" t="str">
+      <x:c r="G132" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H132" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
-      <x:c r="A133" s="7" t="str">
+      <x:c r="A133" s="6" t="str">
         <x:v>char_DORUGAMON</x:v>
       </x:c>
-      <x:c r="B133" s="8" t="str">
+      <x:c r="B133" s="7" t="str">
         <x:v>Dorugamon</x:v>
       </x:c>
-      <x:c r="C133" s="8" t="str">
+      <x:c r="C133" s="7" t="str">
         <x:v>Доругамон</x:v>
       </x:c>
-      <x:c r="D133" s="8" t="str">
+      <x:c r="D133" s="7" t="str">
         <x:v>ДОРУгамон</x:v>
       </x:c>
-      <x:c r="E133" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F133" s="8" t="str">
+      <x:c r="E133" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F133" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/DORUgamon</x:v>
       </x:c>
-      <x:c r="G133" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H133" s="9" t="str">
+      <x:c r="G133" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H133" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
-      <x:c r="A134" s="7" t="str">
+      <x:c r="A134" s="6" t="str">
         <x:v>char_V-DRAMON</x:v>
       </x:c>
-      <x:c r="B134" s="8" t="str">
+      <x:c r="B134" s="7" t="str">
         <x:v>Veedramon</x:v>
       </x:c>
-      <x:c r="C134" s="8" t="str">
+      <x:c r="C134" s="7" t="str">
         <x:v>Ведрамон</x:v>
       </x:c>
-      <x:c r="D134" s="8" t="str">
+      <x:c r="D134" s="7" t="str">
         <x:v>Ви-драмон</x:v>
       </x:c>
-      <x:c r="E134" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F134" s="8" t="str">
+      <x:c r="E134" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F134" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/V-dramon</x:v>
       </x:c>
-      <x:c r="G134" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H134" s="9" t="str">
+      <x:c r="G134" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H134" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
-      <x:c r="A135" s="7" t="str">
+      <x:c r="A135" s="6" t="str">
         <x:v>char_GEKOMON</x:v>
       </x:c>
-      <x:c r="B135" s="8" t="str">
+      <x:c r="B135" s="7" t="str">
         <x:v>Gekomon</x:v>
       </x:c>
-      <x:c r="C135" s="8" t="str">
+      <x:c r="C135" s="7" t="str">
         <x:v>Гекомон</x:v>
       </x:c>
-      <x:c r="D135" s="8" t="str">
+      <x:c r="D135" s="7" t="str">
         <x:v>Гэкомон</x:v>
       </x:c>
-      <x:c r="E135" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F135" s="8" t="str">
+      <x:c r="E135" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F135" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gekomon</x:v>
       </x:c>
-      <x:c r="G135" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H135" s="9" t="str">
+      <x:c r="G135" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H135" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
-      <x:c r="A136" s="7" t="str">
+      <x:c r="A136" s="6" t="str">
         <x:v>char_AEROVEEDRAMON</x:v>
       </x:c>
-      <x:c r="B136" s="8" t="str">
+      <x:c r="B136" s="7" t="str">
         <x:v>AeroVeedramon</x:v>
       </x:c>
-      <x:c r="C136" s="8" t="str">
+      <x:c r="C136" s="7" t="str">
         <x:v>АэроВидрамон</x:v>
       </x:c>
-      <x:c r="D136" s="8" t="str">
+      <x:c r="D136" s="7" t="str">
         <x:v>Аэро Ви-драмон</x:v>
       </x:c>
-      <x:c r="E136" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F136" s="8" t="str">
+      <x:c r="E136" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F136" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Aero_V-dramon</x:v>
       </x:c>
-      <x:c r="G136" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H136" s="9" t="str">
+      <x:c r="G136" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H136" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
-      <x:c r="A137" s="7" t="str">
+      <x:c r="A137" s="6" t="str">
         <x:v>char_SKULLGREYMON</x:v>
       </x:c>
-      <x:c r="B137" s="8" t="str">
+      <x:c r="B137" s="7" t="str">
         <x:v>SkullGreymon</x:v>
       </x:c>
-      <x:c r="C137" s="8" t="str">
+      <x:c r="C137" s="7" t="str">
         <x:v>СкулГреймон</x:v>
       </x:c>
-      <x:c r="D137" s="8" t="str">
+      <x:c r="D137" s="7" t="str">
         <x:v>Скалл Греймон</x:v>
       </x:c>
-      <x:c r="E137" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F137" s="8" t="str">
+      <x:c r="E137" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F137" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Skull_Greymon</x:v>
       </x:c>
-      <x:c r="G137" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H137" s="9" t="str">
+      <x:c r="G137" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H137" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
-      <x:c r="A138" s="7" t="str">
+      <x:c r="A138" s="6" t="str">
         <x:v>char_SKULLGREYMON_BIG</x:v>
       </x:c>
-      <x:c r="B138" s="8" t="str">
+      <x:c r="B138" s="7" t="str">
         <x:v>SkullGreymon</x:v>
       </x:c>
-      <x:c r="C138" s="8" t="str">
+      <x:c r="C138" s="7" t="str">
         <x:v>СкулГреймон</x:v>
       </x:c>
-      <x:c r="D138" s="8" t="str">
+      <x:c r="D138" s="7" t="str">
         <x:v>Скалл Греймон</x:v>
       </x:c>
-      <x:c r="E138" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F138" s="8" t="str">
+      <x:c r="E138" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F138" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Skull_Greymon</x:v>
       </x:c>
-      <x:c r="G138" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H138" s="9" t="str">
+      <x:c r="G138" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H138" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
-      <x:c r="A139" s="7" t="str">
+      <x:c r="A139" s="6" t="str">
         <x:v>char_DEATHMERAMON</x:v>
       </x:c>
-      <x:c r="B139" s="8" t="str">
+      <x:c r="B139" s="7" t="str">
         <x:v>SkullMeramon</x:v>
       </x:c>
-      <x:c r="C139" s="8" t="str">
+      <x:c r="C139" s="7" t="str">
         <x:v>СкулМерамон</x:v>
       </x:c>
-      <x:c r="D139" s="8" t="str">
+      <x:c r="D139" s="7" t="str">
         <x:v>Дес Мерамон</x:v>
       </x:c>
-      <x:c r="E139" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F139" s="8" t="str">
+      <x:c r="E139" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F139" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Death_Meramon</x:v>
       </x:c>
-      <x:c r="G139" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H139" s="9" t="str">
+      <x:c r="G139" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H139" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
-      <x:c r="A140" s="7" t="str">
+      <x:c r="A140" s="6" t="str">
         <x:v>char_PAILDRAMON</x:v>
       </x:c>
-      <x:c r="B140" s="8" t="str">
+      <x:c r="B140" s="7" t="str">
         <x:v>Paildramon</x:v>
       </x:c>
-      <x:c r="C140" s="8" t="str">
+      <x:c r="C140" s="7" t="str">
         <x:v>Пайлдрамон</x:v>
       </x:c>
-      <x:c r="D140" s="8" t="str">
+      <x:c r="D140" s="7" t="str">
         <x:v>Пейлдрамон</x:v>
       </x:c>
-      <x:c r="E140" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F140" s="8" t="str">
+      <x:c r="E140" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F140" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Paildramon</x:v>
       </x:c>
-      <x:c r="G140" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H140" s="9" t="str">
+      <x:c r="G140" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H140" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
-      <x:c r="A141" s="7" t="str">
+      <x:c r="A141" s="6" t="str">
         <x:v>char_PICKLEMON</x:v>
       </x:c>
-      <x:c r="B141" s="8" t="str">
+      <x:c r="B141" s="7" t="str">
         <x:v>Piximon</x:v>
       </x:c>
-      <x:c r="C141" s="8" t="str">
+      <x:c r="C141" s="7" t="str">
         <x:v>Пиксимон</x:v>
       </x:c>
-      <x:c r="D141" s="8" t="str">
+      <x:c r="D141" s="7" t="str">
         <x:v>Пикмон</x:v>
       </x:c>
-      <x:c r="E141" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F141" s="8" t="str">
+      <x:c r="E141" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F141" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Pickmon</x:v>
       </x:c>
-      <x:c r="G141" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H141" s="9" t="str">
+      <x:c r="G141" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H141" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
-      <x:c r="A142" s="7" t="str">
+      <x:c r="A142" s="6" t="str">
         <x:v>char_VADEMON</x:v>
       </x:c>
-      <x:c r="B142" s="8" t="str">
+      <x:c r="B142" s="7" t="str">
         <x:v>Vademon</x:v>
       </x:c>
-      <x:c r="C142" s="8" t="str">
+      <x:c r="C142" s="7" t="str">
         <x:v>Вадемон</x:v>
       </x:c>
-      <x:c r="D142" s="8" t="str">
+      <x:c r="D142" s="7" t="str">
         <x:v>Вейдмон</x:v>
       </x:c>
-      <x:c r="E142" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F142" s="8" t="str">
+      <x:c r="E142" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F142" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Vademon</x:v>
       </x:c>
-      <x:c r="G142" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H142" s="9" t="str">
+      <x:c r="G142" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H142" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
-      <x:c r="A143" s="7" t="str">
+      <x:c r="A143" s="6" t="str">
         <x:v>char_METALMAMEMON</x:v>
       </x:c>
-      <x:c r="B143" s="8" t="str">
+      <x:c r="B143" s="7" t="str">
         <x:v>MetalMamemon</x:v>
       </x:c>
-      <x:c r="C143" s="8" t="str">
+      <x:c r="C143" s="7" t="str">
         <x:v>МеталМамемон</x:v>
       </x:c>
-      <x:c r="D143" s="8" t="str">
+      <x:c r="D143" s="7" t="str">
         <x:v>Металл Мамемон</x:v>
       </x:c>
-      <x:c r="E143" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F143" s="8" t="str">
+      <x:c r="E143" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F143" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Metal_Mamemon</x:v>
       </x:c>
-      <x:c r="G143" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H143" s="9" t="str">
+      <x:c r="G143" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H143" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
-      <x:c r="A144" s="7" t="str">
+      <x:c r="A144" s="6" t="str">
         <x:v>char_PARROTMON</x:v>
       </x:c>
-      <x:c r="B144" s="8" t="str">
+      <x:c r="B144" s="7" t="str">
         <x:v>Parrotmon</x:v>
       </x:c>
-      <x:c r="C144" s="8" t="str">
+      <x:c r="C144" s="7" t="str">
         <x:v>Пэрэтмон</x:v>
       </x:c>
-      <x:c r="D144" s="8" t="str">
+      <x:c r="D144" s="7" t="str">
         <x:v>Пэрротмон</x:v>
       </x:c>
-      <x:c r="E144" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F144" s="8" t="str">
+      <x:c r="E144" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F144" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Parrotmon</x:v>
       </x:c>
-      <x:c r="G144" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H144" s="9" t="str">
+      <x:c r="G144" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H144" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
-      <x:c r="A145" s="7" t="str">
+      <x:c r="A145" s="6" t="str">
         <x:v>char_ULFORCEVDRAMON</x:v>
       </x:c>
-      <x:c r="B145" s="8" t="str">
+      <x:c r="B145" s="7" t="str">
         <x:v>UlforceVeedramon</x:v>
       </x:c>
-      <x:c r="C145" s="8" t="str">
+      <x:c r="C145" s="7" t="str">
         <x:v>АльфорсВидрамон</x:v>
       </x:c>
-      <x:c r="D145" s="8" t="str">
+      <x:c r="D145" s="7" t="str">
         <x:v>Алфорс Ви-драмон</x:v>
       </x:c>
-      <x:c r="E145" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F145" s="8" t="str">
+      <x:c r="E145" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F145" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Ulforce_V-dramon</x:v>
       </x:c>
-      <x:c r="G145" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H145" s="9" t="str">
+      <x:c r="G145" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H145" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
-      <x:c r="A146" s="7" t="str">
+      <x:c r="A146" s="6" t="str">
         <x:v>char_ULFORCEVDRAMON_BIG</x:v>
       </x:c>
-      <x:c r="B146" s="8" t="str">
+      <x:c r="B146" s="7" t="str">
         <x:v>UlforceVeedramon</x:v>
       </x:c>
-      <x:c r="C146" s="8" t="str">
+      <x:c r="C146" s="7" t="str">
         <x:v>АльфорсВидрамон</x:v>
       </x:c>
-      <x:c r="D146" s="8" t="str">
+      <x:c r="D146" s="7" t="str">
         <x:v>Алфорс Ви-драмон</x:v>
       </x:c>
-      <x:c r="E146" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F146" s="8" t="str">
+      <x:c r="E146" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F146" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Ulforce_V-dramon</x:v>
       </x:c>
-      <x:c r="G146" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H146" s="9" t="str">
+      <x:c r="G146" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H146" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
-      <x:c r="A147" s="7" t="str">
+      <x:c r="A147" s="6" t="str">
         <x:v>char_IMPERIALDRAMON_FM</x:v>
       </x:c>
-      <x:c r="B147" s="8" t="str">
+      <x:c r="B147" s="7" t="str">
         <x:v>Imperialdramon FM</x:v>
       </x:c>
-      <x:c r="C147" s="8" t="str">
+      <x:c r="C147" s="7" t="str">
         <x:v>Империалдрамон FM</x:v>
       </x:c>
-      <x:c r="D147" s="8" t="str">
+      <x:c r="D147" s="7" t="str">
         <x:v>Империалдрамон: Режим Бойца</x:v>
       </x:c>
-      <x:c r="E147" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F147" s="8" t="str">
+      <x:c r="E147" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F147" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Imperialdramon%3A_Fighter_Mode</x:v>
       </x:c>
-      <x:c r="G147" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H147" s="9" t="str">
+      <x:c r="G147" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H147" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
-      <x:c r="A148" s="7" t="str">
+      <x:c r="A148" s="6" t="str">
         <x:v>char_IMPERIALDRAMON_PM</x:v>
       </x:c>
-      <x:c r="B148" s="8" t="str">
+      <x:c r="B148" s="7" t="str">
         <x:v>Imperialdramon PM</x:v>
       </x:c>
-      <x:c r="C148" s="8" t="str">
+      <x:c r="C148" s="7" t="str">
         <x:v>Империалдрамон FM</x:v>
       </x:c>
-      <x:c r="D148" s="8" t="str">
+      <x:c r="D148" s="7" t="str">
         <x:v>Империалдрамон: Режим Паладина</x:v>
       </x:c>
-      <x:c r="E148" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F148" s="8" t="str">
+      <x:c r="E148" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F148" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Imperialdramon%3A_Paladin_Mode</x:v>
       </x:c>
-      <x:c r="G148" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H148" s="9" t="str">
+      <x:c r="G148" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H148" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
-      <x:c r="A149" s="7" t="str">
+      <x:c r="A149" s="6" t="str">
         <x:v>char_SABERLEOMON</x:v>
       </x:c>
-      <x:c r="B149" s="8" t="str">
+      <x:c r="B149" s="7" t="str">
         <x:v>SaberLeomon</x:v>
       </x:c>
-      <x:c r="C149" s="8" t="str">
+      <x:c r="C149" s="7" t="str">
         <x:v>СаберЛеомон</x:v>
       </x:c>
-      <x:c r="D149" s="8" t="str">
+      <x:c r="D149" s="7" t="str">
         <x:v>Сэйбер Леомон</x:v>
       </x:c>
-      <x:c r="E149" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F149" s="8" t="str">
+      <x:c r="E149" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F149" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Saber_Leomon</x:v>
       </x:c>
-      <x:c r="G149" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H149" s="9" t="str">
+      <x:c r="G149" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H149" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
-      <x:c r="A150" s="7" t="str">
+      <x:c r="A150" s="6" t="str">
         <x:v>char_PIEDMON</x:v>
       </x:c>
-      <x:c r="B150" s="8" t="str">
+      <x:c r="B150" s="7" t="str">
         <x:v>Piedmon</x:v>
       </x:c>
-      <x:c r="C150" s="8" t="str">
+      <x:c r="C150" s="7" t="str">
         <x:v>Пьемонт</x:v>
       </x:c>
-      <x:c r="D150" s="8" t="str">
+      <x:c r="D150" s="7" t="str">
         <x:v>Пьемон</x:v>
       </x:c>
-      <x:c r="E150" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F150" s="8" t="str">
+      <x:c r="E150" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F150" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Piemon</x:v>
       </x:c>
-      <x:c r="G150" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H150" s="9" t="str">
+      <x:c r="G150" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H150" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
-      <x:c r="A151" s="7" t="str">
+      <x:c r="A151" s="6" t="str">
         <x:v>char_PINOCHIMON</x:v>
       </x:c>
-      <x:c r="B151" s="8" t="str">
+      <x:c r="B151" s="7" t="str">
         <x:v>Puppetmon</x:v>
       </x:c>
-      <x:c r="C151" s="8" t="str">
+      <x:c r="C151" s="7" t="str">
         <x:v>Пуппетмон</x:v>
       </x:c>
-      <x:c r="D151" s="8" t="str">
+      <x:c r="D151" s="7" t="str">
         <x:v>Пиноккимон</x:v>
       </x:c>
-      <x:c r="E151" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F151" s="8" t="str">
+      <x:c r="E151" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F151" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Pinochimon</x:v>
       </x:c>
-      <x:c r="G151" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H151" s="9" t="str">
+      <x:c r="G151" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H151" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
-      <x:c r="A152" s="7" t="str">
+      <x:c r="A152" s="6" t="str">
         <x:v>char_METALSEADRAMON</x:v>
       </x:c>
-      <x:c r="B152" s="8" t="str">
+      <x:c r="B152" s="7" t="str">
         <x:v>MetalSeadramon</x:v>
       </x:c>
-      <x:c r="C152" s="8" t="str">
+      <x:c r="C152" s="7" t="str">
         <x:v>МеталСидрамон</x:v>
       </x:c>
-      <x:c r="D152" s="8" t="str">
+      <x:c r="D152" s="7" t="str">
         <x:v>Металл Сидрамон</x:v>
       </x:c>
-      <x:c r="E152" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F152" s="8" t="str">
+      <x:c r="E152" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F152" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Metal_Seadramon</x:v>
       </x:c>
-      <x:c r="G152" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H152" s="9" t="str">
+      <x:c r="G152" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H152" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
-      <x:c r="A153" s="7" t="str">
+      <x:c r="A153" s="6" t="str">
         <x:v>char_LUCEMON_SM</x:v>
       </x:c>
-      <x:c r="B153" s="8" t="str">
+      <x:c r="B153" s="7" t="str">
         <x:v>Lucemon SM</x:v>
       </x:c>
-      <x:c r="C153" s="8" t="str">
+      <x:c r="C153" s="7" t="str">
         <x:v>Люцемон СМ</x:v>
       </x:c>
-      <x:c r="D153" s="8" t="str">
+      <x:c r="D153" s="7" t="str">
         <x:v>Люцимон: режим Сатаны</x:v>
       </x:c>
-      <x:c r="E153" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F153" s="8" t="str">
+      <x:c r="E153" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F153" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lucemon%3A_Satan_Mode</x:v>
       </x:c>
-      <x:c r="G153" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H153" s="9" t="str">
+      <x:c r="G153" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H153" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
-      <x:c r="A154" s="7" t="str">
+      <x:c r="A154" s="6" t="str">
         <x:v>char_LUCEMON_SM_BIG</x:v>
       </x:c>
-      <x:c r="B154" s="8" t="str">
+      <x:c r="B154" s="7" t="str">
         <x:v>Lucemon SM</x:v>
       </x:c>
-      <x:c r="C154" s="8" t="str">
+      <x:c r="C154" s="7" t="str">
         <x:v>Люцемон СМ</x:v>
       </x:c>
-      <x:c r="D154" s="8" t="str">
+      <x:c r="D154" s="7" t="str">
         <x:v>Люцимон: режим Сатаны</x:v>
       </x:c>
-      <x:c r="E154" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F154" s="8" t="str">
+      <x:c r="E154" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F154" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lucemon%3A_Satan_Mode</x:v>
       </x:c>
-      <x:c r="G154" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H154" s="9" t="str">
+      <x:c r="G154" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H154" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
-      <x:c r="A155" s="7" t="str">
+      <x:c r="A155" s="6" t="str">
         <x:v>char_TITAMON_2</x:v>
       </x:c>
-      <x:c r="B155" s="8" t="str">
+      <x:c r="B155" s="7" t="str">
         <x:v>Titamon (Berserk)</x:v>
       </x:c>
-      <x:c r="C155" s="8" t="str">
+      <x:c r="C155" s="7" t="str">
         <x:v>Титамон (Берсерк)</x:v>
       </x:c>
-      <x:c r="D155" s="8" t="str">
+      <x:c r="D155" s="7" t="str">
         <x:v>Титамон (берсерк)</x:v>
       </x:c>
-      <x:c r="E155" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F155" s="8" t="str">
+      <x:c r="E155" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F155" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Titamon</x:v>
       </x:c>
-      <x:c r="G155" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H155" s="9" t="str">
+      <x:c r="G155" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H155" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
-      <x:c r="A156" s="7" t="str">
+      <x:c r="A156" s="6" t="str">
         <x:v>char_TITAMON_ADD</x:v>
       </x:c>
-      <x:c r="B156" s="8" t="str">
+      <x:c r="B156" s="7" t="str">
         <x:v>Titamon (Berserk) (Twin Blades)</x:v>
       </x:c>
-      <x:c r="C156" s="8" t="str">
+      <x:c r="C156" s="7" t="str">
         <x:v>Титамон (Берсерк) (Двойные Клинки)</x:v>
       </x:c>
-      <x:c r="D156" s="8" t="str">
+      <x:c r="D156" s="7" t="str">
         <x:v>Титамон (двойные клинки)</x:v>
       </x:c>
-      <x:c r="E156" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F156" s="8" t="str">
+      <x:c r="E156" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F156" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Titamon</x:v>
       </x:c>
-      <x:c r="G156" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H156" s="9" t="str">
+      <x:c r="G156" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H156" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
-      <x:c r="A157" s="7" t="str">
+      <x:c r="A157" s="6" t="str">
         <x:v>char_TITAMON_TWIN BLADE</x:v>
       </x:c>
-      <x:c r="B157" s="8" t="str">
+      <x:c r="B157" s="7" t="str">
         <x:v>Titamon (Twin Blades)</x:v>
       </x:c>
-      <x:c r="C157" s="8" t="str">
+      <x:c r="C157" s="7" t="str">
         <x:v>Титамон (Двойные лезвия)</x:v>
       </x:c>
-      <x:c r="D157" s="8" t="str">
+      <x:c r="D157" s="7" t="str">
         <x:v>Титамон (двойные лезвия)</x:v>
       </x:c>
-      <x:c r="E157" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F157" s="8" t="str">
+      <x:c r="E157" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F157" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Titamon</x:v>
       </x:c>
-      <x:c r="G157" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H157" s="9" t="str">
+      <x:c r="G157" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H157" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
-      <x:c r="A158" s="7" t="str">
+      <x:c r="A158" s="6" t="str">
         <x:v>char_HOLYDRAMON</x:v>
       </x:c>
-      <x:c r="B158" s="8" t="str">
+      <x:c r="B158" s="7" t="str">
         <x:v>Magnadramon</x:v>
       </x:c>
-      <x:c r="C158" s="8" t="str">
+      <x:c r="C158" s="7" t="str">
         <x:v>Магнадрамон</x:v>
       </x:c>
-      <x:c r="D158" s="8" t="str">
+      <x:c r="D158" s="7" t="str">
         <x:v>Холидрамон</x:v>
       </x:c>
-      <x:c r="E158" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F158" s="8" t="str">
+      <x:c r="E158" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F158" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Holydramon</x:v>
       </x:c>
-      <x:c r="G158" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H158" s="9" t="str">
+      <x:c r="G158" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H158" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
-      <x:c r="A159" s="7" t="str">
+      <x:c r="A159" s="6" t="str">
         <x:v>char_WASPMON</x:v>
       </x:c>
-      <x:c r="B159" s="8" t="str">
+      <x:c r="B159" s="7" t="str">
         <x:v>Waspmon</x:v>
       </x:c>
-      <x:c r="C159" s="8" t="str">
+      <x:c r="C159" s="7" t="str">
         <x:v>Осмон</x:v>
       </x:c>
-      <x:c r="D159" s="8" t="str">
+      <x:c r="D159" s="7" t="str">
         <x:v>Васпмон</x:v>
       </x:c>
-      <x:c r="E159" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F159" s="8" t="str">
+      <x:c r="E159" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F159" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Waspmon</x:v>
       </x:c>
-      <x:c r="G159" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H159" s="9" t="str">
+      <x:c r="G159" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H159" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
-      <x:c r="A160" s="7" t="str">
+      <x:c r="A160" s="6" t="str">
         <x:v>char_REVOLMON</x:v>
       </x:c>
-      <x:c r="B160" s="8" t="str">
+      <x:c r="B160" s="7" t="str">
         <x:v>Deputymon</x:v>
       </x:c>
-      <x:c r="C160" s="8" t="str">
+      <x:c r="C160" s="7" t="str">
         <x:v>Депутимон</x:v>
       </x:c>
-      <x:c r="D160" s="8" t="str">
+      <x:c r="D160" s="7" t="str">
         <x:v>Револьмон</x:v>
       </x:c>
-      <x:c r="E160" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F160" s="8" t="str">
+      <x:c r="E160" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F160" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Revolmon</x:v>
       </x:c>
-      <x:c r="G160" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H160" s="9" t="str">
+      <x:c r="G160" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H160" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
-      <x:c r="A161" s="7" t="str">
+      <x:c r="A161" s="6" t="str">
         <x:v>char_DRACUMON</x:v>
       </x:c>
-      <x:c r="B161" s="8" t="str">
+      <x:c r="B161" s="7" t="str">
         <x:v>Dracmon</x:v>
       </x:c>
-      <x:c r="C161" s="8" t="str">
+      <x:c r="C161" s="7" t="str">
         <x:v>Дракомон</x:v>
       </x:c>
-      <x:c r="D161" s="8" t="str">
+      <x:c r="D161" s="7" t="str">
         <x:v>Дракумон</x:v>
       </x:c>
-      <x:c r="E161" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F161" s="8" t="str">
+      <x:c r="E161" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F161" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dracumon</x:v>
       </x:c>
-      <x:c r="G161" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H161" s="9" t="str">
+      <x:c r="G161" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H161" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
-      <x:c r="A162" s="7" t="str">
+      <x:c r="A162" s="6" t="str">
         <x:v>char_DINOHUMON</x:v>
       </x:c>
-      <x:c r="B162" s="8" t="str">
+      <x:c r="B162" s="7" t="str">
         <x:v>Dinohyumon</x:v>
       </x:c>
-      <x:c r="C162" s="8" t="str">
+      <x:c r="C162" s="7" t="str">
         <x:v>Диногьюмон</x:v>
       </x:c>
-      <x:c r="D162" s="8" t="str">
+      <x:c r="D162" s="7" t="str">
         <x:v>Динохьюмон</x:v>
       </x:c>
-      <x:c r="E162" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F162" s="8" t="str">
+      <x:c r="E162" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F162" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dinohumon</x:v>
       </x:c>
-      <x:c r="G162" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H162" s="9" t="str">
+      <x:c r="G162" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H162" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
-      <x:c r="A163" s="7" t="str">
+      <x:c r="A163" s="6" t="str">
         <x:v>char_LOADERLIOMON</x:v>
       </x:c>
-      <x:c r="B163" s="8" t="str">
+      <x:c r="B163" s="7" t="str">
         <x:v>LoaderLeomon</x:v>
       </x:c>
-      <x:c r="C163" s="8" t="str">
+      <x:c r="C163" s="7" t="str">
         <x:v>ЛоудерЛеомон</x:v>
       </x:c>
-      <x:c r="D163" s="8" t="str">
+      <x:c r="D163" s="7" t="str">
         <x:v>Лоадер Лиомон</x:v>
       </x:c>
-      <x:c r="E163" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F163" s="8" t="str">
+      <x:c r="E163" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F163" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Loader_Liomon</x:v>
       </x:c>
-      <x:c r="G163" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H163" s="9" t="str">
+      <x:c r="G163" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H163" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
-      <x:c r="A164" s="7" t="str">
+      <x:c r="A164" s="6" t="str">
         <x:v>char_AGUMON_KIZUNA</x:v>
       </x:c>
-      <x:c r="B164" s="8" t="str">
+      <x:c r="B164" s="7" t="str">
         <x:v>Agumon (Bond of Bravery)</x:v>
       </x:c>
-      <x:c r="C164" s="8" t="str">
+      <x:c r="C164" s="7" t="str">
         <x:v>Агумон (Узы Храбрости)</x:v>
       </x:c>
-      <x:c r="D164" s="8" t="str">
+      <x:c r="D164" s="7" t="str">
         <x:v>Агумон (узы храбрости)</x:v>
       </x:c>
-      <x:c r="E164" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F164" s="8" t="str">
+      <x:c r="E164" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F164" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Agumon</x:v>
       </x:c>
-      <x:c r="G164" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H164" s="9" t="str">
+      <x:c r="G164" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H164" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
-      <x:c r="A165" s="7" t="str">
+      <x:c r="A165" s="6" t="str">
         <x:v>char_GABUMON_KIZUNA</x:v>
       </x:c>
-      <x:c r="B165" s="8" t="str">
+      <x:c r="B165" s="7" t="str">
         <x:v>Gabumon (Bond of Friendship)</x:v>
       </x:c>
-      <x:c r="C165" s="8" t="str">
+      <x:c r="C165" s="7" t="str">
         <x:v>Габумон (Узы дружбы)</x:v>
       </x:c>
-      <x:c r="D165" s="8" t="str">
+      <x:c r="D165" s="7" t="str">
         <x:v>Габумон (узы дружбы)</x:v>
       </x:c>
-      <x:c r="E165" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F165" s="8" t="str">
+      <x:c r="E165" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F165" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gabumon</x:v>
       </x:c>
-      <x:c r="G165" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H165" s="9" t="str">
+      <x:c r="G165" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H165" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
-      <x:c r="A166" s="7" t="str">
+      <x:c r="A166" s="6" t="str">
         <x:v>char_CHARISMON</x:v>
       </x:c>
-      <x:c r="B166" s="8" t="str">
+      <x:c r="B166" s="7" t="str">
         <x:v>Callismon</x:v>
       </x:c>
-      <x:c r="C166" s="8" t="str">
+      <x:c r="C166" s="7" t="str">
         <x:v>Каллисон</x:v>
       </x:c>
-      <x:c r="D166" s="8" t="str">
+      <x:c r="D166" s="7" t="str">
         <x:v>Каллисмон</x:v>
       </x:c>
-      <x:c r="E166" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F166" s="8" t="str">
+      <x:c r="E166" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F166" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Callismon</x:v>
       </x:c>
-      <x:c r="G166" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H166" s="9" t="str">
+      <x:c r="G166" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H166" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
-      <x:c r="A167" s="7" t="str">
+      <x:c r="A167" s="6" t="str">
         <x:v>char_CHARISMON_LAST</x:v>
       </x:c>
-      <x:c r="B167" s="8" t="str">
+      <x:c r="B167" s="7" t="str">
         <x:v>Callismon</x:v>
       </x:c>
-      <x:c r="C167" s="8" t="str">
+      <x:c r="C167" s="7" t="str">
         <x:v>Каллисон</x:v>
       </x:c>
-      <x:c r="D167" s="8" t="str">
+      <x:c r="D167" s="7" t="str">
         <x:v>Каллисмон</x:v>
       </x:c>
-      <x:c r="E167" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F167" s="8" t="str">
+      <x:c r="E167" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F167" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Callismon</x:v>
       </x:c>
-      <x:c r="G167" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H167" s="9" t="str">
+      <x:c r="G167" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H167" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
-      <x:c r="A168" s="7" t="str">
+      <x:c r="A168" s="6" t="str">
         <x:v>char_PYOCOMON</x:v>
       </x:c>
-      <x:c r="B168" s="8" t="str">
+      <x:c r="B168" s="7" t="str">
         <x:v>Yokomon</x:v>
       </x:c>
-      <x:c r="C168" s="8" t="str">
+      <x:c r="C168" s="7" t="str">
         <x:v>Йокомон</x:v>
       </x:c>
-      <x:c r="D168" s="8" t="str">
+      <x:c r="D168" s="7" t="str">
         <x:v>Пьёкомон</x:v>
       </x:c>
-      <x:c r="E168" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F168" s="8" t="str">
+      <x:c r="E168" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F168" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Pyocomon</x:v>
       </x:c>
-      <x:c r="G168" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H168" s="9" t="str">
+      <x:c r="G168" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H168" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
-      <x:c r="A169" s="7" t="str">
+      <x:c r="A169" s="6" t="str">
         <x:v>char_TANEMON</x:v>
       </x:c>
-      <x:c r="B169" s="8" t="str">
+      <x:c r="B169" s="7" t="str">
         <x:v>Tanemon</x:v>
       </x:c>
-      <x:c r="C169" s="8" t="str">
+      <x:c r="C169" s="7" t="str">
         <x:v>Танемон</x:v>
       </x:c>
-      <x:c r="D169" s="8" t="str">
+      <x:c r="D169" s="7" t="str">
         <x:v>Танэмон</x:v>
       </x:c>
-      <x:c r="E169" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F169" s="8" t="str">
+      <x:c r="E169" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F169" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tanemon</x:v>
       </x:c>
-      <x:c r="G169" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H169" s="9" t="str">
+      <x:c r="G169" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H169" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
-      <x:c r="A170" s="7" t="str">
+      <x:c r="A170" s="6" t="str">
         <x:v>char_PUKAMON</x:v>
       </x:c>
-      <x:c r="B170" s="8" t="str">
+      <x:c r="B170" s="7" t="str">
         <x:v>Bukamon</x:v>
       </x:c>
-      <x:c r="C170" s="8" t="str">
+      <x:c r="C170" s="7" t="str">
         <x:v>Букамон</x:v>
       </x:c>
-      <x:c r="D170" s="8" t="str">
+      <x:c r="D170" s="7" t="str">
         <x:v>Пукамон</x:v>
       </x:c>
-      <x:c r="E170" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F170" s="8" t="str">
+      <x:c r="E170" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F170" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Pukamon</x:v>
       </x:c>
-      <x:c r="G170" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H170" s="9" t="str">
+      <x:c r="G170" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H170" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
-      <x:c r="A171" s="7" t="str">
+      <x:c r="A171" s="6" t="str">
         <x:v>char_YUNIMON</x:v>
       </x:c>
-      <x:c r="B171" s="8" t="str">
+      <x:c r="B171" s="7" t="str">
         <x:v>Unimon</x:v>
       </x:c>
-      <x:c r="C171" s="8" t="str">
+      <x:c r="C171" s="7" t="str">
         <x:v>Унимон</x:v>
       </x:c>
-      <x:c r="D171" s="8" t="str">
+      <x:c r="D171" s="7" t="str">
         <x:v>Юнимон</x:v>
       </x:c>
-      <x:c r="E171" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F171" s="8" t="str">
+      <x:c r="E171" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F171" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Unimon</x:v>
       </x:c>
-      <x:c r="G171" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H171" s="9" t="str">
+      <x:c r="G171" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H171" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
-      <x:c r="A172" s="7" t="str">
+      <x:c r="A172" s="6" t="str">
         <x:v>char_HYOKOMON</x:v>
       </x:c>
-      <x:c r="B172" s="8" t="str">
+      <x:c r="B172" s="7" t="str">
         <x:v>Hyokomon</x:v>
       </x:c>
-      <x:c r="C172" s="8" t="str">
+      <x:c r="C172" s="7" t="str">
         <x:v>Хекомон</x:v>
       </x:c>
-      <x:c r="D172" s="8" t="str">
+      <x:c r="D172" s="7" t="str">
         <x:v>Хёкомон</x:v>
       </x:c>
-      <x:c r="E172" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F172" s="8" t="str">
+      <x:c r="E172" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F172" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Hyokomon</x:v>
       </x:c>
-      <x:c r="G172" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H172" s="9" t="str">
+      <x:c r="G172" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H172" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
-      <x:c r="A173" s="7" t="str">
+      <x:c r="A173" s="6" t="str">
         <x:v>char_BURAIMON</x:v>
       </x:c>
-      <x:c r="B173" s="8" t="str">
+      <x:c r="B173" s="7" t="str">
         <x:v>Buraimon</x:v>
       </x:c>
-      <x:c r="C173" s="8" t="str">
+      <x:c r="C173" s="7" t="str">
         <x:v>Бураймон</x:v>
       </x:c>
-      <x:c r="D173" s="8" t="str">
+      <x:c r="D173" s="7" t="str">
         <x:v>Бураимон</x:v>
       </x:c>
-      <x:c r="E173" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F173" s="8" t="str">
+      <x:c r="E173" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F173" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Buraimon</x:v>
       </x:c>
-      <x:c r="G173" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H173" s="9" t="str">
+      <x:c r="G173" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H173" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
-      <x:c r="A174" s="7" t="str">
+      <x:c r="A174" s="6" t="str">
         <x:v>char_SNOWGOBURIMON</x:v>
       </x:c>
-      <x:c r="B174" s="8" t="str">
+      <x:c r="B174" s="7" t="str">
         <x:v>SnowGoblimon</x:v>
       </x:c>
-      <x:c r="C174" s="8" t="str">
+      <x:c r="C174" s="7" t="str">
         <x:v>СноуГоблимон</x:v>
       </x:c>
-      <x:c r="D174" s="8" t="str">
+      <x:c r="D174" s="7" t="str">
         <x:v>Сноу Гобуримон</x:v>
       </x:c>
-      <x:c r="E174" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F174" s="8" t="str">
+      <x:c r="E174" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F174" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Snow_Goburimon</x:v>
       </x:c>
-      <x:c r="G174" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H174" s="9" t="str">
+      <x:c r="G174" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H174" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
-      <x:c r="A175" s="7" t="str">
+      <x:c r="A175" s="6" t="str">
         <x:v>char_FLYMON</x:v>
       </x:c>
-      <x:c r="B175" s="8" t="str">
+      <x:c r="B175" s="7" t="str">
         <x:v>Flymon</x:v>
       </x:c>
-      <x:c r="C175" s="8" t="str">
+      <x:c r="C175" s="7" t="str">
         <x:v>Флимон</x:v>
       </x:c>
-      <x:c r="D175" s="8" t="str">
+      <x:c r="D175" s="7" t="str">
         <x:v>Флаймон</x:v>
       </x:c>
-      <x:c r="E175" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F175" s="8" t="str">
+      <x:c r="E175" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F175" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Flymon</x:v>
       </x:c>
-      <x:c r="G175" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H175" s="9" t="str">
+      <x:c r="G175" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H175" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
-      <x:c r="A176" s="7" t="str">
+      <x:c r="A176" s="6" t="str">
         <x:v>char_MAMMON</x:v>
       </x:c>
-      <x:c r="B176" s="8" t="str">
+      <x:c r="B176" s="7" t="str">
         <x:v>Mammothmon</x:v>
       </x:c>
-      <x:c r="C176" s="8" t="str">
+      <x:c r="C176" s="7" t="str">
         <x:v>Мамонтомон</x:v>
       </x:c>
-      <x:c r="D176" s="8" t="str">
+      <x:c r="D176" s="7" t="str">
         <x:v>Маммон</x:v>
       </x:c>
-      <x:c r="E176" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F176" s="8" t="str">
+      <x:c r="E176" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F176" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mammon</x:v>
       </x:c>
-      <x:c r="G176" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H176" s="9" t="str">
+      <x:c r="G176" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H176" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
-      <x:c r="A177" s="7" t="str">
+      <x:c r="A177" s="6" t="str">
         <x:v>char_MAMMON_BIG</x:v>
       </x:c>
-      <x:c r="B177" s="8" t="str">
+      <x:c r="B177" s="7" t="str">
         <x:v>Mammothmon</x:v>
       </x:c>
-      <x:c r="C177" s="8" t="str">
+      <x:c r="C177" s="7" t="str">
         <x:v>Мамонтомон</x:v>
       </x:c>
-      <x:c r="D177" s="8" t="str">
+      <x:c r="D177" s="7" t="str">
         <x:v>Маммон</x:v>
       </x:c>
-      <x:c r="E177" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F177" s="8" t="str">
+      <x:c r="E177" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F177" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mammon</x:v>
       </x:c>
-      <x:c r="G177" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H177" s="9" t="str">
+      <x:c r="G177" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H177" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
-      <x:c r="A178" s="7" t="str">
+      <x:c r="A178" s="6" t="str">
         <x:v>char_RAREMON</x:v>
       </x:c>
-      <x:c r="B178" s="8" t="str">
+      <x:c r="B178" s="7" t="str">
         <x:v>Raremon</x:v>
       </x:c>
-      <x:c r="C178" s="8" t="str">
+      <x:c r="C178" s="7" t="str">
         <x:v>Редмон</x:v>
       </x:c>
-      <x:c r="D178" s="8" t="str">
+      <x:c r="D178" s="7" t="str">
         <x:v>Рэйрмон</x:v>
       </x:c>
-      <x:c r="E178" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F178" s="8" t="str">
+      <x:c r="E178" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F178" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Raremon</x:v>
       </x:c>
-      <x:c r="G178" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H178" s="9" t="str">
+      <x:c r="G178" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H178" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
-      <x:c r="A179" s="7" t="str">
+      <x:c r="A179" s="6" t="str">
         <x:v>char_GOTTSUMON</x:v>
       </x:c>
-      <x:c r="B179" s="8" t="str">
+      <x:c r="B179" s="7" t="str">
         <x:v>Gotsumon</x:v>
       </x:c>
-      <x:c r="C179" s="8" t="str">
+      <x:c r="C179" s="7" t="str">
         <x:v>Готсумон</x:v>
       </x:c>
-      <x:c r="D179" s="8" t="str">
+      <x:c r="D179" s="7" t="str">
         <x:v>Готцумон</x:v>
       </x:c>
-      <x:c r="E179" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F179" s="8" t="str">
+      <x:c r="E179" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F179" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gottsumon</x:v>
       </x:c>
-      <x:c r="G179" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H179" s="9" t="str">
+      <x:c r="G179" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H179" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
-      <x:c r="A180" s="7" t="str">
+      <x:c r="A180" s="6" t="str">
         <x:v>char_PUMPMON</x:v>
       </x:c>
-      <x:c r="B180" s="8" t="str">
+      <x:c r="B180" s="7" t="str">
         <x:v>Pumpkinmon</x:v>
       </x:c>
-      <x:c r="C180" s="8" t="str">
+      <x:c r="C180" s="7" t="str">
         <x:v>Памкинмон</x:v>
       </x:c>
-      <x:c r="D180" s="8" t="str">
+      <x:c r="D180" s="7" t="str">
         <x:v>Пампмон</x:v>
       </x:c>
-      <x:c r="E180" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F180" s="8" t="str">
+      <x:c r="E180" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F180" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Pumpmon</x:v>
       </x:c>
-      <x:c r="G180" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H180" s="9" t="str">
+      <x:c r="G180" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H180" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
-      <x:c r="A181" s="7" t="str">
+      <x:c r="A181" s="6" t="str">
         <x:v>char_SNIMON</x:v>
       </x:c>
-      <x:c r="B181" s="8" t="str">
+      <x:c r="B181" s="7" t="str">
         <x:v>Snimon</x:v>
       </x:c>
-      <x:c r="C181" s="8" t="str">
+      <x:c r="C181" s="7" t="str">
         <x:v>Снимон</x:v>
       </x:c>
-      <x:c r="D181" s="8" t="str">
+      <x:c r="D181" s="7" t="str">
         <x:v>Снаймон</x:v>
       </x:c>
-      <x:c r="E181" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F181" s="8" t="str">
+      <x:c r="E181" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F181" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Snimon</x:v>
       </x:c>
-      <x:c r="G181" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H181" s="9" t="str">
+      <x:c r="G181" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H181" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
-      <x:c r="A182" s="7" t="str">
+      <x:c r="A182" s="6" t="str">
         <x:v>char_MEDIEVALDUKEMON</x:v>
       </x:c>
-      <x:c r="B182" s="8" t="str">
+      <x:c r="B182" s="7" t="str">
         <x:v>MedievalGallantmon</x:v>
       </x:c>
-      <x:c r="C182" s="8" t="str">
+      <x:c r="C182" s="7" t="str">
         <x:v>МедивалГаллантмон</x:v>
       </x:c>
-      <x:c r="D182" s="8" t="str">
+      <x:c r="D182" s="7" t="str">
         <x:v>Средневековый Дюкмон</x:v>
       </x:c>
-      <x:c r="E182" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F182" s="8" t="str">
+      <x:c r="E182" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F182" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Medieval_Dukemon</x:v>
       </x:c>
-      <x:c r="G182" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H182" s="9" t="str">
+      <x:c r="G182" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H182" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
-      <x:c r="A183" s="7" t="str">
+      <x:c r="A183" s="6" t="str">
         <x:v>char_GRACENOVAMON</x:v>
       </x:c>
-      <x:c r="B183" s="8" t="str">
+      <x:c r="B183" s="7" t="str">
         <x:v>GraceNovamon</x:v>
       </x:c>
-      <x:c r="C183" s="8" t="str">
+      <x:c r="C183" s="7" t="str">
         <x:v>Грейсеновамон</x:v>
       </x:c>
-      <x:c r="D183" s="8" t="str">
+      <x:c r="D183" s="7" t="str">
         <x:v>Грейс Новамон</x:v>
       </x:c>
-      <x:c r="E183" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F183" s="8" t="str">
+      <x:c r="E183" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F183" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Grace_Novamon</x:v>
       </x:c>
-      <x:c r="G183" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H183" s="9" t="str">
+      <x:c r="G183" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H183" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
-      <x:c r="A184" s="7" t="str">
+      <x:c r="A184" s="6" t="str">
         <x:v>char_GRACENOVAMON_SUB</x:v>
       </x:c>
-      <x:c r="B184" s="8" t="str">
+      <x:c r="B184" s="7" t="str">
         <x:v>GraceNovamon</x:v>
       </x:c>
-      <x:c r="C184" s="8" t="str">
+      <x:c r="C184" s="7" t="str">
         <x:v>Грейсеновамон</x:v>
       </x:c>
-      <x:c r="D184" s="8" t="str">
+      <x:c r="D184" s="7" t="str">
         <x:v>Грейс Новамон</x:v>
       </x:c>
-      <x:c r="E184" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F184" s="8" t="str">
+      <x:c r="E184" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F184" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Grace_Novamon</x:v>
       </x:c>
-      <x:c r="G184" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H184" s="9" t="str">
+      <x:c r="G184" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H184" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
-      <x:c r="A185" s="7" t="str">
+      <x:c r="A185" s="6" t="str">
         <x:v>char_GRACENOVAMON_BIG</x:v>
       </x:c>
-      <x:c r="B185" s="8" t="str">
+      <x:c r="B185" s="7" t="str">
         <x:v>GraceNovamon</x:v>
       </x:c>
-      <x:c r="C185" s="8" t="str">
+      <x:c r="C185" s="7" t="str">
         <x:v>Грейсеновамон</x:v>
       </x:c>
-      <x:c r="D185" s="8" t="str">
+      <x:c r="D185" s="7" t="str">
         <x:v>Грейс Новамон</x:v>
       </x:c>
-      <x:c r="E185" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F185" s="8" t="str">
+      <x:c r="E185" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F185" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Grace_Novamon</x:v>
       </x:c>
-      <x:c r="G185" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H185" s="9" t="str">
+      <x:c r="G185" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H185" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
-      <x:c r="A186" s="7" t="str">
+      <x:c r="A186" s="6" t="str">
         <x:v>char_ANOMALOCARIMON</x:v>
       </x:c>
-      <x:c r="B186" s="8" t="str">
+      <x:c r="B186" s="7" t="str">
         <x:v>Scorpiomon</x:v>
       </x:c>
-      <x:c r="C186" s="8" t="str">
+      <x:c r="C186" s="7" t="str">
         <x:v>Скорпиомон</x:v>
       </x:c>
-      <x:c r="D186" s="8" t="str">
+      <x:c r="D186" s="7" t="str">
         <x:v>Аномалокаримон</x:v>
       </x:c>
-      <x:c r="E186" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F186" s="8" t="str">
+      <x:c r="E186" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F186" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Anomalocarimon</x:v>
       </x:c>
-      <x:c r="G186" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H186" s="9" t="str">
+      <x:c r="G186" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H186" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="15" hidden="0" customHeight="1">
-      <x:c r="A187" s="7" t="str">
+      <x:c r="A187" s="6" t="str">
         <x:v>char_ANOMALOCARIMON_BIG</x:v>
       </x:c>
-      <x:c r="B187" s="8" t="str">
+      <x:c r="B187" s="7" t="str">
         <x:v>Scorpiomon</x:v>
       </x:c>
-      <x:c r="C187" s="8" t="str">
+      <x:c r="C187" s="7" t="str">
         <x:v>Скорпиомон</x:v>
       </x:c>
-      <x:c r="D187" s="8" t="str">
+      <x:c r="D187" s="7" t="str">
         <x:v>Аномалокаримон</x:v>
       </x:c>
-      <x:c r="E187" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F187" s="8" t="str">
+      <x:c r="E187" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F187" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Anomalocarimon</x:v>
       </x:c>
-      <x:c r="G187" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H187" s="9" t="str">
+      <x:c r="G187" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H187" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
-      <x:c r="A188" s="7" t="str">
+      <x:c r="A188" s="6" t="str">
         <x:v>char_HANGYOMON</x:v>
       </x:c>
-      <x:c r="B188" s="8" t="str">
+      <x:c r="B188" s="7" t="str">
         <x:v>Divermon</x:v>
       </x:c>
-      <x:c r="C188" s="8" t="str">
+      <x:c r="C188" s="7" t="str">
         <x:v>Дивермон</x:v>
       </x:c>
-      <x:c r="D188" s="8" t="str">
+      <x:c r="D188" s="7" t="str">
         <x:v>Хангёмон</x:v>
       </x:c>
-      <x:c r="E188" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F188" s="8" t="str">
+      <x:c r="E188" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F188" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Hangyomon</x:v>
       </x:c>
-      <x:c r="G188" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H188" s="9" t="str">
+      <x:c r="G188" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H188" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
-      <x:c r="A189" s="7" t="str">
+      <x:c r="A189" s="6" t="str">
         <x:v>char_HANGYOMON_SCAR</x:v>
       </x:c>
-      <x:c r="B189" s="8" t="str">
+      <x:c r="B189" s="7" t="str">
         <x:v>Divermon</x:v>
       </x:c>
-      <x:c r="C189" s="8" t="str">
+      <x:c r="C189" s="7" t="str">
         <x:v>Дивермон</x:v>
       </x:c>
-      <x:c r="D189" s="8" t="str">
+      <x:c r="D189" s="7" t="str">
         <x:v>Хангёмон</x:v>
       </x:c>
-      <x:c r="E189" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F189" s="8" t="str">
+      <x:c r="E189" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F189" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Hangyomon</x:v>
       </x:c>
-      <x:c r="G189" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H189" s="9" t="str">
+      <x:c r="G189" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H189" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
-      <x:c r="A190" s="7" t="str">
+      <x:c r="A190" s="6" t="str">
         <x:v>char_HANGYOMON_SCARF</x:v>
       </x:c>
-      <x:c r="B190" s="8" t="str">
+      <x:c r="B190" s="7" t="str">
         <x:v>Divermon</x:v>
       </x:c>
-      <x:c r="C190" s="8" t="str">
+      <x:c r="C190" s="7" t="str">
         <x:v>Дивермон</x:v>
       </x:c>
-      <x:c r="D190" s="8" t="str">
+      <x:c r="D190" s="7" t="str">
         <x:v>Хангёмон</x:v>
       </x:c>
-      <x:c r="E190" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F190" s="8" t="str">
+      <x:c r="E190" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F190" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Hangyomon</x:v>
       </x:c>
-      <x:c r="G190" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H190" s="9" t="str">
+      <x:c r="G190" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H190" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
-      <x:c r="A191" s="7" t="str">
+      <x:c r="A191" s="6" t="str">
         <x:v>char_MUSHMON</x:v>
       </x:c>
-      <x:c r="B191" s="8" t="str">
+      <x:c r="B191" s="7" t="str">
         <x:v>Mushroomon</x:v>
       </x:c>
-      <x:c r="C191" s="8" t="str">
+      <x:c r="C191" s="7" t="str">
         <x:v>Машрумон</x:v>
       </x:c>
-      <x:c r="D191" s="8" t="str">
+      <x:c r="D191" s="7" t="str">
         <x:v>Машмон</x:v>
       </x:c>
-      <x:c r="E191" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F191" s="8" t="str">
+      <x:c r="E191" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F191" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mushmon</x:v>
       </x:c>
-      <x:c r="G191" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H191" s="9" t="str">
+      <x:c r="G191" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H191" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
-      <x:c r="A192" s="7" t="str">
+      <x:c r="A192" s="6" t="str">
         <x:v>char_CLAVISANGEMON</x:v>
       </x:c>
-      <x:c r="B192" s="8" t="str">
+      <x:c r="B192" s="7" t="str">
         <x:v>ClavisAngemon</x:v>
       </x:c>
-      <x:c r="C192" s="8" t="str">
+      <x:c r="C192" s="7" t="str">
         <x:v>КлависАнгемон</x:v>
       </x:c>
-      <x:c r="D192" s="8" t="str">
+      <x:c r="D192" s="7" t="str">
         <x:v>Клавис Ангемон</x:v>
       </x:c>
-      <x:c r="E192" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F192" s="8" t="str">
+      <x:c r="E192" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F192" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Clavis_Angemon</x:v>
       </x:c>
-      <x:c r="G192" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H192" s="9" t="str">
+      <x:c r="G192" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H192" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
-      <x:c r="A193" s="7" t="str">
+      <x:c r="A193" s="6" t="str">
         <x:v>char_CLAVISANGEMON_BIG</x:v>
       </x:c>
-      <x:c r="B193" s="8" t="str">
+      <x:c r="B193" s="7" t="str">
         <x:v>ClavisAngemon</x:v>
       </x:c>
-      <x:c r="C193" s="8" t="str">
+      <x:c r="C193" s="7" t="str">
         <x:v>КлависАнгемон</x:v>
       </x:c>
-      <x:c r="D193" s="8" t="str">
+      <x:c r="D193" s="7" t="str">
         <x:v>Клавис Ангемон</x:v>
       </x:c>
-      <x:c r="E193" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F193" s="8" t="str">
+      <x:c r="E193" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F193" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Clavis_Angemon</x:v>
       </x:c>
-      <x:c r="G193" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H193" s="9" t="str">
+      <x:c r="G193" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H193" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
-      <x:c r="A194" s="7" t="str">
+      <x:c r="A194" s="6" t="str">
         <x:v>char_MECHANORIMON</x:v>
       </x:c>
-      <x:c r="B194" s="8" t="str">
+      <x:c r="B194" s="7" t="str">
         <x:v>Mekanorimon</x:v>
       </x:c>
-      <x:c r="C194" s="8" t="str">
+      <x:c r="C194" s="7" t="str">
         <x:v>Меканоримон</x:v>
       </x:c>
-      <x:c r="D194" s="8" t="str">
+      <x:c r="D194" s="7" t="str">
         <x:v>Механоримон</x:v>
       </x:c>
-      <x:c r="E194" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F194" s="8" t="str">
+      <x:c r="E194" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F194" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mechanorimon</x:v>
       </x:c>
-      <x:c r="G194" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H194" s="9" t="str">
+      <x:c r="G194" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H194" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
-      <x:c r="A195" s="7" t="str">
+      <x:c r="A195" s="6" t="str">
         <x:v>char_PENMON</x:v>
       </x:c>
-      <x:c r="B195" s="8" t="str">
+      <x:c r="B195" s="7" t="str">
         <x:v>Penmon</x:v>
       </x:c>
-      <x:c r="C195" s="8" t="str">
+      <x:c r="C195" s="7" t="str">
         <x:v>Пенмон</x:v>
       </x:c>
-      <x:c r="D195" s="8" t="str">
+      <x:c r="D195" s="7" t="str">
         <x:v>Пинмон</x:v>
       </x:c>
-      <x:c r="E195" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F195" s="8" t="str">
+      <x:c r="E195" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F195" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Penmon</x:v>
       </x:c>
-      <x:c r="G195" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H195" s="9" t="str">
+      <x:c r="G195" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H195" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
-      <x:c r="A196" s="7" t="str">
+      <x:c r="A196" s="6" t="str">
         <x:v>char_TSUMEMON</x:v>
       </x:c>
-      <x:c r="B196" s="8" t="str">
+      <x:c r="B196" s="7" t="str">
         <x:v>Tsumemon</x:v>
       </x:c>
-      <x:c r="C196" s="8" t="str">
+      <x:c r="C196" s="7" t="str">
         <x:v>Цумемон</x:v>
       </x:c>
-      <x:c r="D196" s="8" t="str">
+      <x:c r="D196" s="7" t="str">
         <x:v>Цумэмон</x:v>
       </x:c>
-      <x:c r="E196" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F196" s="8" t="str">
+      <x:c r="E196" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F196" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Tsumemon</x:v>
       </x:c>
-      <x:c r="G196" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H196" s="9" t="str">
+      <x:c r="G196" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H196" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
-      <x:c r="A197" s="7" t="str">
+      <x:c r="A197" s="6" t="str">
         <x:v>char_MAGNAGARURUMON_SEPARATION</x:v>
       </x:c>
-      <x:c r="B197" s="8" t="str">
+      <x:c r="B197" s="7" t="str">
         <x:v>MagnaGarurumon (Detached)</x:v>
       </x:c>
-      <x:c r="C197" s="8" t="str">
+      <x:c r="C197" s="7" t="str">
         <x:v>МагнаГарурумон (Открепленный)</x:v>
       </x:c>
-      <x:c r="D197" s="8" t="str">
+      <x:c r="D197" s="7" t="str">
         <x:v>Магна Гарурумон (открепленный)</x:v>
       </x:c>
-      <x:c r="E197" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F197" s="8" t="str">
+      <x:c r="E197" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F197" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Magna_Garurumon</x:v>
       </x:c>
-      <x:c r="G197" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H197" s="9" t="str">
+      <x:c r="G197" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H197" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
-      <x:c r="A198" s="7" t="str">
+      <x:c r="A198" s="6" t="str">
         <x:v>char_AGNIMON</x:v>
       </x:c>
-      <x:c r="B198" s="8" t="str">
+      <x:c r="B198" s="7" t="str">
         <x:v>Agunimon</x:v>
       </x:c>
-      <x:c r="C198" s="8" t="str">
+      <x:c r="C198" s="7" t="str">
         <x:v>Агунимон</x:v>
       </x:c>
-      <x:c r="D198" s="8" t="str">
+      <x:c r="D198" s="7" t="str">
         <x:v>Агнимон</x:v>
       </x:c>
-      <x:c r="E198" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F198" s="8" t="str">
+      <x:c r="E198" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F198" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Agnimon</x:v>
       </x:c>
-      <x:c r="G198" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H198" s="9" t="str">
+      <x:c r="G198" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H198" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
-      <x:c r="A199" s="7" t="str">
+      <x:c r="A199" s="6" t="str">
         <x:v>char_KAISERGREYMON</x:v>
       </x:c>
-      <x:c r="B199" s="8" t="str">
+      <x:c r="B199" s="7" t="str">
         <x:v>EmperorGreymon</x:v>
       </x:c>
-      <x:c r="C199" s="8" t="str">
+      <x:c r="C199" s="7" t="str">
         <x:v>ИмпериорГреймон</x:v>
       </x:c>
-      <x:c r="D199" s="8" t="str">
+      <x:c r="D199" s="7" t="str">
         <x:v>Кайзер Греймон</x:v>
       </x:c>
-      <x:c r="E199" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F199" s="8" t="str">
+      <x:c r="E199" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F199" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Kaiser_Greymon</x:v>
       </x:c>
-      <x:c r="G199" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H199" s="9" t="str">
+      <x:c r="G199" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H199" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
-      <x:c r="A200" s="7" t="str">
+      <x:c r="A200" s="6" t="str">
         <x:v>char_MAGNAGARURUMON</x:v>
       </x:c>
-      <x:c r="B200" s="8" t="str">
+      <x:c r="B200" s="7" t="str">
         <x:v>MagnaGarurumon</x:v>
       </x:c>
-      <x:c r="C200" s="8" t="str">
+      <x:c r="C200" s="7" t="str">
         <x:v>МагнаГарурумон</x:v>
       </x:c>
-      <x:c r="D200" s="8" t="str">
+      <x:c r="D200" s="7" t="str">
         <x:v>Магна Гарурумон</x:v>
       </x:c>
-      <x:c r="E200" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F200" s="8" t="str">
+      <x:c r="E200" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F200" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Magna_Garurumon</x:v>
       </x:c>
-      <x:c r="G200" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H200" s="9" t="str">
+      <x:c r="G200" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H200" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
-      <x:c r="A201" s="7" t="str">
+      <x:c r="A201" s="6" t="str">
         <x:v>char_VRITRAMON</x:v>
       </x:c>
-      <x:c r="B201" s="8" t="str">
+      <x:c r="B201" s="7" t="str">
         <x:v>BurningGreymon</x:v>
       </x:c>
-      <x:c r="C201" s="8" t="str">
+      <x:c r="C201" s="7" t="str">
         <x:v>БёрнингГреймон</x:v>
       </x:c>
-      <x:c r="D201" s="8" t="str">
+      <x:c r="D201" s="7" t="str">
         <x:v>Вритрамон</x:v>
       </x:c>
-      <x:c r="E201" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F201" s="8" t="str">
+      <x:c r="E201" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F201" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Vritramon</x:v>
       </x:c>
-      <x:c r="G201" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H201" s="9" t="str">
+      <x:c r="G201" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H201" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
-      <x:c r="A202" s="7" t="str">
+      <x:c r="A202" s="6" t="str">
         <x:v>char_WOLFMON</x:v>
       </x:c>
-      <x:c r="B202" s="8" t="str">
+      <x:c r="B202" s="7" t="str">
         <x:v>Lobomon</x:v>
       </x:c>
-      <x:c r="C202" s="8" t="str">
+      <x:c r="C202" s="7" t="str">
         <x:v>Лобомон</x:v>
       </x:c>
-      <x:c r="D202" s="8" t="str">
+      <x:c r="D202" s="7" t="str">
         <x:v>Вольфмон</x:v>
       </x:c>
-      <x:c r="E202" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F202" s="8" t="str">
+      <x:c r="E202" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F202" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Wolfmon</x:v>
       </x:c>
-      <x:c r="G202" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H202" s="9" t="str">
+      <x:c r="G202" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H202" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
-      <x:c r="A203" s="7" t="str">
+      <x:c r="A203" s="6" t="str">
         <x:v>char_GARUMMON</x:v>
       </x:c>
-      <x:c r="B203" s="8" t="str">
+      <x:c r="B203" s="7" t="str">
         <x:v>KendoGarurumon</x:v>
       </x:c>
-      <x:c r="C203" s="8" t="str">
+      <x:c r="C203" s="7" t="str">
         <x:v>КендоГарурумон</x:v>
       </x:c>
-      <x:c r="D203" s="8" t="str">
+      <x:c r="D203" s="7" t="str">
         <x:v>Гаруммон</x:v>
       </x:c>
-      <x:c r="E203" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F203" s="8" t="str">
+      <x:c r="E203" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F203" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Garummon</x:v>
       </x:c>
-      <x:c r="G203" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H203" s="9" t="str">
+      <x:c r="G203" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H203" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
-      <x:c r="A204" s="7" t="str">
+      <x:c r="A204" s="6" t="str">
         <x:v>char_OMEGASHOUTMON</x:v>
       </x:c>
-      <x:c r="B204" s="8" t="str">
+      <x:c r="B204" s="7" t="str">
         <x:v>OmniShoutmon</x:v>
       </x:c>
-      <x:c r="C204" s="8" t="str">
+      <x:c r="C204" s="7" t="str">
         <x:v>ОмниШаутмон</x:v>
       </x:c>
-      <x:c r="D204" s="8" t="str">
+      <x:c r="D204" s="7" t="str">
         <x:v>Омега Шаутмон</x:v>
       </x:c>
-      <x:c r="E204" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F204" s="8" t="str">
+      <x:c r="E204" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F204" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Omega_Shoutmon</x:v>
       </x:c>
-      <x:c r="G204" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H204" s="9" t="str">
+      <x:c r="G204" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H204" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
-      <x:c r="A205" s="7" t="str">
+      <x:c r="A205" s="6" t="str">
         <x:v>char_GANKOOMON</x:v>
       </x:c>
-      <x:c r="B205" s="8" t="str">
+      <x:c r="B205" s="7" t="str">
         <x:v>Gankoomon</x:v>
       </x:c>
-      <x:c r="C205" s="8" t="str">
+      <x:c r="C205" s="7" t="str">
         <x:v>Ганкумон</x:v>
       </x:c>
-      <x:c r="D205" s="8" t="str">
+      <x:c r="D205" s="7" t="str">
         <x:v>Гэнкумон</x:v>
       </x:c>
-      <x:c r="E205" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F205" s="8" t="str">
+      <x:c r="E205" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F205" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Gankoomon</x:v>
       </x:c>
-      <x:c r="G205" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H205" s="9" t="str">
+      <x:c r="G205" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H205" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
-      <x:c r="A206" s="7" t="str">
+      <x:c r="A206" s="6" t="str">
         <x:v>char_ZUBAEAGERMON</x:v>
       </x:c>
-      <x:c r="B206" s="8" t="str">
+      <x:c r="B206" s="7" t="str">
         <x:v>ZubaEagermon</x:v>
       </x:c>
-      <x:c r="C206" s="8" t="str">
+      <x:c r="C206" s="7" t="str">
         <x:v>Зубагермон</x:v>
       </x:c>
-      <x:c r="D206" s="8" t="str">
+      <x:c r="D206" s="7" t="str">
         <x:v>Зубаигермон</x:v>
       </x:c>
-      <x:c r="E206" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F206" s="8" t="str">
+      <x:c r="E206" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F206" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Zubaeagermon</x:v>
       </x:c>
-      <x:c r="G206" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H206" s="9" t="str">
+      <x:c r="G206" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H206" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
-      <x:c r="A207" s="7" t="str">
+      <x:c r="A207" s="6" t="str">
         <x:v>char_LOADKNIGHTMON</x:v>
       </x:c>
-      <x:c r="B207" s="8" t="str">
+      <x:c r="B207" s="7" t="str">
         <x:v>LordKnightmon</x:v>
       </x:c>
-      <x:c r="C207" s="8" t="str">
+      <x:c r="C207" s="7" t="str">
         <x:v>ЛордНайтмон</x:v>
       </x:c>
-      <x:c r="D207" s="8" t="str">
+      <x:c r="D207" s="7" t="str">
         <x:v>Лорд Найтмон</x:v>
       </x:c>
-      <x:c r="E207" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F207" s="8" t="str">
+      <x:c r="E207" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F207" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lord_Knightmon</x:v>
       </x:c>
-      <x:c r="G207" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H207" s="9" t="str">
+      <x:c r="G207" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H207" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
-      <x:c r="A208" s="7" t="str">
+      <x:c r="A208" s="6" t="str">
         <x:v>char_LOADKNIGHTMON_BIG</x:v>
       </x:c>
-      <x:c r="B208" s="8" t="str">
+      <x:c r="B208" s="7" t="str">
         <x:v>LordKnightmon</x:v>
       </x:c>
-      <x:c r="C208" s="8" t="str">
+      <x:c r="C208" s="7" t="str">
         <x:v>ЛордНайтмон</x:v>
       </x:c>
-      <x:c r="D208" s="8" t="str">
+      <x:c r="D208" s="7" t="str">
         <x:v>Лорд Найтмон</x:v>
       </x:c>
-      <x:c r="E208" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F208" s="8" t="str">
+      <x:c r="E208" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F208" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Lord_Knightmon</x:v>
       </x:c>
-      <x:c r="G208" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H208" s="9" t="str">
+      <x:c r="G208" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H208" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
-      <x:c r="A209" s="7" t="str">
+      <x:c r="A209" s="6" t="str">
         <x:v>char_HAWKMON</x:v>
       </x:c>
-      <x:c r="B209" s="8" t="str">
+      <x:c r="B209" s="7" t="str">
         <x:v>Hawkmon</x:v>
       </x:c>
-      <x:c r="C209" s="8" t="str">
+      <x:c r="C209" s="7" t="str">
         <x:v>Хокмон</x:v>
       </x:c>
-      <x:c r="D209" s="8" t="str">
+      <x:c r="D209" s="7" t="str">
         <x:v>Хоукмон</x:v>
       </x:c>
-      <x:c r="E209" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F209" s="8" t="str">
+      <x:c r="E209" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F209" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Hawkmon</x:v>
       </x:c>
-      <x:c r="G209" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H209" s="9" t="str">
+      <x:c r="G209" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H209" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
-      <x:c r="A210" s="7" t="str">
+      <x:c r="A210" s="6" t="str">
         <x:v>char_TOYAGUMON</x:v>
       </x:c>
-      <x:c r="B210" s="8" t="str">
+      <x:c r="B210" s="7" t="str">
         <x:v>ToyAgumon</x:v>
       </x:c>
-      <x:c r="C210" s="8" t="str">
+      <x:c r="C210" s="7" t="str">
         <x:v>Тойагумон</x:v>
       </x:c>
-      <x:c r="D210" s="8" t="str">
+      <x:c r="D210" s="7" t="str">
         <x:v>Той Агумон</x:v>
       </x:c>
-      <x:c r="E210" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F210" s="8" t="str">
+      <x:c r="E210" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F210" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Toy_Agumon</x:v>
       </x:c>
-      <x:c r="G210" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H210" s="9" t="str">
+      <x:c r="G210" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H210" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
-      <x:c r="A211" s="7" t="str">
+      <x:c r="A211" s="6" t="str">
         <x:v>char_TOYAGUMON_BIG</x:v>
       </x:c>
-      <x:c r="B211" s="8" t="str">
+      <x:c r="B211" s="7" t="str">
         <x:v>ToyAgumon</x:v>
       </x:c>
-      <x:c r="C211" s="8" t="str">
+      <x:c r="C211" s="7" t="str">
         <x:v>Тойагумон</x:v>
       </x:c>
-      <x:c r="D211" s="8" t="str">
+      <x:c r="D211" s="7" t="str">
         <x:v>Той Агумон</x:v>
       </x:c>
-      <x:c r="E211" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F211" s="8" t="str">
+      <x:c r="E211" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F211" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Toy_Agumon</x:v>
       </x:c>
-      <x:c r="G211" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H211" s="9" t="str">
+      <x:c r="G211" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H211" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
-      <x:c r="A212" s="7" t="str">
+      <x:c r="A212" s="6" t="str">
         <x:v>char_YATAGARAMON</x:v>
       </x:c>
-      <x:c r="B212" s="8" t="str">
+      <x:c r="B212" s="7" t="str">
         <x:v>Crowmon</x:v>
       </x:c>
-      <x:c r="C212" s="8" t="str">
+      <x:c r="C212" s="7" t="str">
         <x:v>Кромон</x:v>
       </x:c>
-      <x:c r="D212" s="8" t="str">
+      <x:c r="D212" s="7" t="str">
         <x:v>Ятагарамон</x:v>
       </x:c>
-      <x:c r="E212" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F212" s="8" t="str">
+      <x:c r="E212" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F212" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Yatagaramon</x:v>
       </x:c>
-      <x:c r="G212" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H212" s="9" t="str">
+      <x:c r="G212" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H212" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
-      <x:c r="A213" s="7" t="str">
+      <x:c r="A213" s="6" t="str">
         <x:v>char_BRAKIMON</x:v>
       </x:c>
-      <x:c r="B213" s="8" t="str">
+      <x:c r="B213" s="7" t="str">
         <x:v>Brachiomon</x:v>
       </x:c>
-      <x:c r="C213" s="8" t="str">
+      <x:c r="C213" s="7" t="str">
         <x:v>Брахиомон</x:v>
       </x:c>
-      <x:c r="D213" s="8" t="str">
+      <x:c r="D213" s="7" t="str">
         <x:v>Брахимон</x:v>
       </x:c>
-      <x:c r="E213" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F213" s="8" t="str">
+      <x:c r="E213" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F213" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Brachiomon</x:v>
       </x:c>
-      <x:c r="G213" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H213" s="9" t="str">
+      <x:c r="G213" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H213" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
-      <x:c r="A214" s="7" t="str">
+      <x:c r="A214" s="6" t="str">
         <x:v>char_IMPERIALDRAMON_DM</x:v>
       </x:c>
-      <x:c r="B214" s="8" t="str">
+      <x:c r="B214" s="7" t="str">
         <x:v>Imperialdramon DM</x:v>
       </x:c>
-      <x:c r="C214" s="8" t="str">
+      <x:c r="C214" s="7" t="str">
         <x:v>Империалдрамон ДМ</x:v>
       </x:c>
-      <x:c r="D214" s="8" t="str">
+      <x:c r="D214" s="7" t="str">
         <x:v>Империалдрамон: Режим дракона</x:v>
       </x:c>
-      <x:c r="E214" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F214" s="8" t="str">
+      <x:c r="E214" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F214" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Imperialdramon%3A_Dragon_Mode</x:v>
       </x:c>
-      <x:c r="G214" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H214" s="9" t="str">
+      <x:c r="G214" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H214" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="15" hidden="0" customHeight="1">
-      <x:c r="A215" s="7" t="str">
+      <x:c r="A215" s="6" t="str">
         <x:v>char_DIANAMON</x:v>
       </x:c>
-      <x:c r="B215" s="8" t="str">
+      <x:c r="B215" s="7" t="str">
         <x:v>Dianamon</x:v>
       </x:c>
-      <x:c r="C215" s="8" t="str">
+      <x:c r="C215" s="7" t="str">
         <x:v>Дайанамон</x:v>
       </x:c>
-      <x:c r="D215" s="8" t="str">
+      <x:c r="D215" s="7" t="str">
         <x:v>Дианамон</x:v>
       </x:c>
-      <x:c r="E215" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F215" s="8" t="str">
+      <x:c r="E215" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F215" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dianamon</x:v>
       </x:c>
-      <x:c r="G215" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H215" s="9" t="str">
+      <x:c r="G215" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H215" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
-      <x:c r="A216" s="7" t="str">
+      <x:c r="A216" s="6" t="str">
         <x:v>char_DIANAMON_BIG</x:v>
       </x:c>
-      <x:c r="B216" s="8" t="str">
+      <x:c r="B216" s="7" t="str">
         <x:v>Dianamon</x:v>
       </x:c>
-      <x:c r="C216" s="8" t="str">
+      <x:c r="C216" s="7" t="str">
         <x:v>Дайанамон</x:v>
       </x:c>
-      <x:c r="D216" s="8" t="str">
+      <x:c r="D216" s="7" t="str">
         <x:v>Дианамон</x:v>
       </x:c>
-      <x:c r="E216" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F216" s="8" t="str">
+      <x:c r="E216" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F216" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dianamon</x:v>
       </x:c>
-      <x:c r="G216" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H216" s="9" t="str">
+      <x:c r="G216" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H216" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
-      <x:c r="A217" s="7" t="str">
+      <x:c r="A217" s="6" t="str">
         <x:v>char_KERPYMON_GOOD</x:v>
       </x:c>
-      <x:c r="B217" s="8" t="str">
+      <x:c r="B217" s="7" t="str">
         <x:v>Cherubimon (Good)</x:v>
       </x:c>
-      <x:c r="C217" s="8" t="str">
+      <x:c r="C217" s="7" t="str">
         <x:v>Керубимон (Добрый)</x:v>
       </x:c>
-      <x:c r="D217" s="8" t="str">
+      <x:c r="D217" s="7" t="str">
         <x:v>Херувимон (Добродетельный)</x:v>
       </x:c>
-      <x:c r="E217" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F217" s="8" t="str">
+      <x:c r="E217" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F217" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Cherubimon_%28Virtue%29</x:v>
       </x:c>
-      <x:c r="G217" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H217" s="9" t="str">
+      <x:c r="G217" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H217" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
-      <x:c r="A218" s="7" t="str">
+      <x:c r="A218" s="6" t="str">
         <x:v>char_DYNASMON</x:v>
       </x:c>
-      <x:c r="B218" s="8" t="str">
+      <x:c r="B218" s="7" t="str">
         <x:v>Dynasmon</x:v>
       </x:c>
-      <x:c r="C218" s="8" t="str">
+      <x:c r="C218" s="7" t="str">
         <x:v>Династмон</x:v>
       </x:c>
-      <x:c r="D218" s="8" t="str">
+      <x:c r="D218" s="7" t="str">
         <x:v>Динасмон</x:v>
       </x:c>
-      <x:c r="E218" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F218" s="8" t="str">
+      <x:c r="E218" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F218" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dynasmon</x:v>
       </x:c>
-      <x:c r="G218" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H218" s="9" t="str">
+      <x:c r="G218" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H218" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="15" hidden="0" customHeight="1">
-      <x:c r="A219" s="7" t="str">
+      <x:c r="A219" s="6" t="str">
         <x:v>char_DYNASMON_BIG</x:v>
       </x:c>
-      <x:c r="B219" s="8" t="str">
+      <x:c r="B219" s="7" t="str">
         <x:v>Dynasmon</x:v>
       </x:c>
-      <x:c r="C219" s="8" t="str">
+      <x:c r="C219" s="7" t="str">
         <x:v>Династмон</x:v>
       </x:c>
-      <x:c r="D219" s="8" t="str">
+      <x:c r="D219" s="7" t="str">
         <x:v>Динасмон</x:v>
       </x:c>
-      <x:c r="E219" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F219" s="8" t="str">
+      <x:c r="E219" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F219" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dynasmon</x:v>
       </x:c>
-      <x:c r="G219" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H219" s="9" t="str">
+      <x:c r="G219" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H219" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="15" hidden="0" customHeight="1">
-      <x:c r="A220" s="7" t="str">
+      <x:c r="A220" s="6" t="str">
         <x:v>char_DUFTMON</x:v>
       </x:c>
-      <x:c r="B220" s="8" t="str">
+      <x:c r="B220" s="7" t="str">
         <x:v>Leopardmon</x:v>
       </x:c>
-      <x:c r="C220" s="8" t="str">
+      <x:c r="C220" s="7" t="str">
         <x:v>Леопардмон</x:v>
       </x:c>
-      <x:c r="D220" s="8" t="str">
+      <x:c r="D220" s="7" t="str">
         <x:v>Дуфтмон</x:v>
       </x:c>
-      <x:c r="E220" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F220" s="8" t="str">
+      <x:c r="E220" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F220" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Duftmon</x:v>
       </x:c>
-      <x:c r="G220" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H220" s="9" t="str">
+      <x:c r="G220" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H220" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
-      <x:c r="A221" s="7" t="str">
+      <x:c r="A221" s="6" t="str">
         <x:v>char_DUFTMON_BIG</x:v>
       </x:c>
-      <x:c r="B221" s="8" t="str">
+      <x:c r="B221" s="7" t="str">
         <x:v>Leopardmon</x:v>
       </x:c>
-      <x:c r="C221" s="8" t="str">
+      <x:c r="C221" s="7" t="str">
         <x:v>Леопардмон</x:v>
       </x:c>
-      <x:c r="D221" s="8" t="str">
+      <x:c r="D221" s="7" t="str">
         <x:v>Дуфтмон</x:v>
       </x:c>
-      <x:c r="E221" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F221" s="8" t="str">
+      <x:c r="E221" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F221" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Duftmon</x:v>
       </x:c>
-      <x:c r="G221" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H221" s="9" t="str">
+      <x:c r="G221" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H221" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="15" hidden="0" customHeight="1">
-      <x:c r="A222" s="7" t="str">
+      <x:c r="A222" s="6" t="str">
         <x:v>char_SAINTGALGOMON</x:v>
       </x:c>
-      <x:c r="B222" s="8" t="str">
+      <x:c r="B222" s="7" t="str">
         <x:v>MegaGargomon</x:v>
       </x:c>
-      <x:c r="C222" s="8" t="str">
+      <x:c r="C222" s="7" t="str">
         <x:v>МегаГаргомон</x:v>
       </x:c>
-      <x:c r="D222" s="8" t="str">
+      <x:c r="D222" s="7" t="str">
         <x:v>Сен Гальгомон</x:v>
       </x:c>
-      <x:c r="E222" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F222" s="8" t="str">
+      <x:c r="E222" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F222" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Saint_Galgomon</x:v>
       </x:c>
-      <x:c r="G222" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H222" s="9" t="str">
+      <x:c r="G222" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H222" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="15" hidden="0" customHeight="1">
-      <x:c r="A223" s="7" t="str">
+      <x:c r="A223" s="6" t="str">
         <x:v>char_SAINTGALGOMON_BIG</x:v>
       </x:c>
-      <x:c r="B223" s="8" t="str">
+      <x:c r="B223" s="7" t="str">
         <x:v>MegaGargomon</x:v>
       </x:c>
-      <x:c r="C223" s="8" t="str">
+      <x:c r="C223" s="7" t="str">
         <x:v>МегаГаргомон</x:v>
       </x:c>
-      <x:c r="D223" s="8" t="str">
+      <x:c r="D223" s="7" t="str">
         <x:v>Сен Гальгомон</x:v>
       </x:c>
-      <x:c r="E223" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F223" s="8" t="str">
+      <x:c r="E223" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F223" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Saint_Galgomon</x:v>
       </x:c>
-      <x:c r="G223" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H223" s="9" t="str">
+      <x:c r="G223" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H223" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="15" hidden="0" customHeight="1">
-      <x:c r="A224" s="7" t="str">
+      <x:c r="A224" s="6" t="str">
         <x:v>char_DUFTMON_LM</x:v>
       </x:c>
-      <x:c r="B224" s="8" t="str">
+      <x:c r="B224" s="7" t="str">
         <x:v>Leopardmon LM</x:v>
       </x:c>
-      <x:c r="C224" s="8" t="str">
+      <x:c r="C224" s="7" t="str">
         <x:v>Леопардмон ЛМ</x:v>
       </x:c>
-      <x:c r="D224" s="8" t="str">
+      <x:c r="D224" s="7" t="str">
         <x:v>Дуфтмон: Режим леопарда</x:v>
       </x:c>
-      <x:c r="E224" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F224" s="8" t="str">
+      <x:c r="E224" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F224" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Duftmon%3A_Leopard_Mode</x:v>
       </x:c>
-      <x:c r="G224" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H224" s="9" t="str">
+      <x:c r="G224" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H224" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="15" hidden="0" customHeight="1">
-      <x:c r="A225" s="7" t="str">
+      <x:c r="A225" s="6" t="str">
         <x:v>char_KUZUHAMON</x:v>
       </x:c>
-      <x:c r="B225" s="8" t="str">
+      <x:c r="B225" s="7" t="str">
         <x:v>Kuzuhamon</x:v>
       </x:c>
-      <x:c r="C225" s="8" t="str">
+      <x:c r="C225" s="7" t="str">
         <x:v>Кузухамон</x:v>
       </x:c>
-      <x:c r="D225" s="8" t="str">
+      <x:c r="D225" s="7" t="str">
         <x:v>Кудзухамон</x:v>
       </x:c>
-      <x:c r="E225" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F225" s="8" t="str">
+      <x:c r="E225" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F225" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Kuzuhamon</x:v>
       </x:c>
-      <x:c r="G225" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H225" s="9" t="str">
+      <x:c r="G225" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H225" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
-      <x:c r="A226" s="7" t="str">
+      <x:c r="A226" s="6" t="str">
         <x:v>char_INSEKIMON</x:v>
       </x:c>
-      <x:c r="B226" s="8" t="str">
+      <x:c r="B226" s="7" t="str">
         <x:v>Meteormon</x:v>
       </x:c>
-      <x:c r="C226" s="8" t="str">
+      <x:c r="C226" s="7" t="str">
         <x:v>Метеормон</x:v>
       </x:c>
-      <x:c r="D226" s="8" t="str">
+      <x:c r="D226" s="7" t="str">
         <x:v>Инсэкимон</x:v>
       </x:c>
-      <x:c r="E226" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F226" s="8" t="str">
+      <x:c r="E226" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F226" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Insekimon</x:v>
       </x:c>
-      <x:c r="G226" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H226" s="9" t="str">
+      <x:c r="G226" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H226" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="15" hidden="0" customHeight="1">
-      <x:c r="A227" s="7" t="str">
+      <x:c r="A227" s="6" t="str">
         <x:v>char_OMEGAMON_ZWART</x:v>
       </x:c>
-      <x:c r="B227" s="8" t="str">
+      <x:c r="B227" s="7" t="str">
         <x:v>Omnimon Zwart</x:v>
       </x:c>
-      <x:c r="C227" s="8" t="str">
+      <x:c r="C227" s="7" t="str">
         <x:v>Омнимон Цварт</x:v>
       </x:c>
-      <x:c r="D227" s="8" t="str">
+      <x:c r="D227" s="7" t="str">
         <x:v>Омегамон Цварт</x:v>
       </x:c>
-      <x:c r="E227" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F227" s="8" t="str">
+      <x:c r="E227" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F227" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Omegamon_Zwart</x:v>
       </x:c>
-      <x:c r="G227" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H227" s="9" t="str">
+      <x:c r="G227" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H227" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="15" hidden="0" customHeight="1">
-      <x:c r="A228" s="7" t="str">
+      <x:c r="A228" s="6" t="str">
         <x:v>char_GUARDROMON_GL</x:v>
       </x:c>
-      <x:c r="B228" s="8" t="str">
+      <x:c r="B228" s="7" t="str">
         <x:v>Guardromon (Gold)</x:v>
       </x:c>
-      <x:c r="C228" s="8" t="str">
+      <x:c r="C228" s="7" t="str">
         <x:v>Гардромон (Золотой)</x:v>
       </x:c>
-      <x:c r="D228" s="8" t="str">
+      <x:c r="D228" s="7" t="str">
         <x:v>Гардромон (золотой)</x:v>
       </x:c>
-      <x:c r="E228" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F228" s="8" t="str">
+      <x:c r="E228" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F228" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Guardromon</x:v>
       </x:c>
-      <x:c r="G228" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H228" s="9" t="str">
+      <x:c r="G228" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H228" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="15" hidden="0" customHeight="1">
-      <x:c r="A229" s="7" t="str">
+      <x:c r="A229" s="6" t="str">
         <x:v>char_ALPHAMON_OURYUKEN</x:v>
       </x:c>
-      <x:c r="B229" s="8" t="str">
+      <x:c r="B229" s="7" t="str">
         <x:v>Alphamon: Ouryuken</x:v>
       </x:c>
-      <x:c r="C229" s="8" t="str">
+      <x:c r="C229" s="7" t="str">
         <x:v>Альфамон: Оурюкен</x:v>
       </x:c>
-      <x:c r="D229" s="8" t="str">
+      <x:c r="D229" s="7" t="str">
         <x:v>Альфамон: Орюкен</x:v>
       </x:c>
-      <x:c r="E229" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F229" s="8" t="str">
+      <x:c r="E229" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F229" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Alphamon%3A_Ouryuken</x:v>
       </x:c>
-      <x:c r="G229" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H229" s="9" t="str">
+      <x:c r="G229" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H229" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="15" hidden="0" customHeight="1">
-      <x:c r="A230" s="7" t="str">
+      <x:c r="A230" s="6" t="str">
         <x:v>char_KERPYMON_BAD</x:v>
       </x:c>
-      <x:c r="B230" s="8" t="str">
+      <x:c r="B230" s="7" t="str">
         <x:v>Cherubimon (Black)</x:v>
       </x:c>
-      <x:c r="C230" s="8" t="str">
+      <x:c r="C230" s="7" t="str">
         <x:v>Керубимон (Чёрный)</x:v>
       </x:c>
-      <x:c r="D230" s="8" t="str">
+      <x:c r="D230" s="7" t="str">
         <x:v>Херувимон (Порочный)</x:v>
       </x:c>
-      <x:c r="E230" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F230" s="8" t="str">
+      <x:c r="E230" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F230" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Cherubimon_%28Vice%29</x:v>
       </x:c>
-      <x:c r="G230" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H230" s="9" t="str">
+      <x:c r="G230" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H230" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="15" hidden="0" customHeight="1">
-      <x:c r="A231" s="7" t="str">
+      <x:c r="A231" s="6" t="str">
         <x:v>char_MIRAGEGAOGAMON_BM</x:v>
       </x:c>
-      <x:c r="B231" s="8" t="str">
+      <x:c r="B231" s="7" t="str">
         <x:v>MirageGaogamon BM</x:v>
       </x:c>
-      <x:c r="C231" s="8" t="str">
+      <x:c r="C231" s="7" t="str">
         <x:v>МиражГаогамон БМ</x:v>
       </x:c>
-      <x:c r="D231" s="8" t="str">
+      <x:c r="D231" s="7" t="str">
         <x:v>Мираж Гаогамон: Взрывной режим</x:v>
       </x:c>
-      <x:c r="E231" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F231" s="8" t="str">
+      <x:c r="E231" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F231" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Mirage_Gaogamon%3A_Burst_Mode</x:v>
       </x:c>
-      <x:c r="G231" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H231" s="9" t="str">
+      <x:c r="G231" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H231" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="15" hidden="0" customHeight="1">
-      <x:c r="A232" s="7" t="str">
+      <x:c r="A232" s="6" t="str">
         <x:v>char_RAREMON_BIG</x:v>
       </x:c>
-      <x:c r="B232" s="8" t="str">
+      <x:c r="B232" s="7" t="str">
         <x:v>Raremon</x:v>
       </x:c>
-      <x:c r="C232" s="8" t="str">
+      <x:c r="C232" s="7" t="str">
         <x:v>Рэармон</x:v>
       </x:c>
-      <x:c r="D232" s="8" t="str">
+      <x:c r="D232" s="7" t="str">
         <x:v>Рэйрмон</x:v>
       </x:c>
-      <x:c r="E232" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F232" s="8" t="str">
+      <x:c r="E232" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F232" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Raremon</x:v>
       </x:c>
-      <x:c r="G232" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H232" s="9" t="str">
+      <x:c r="G232" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H232" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="15" hidden="0" customHeight="1">
-      <x:c r="A233" s="7" t="str">
+      <x:c r="A233" s="6" t="str">
         <x:v>char_GREYMON_BIG_BL_ADD</x:v>
       </x:c>
-      <x:c r="B233" s="8" t="str">
+      <x:c r="B233" s="7" t="str">
         <x:v>Greymon (Blue) (Head Shell)</x:v>
       </x:c>
-      <x:c r="C233" s="8" t="str">
+      <x:c r="C233" s="7" t="str">
         <x:v>Греймон (Синий) (Головной убор)</x:v>
       </x:c>
-      <x:c r="D233" s="8" t="str">
+      <x:c r="D233" s="7" t="str">
         <x:v>Греймон (головной убор)</x:v>
       </x:c>
-      <x:c r="E233" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F233" s="8" t="str">
+      <x:c r="E233" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F233" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Greymon</x:v>
       </x:c>
-      <x:c r="G233" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H233" s="9" t="str">
+      <x:c r="G233" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H233" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="15" hidden="0" customHeight="1">
-      <x:c r="A234" s="7" t="str">
+      <x:c r="A234" s="6" t="str">
         <x:v>char_CHARISMON_ADD</x:v>
       </x:c>
-      <x:c r="B234" s="8" t="str">
+      <x:c r="B234" s="7" t="str">
         <x:v>Callismon (Gun)</x:v>
       </x:c>
-      <x:c r="C234" s="8" t="str">
+      <x:c r="C234" s="7" t="str">
         <x:v>Каллисмон (Пистолет)</x:v>
       </x:c>
-      <x:c r="D234" s="8" t="str">
+      <x:c r="D234" s="7" t="str">
         <x:v>Каллисмон (пистолет)</x:v>
       </x:c>
-      <x:c r="E234" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F234" s="8" t="str">
+      <x:c r="E234" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F234" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Callismon</x:v>
       </x:c>
-      <x:c r="G234" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H234" s="9" t="str">
+      <x:c r="G234" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H234" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="15" hidden="0" customHeight="1">
-      <x:c r="A235" s="7" t="str">
+      <x:c r="A235" s="6" t="str">
         <x:v>char_DIANAMON_ADD</x:v>
       </x:c>
-      <x:c r="B235" s="8" t="str">
+      <x:c r="B235" s="7" t="str">
         <x:v>Dianamon &amp; the Goodnight Sisters</x:v>
       </x:c>
-      <x:c r="C235" s="8" t="str">
+      <x:c r="C235" s="7" t="str">
         <x:v>Дайанамон и сестры Гуднайт</x:v>
       </x:c>
-      <x:c r="D235" s="8" t="str">
+      <x:c r="D235" s="7" t="str">
         <x:v>Дианамон</x:v>
       </x:c>
-      <x:c r="E235" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F235" s="8" t="str">
+      <x:c r="E235" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F235" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Dianamon</x:v>
       </x:c>
-      <x:c r="G235" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H235" s="9" t="str">
+      <x:c r="G235" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H235" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="15" hidden="0" customHeight="1">
-      <x:c r="A236" s="7" t="str">
+      <x:c r="A236" s="6" t="str">
         <x:v>char_LOCOMON_EVENT</x:v>
       </x:c>
-      <x:c r="B236" s="8" t="str">
+      <x:c r="B236" s="7" t="str">
         <x:v>Locomon (Event)</x:v>
       </x:c>
-      <x:c r="C236" s="8" t="str">
+      <x:c r="C236" s="7" t="str">
         <x:v>Локомон (Событие)</x:v>
       </x:c>
-      <x:c r="D236" s="8" t="str">
+      <x:c r="D236" s="7" t="str">
         <x:v>Локомон (событие)</x:v>
       </x:c>
-      <x:c r="E236" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F236" s="8" t="str">
+      <x:c r="E236" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F236" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Locomon</x:v>
       </x:c>
-      <x:c r="G236" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H236" s="9" t="str">
+      <x:c r="G236" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H236" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="15" hidden="0" customHeight="1">
-      <x:c r="A237" s="7" t="str">
+      <x:c r="A237" s="6" t="str">
         <x:v>char_ENBARRMON_CRANIAMON</x:v>
       </x:c>
-      <x:c r="B237" s="8" t="str">
+      <x:c r="B237" s="7" t="str">
         <x:v>Craniamon + Enbarrmon</x:v>
       </x:c>
-      <x:c r="C237" s="8" t="str">
+      <x:c r="C237" s="7" t="str">
         <x:v>Краниамон + Энбаррмон</x:v>
       </x:c>
-      <x:c r="D237" s="8" t="str">
+      <x:c r="D237" s="7" t="str">
         <x:v>Энбаррмон</x:v>
       </x:c>
-      <x:c r="E237" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F237" s="8" t="str">
+      <x:c r="E237" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F237" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Enbarrmon</x:v>
       </x:c>
-      <x:c r="G237" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H237" s="9" t="str">
+      <x:c r="G237" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H237" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="15" hidden="0" customHeight="1">
-      <x:c r="A238" s="7" t="str">
+      <x:c r="A238" s="6" t="str">
         <x:v>char_ENBARRMON_CRANIAMON_E</x:v>
       </x:c>
-      <x:c r="B238" s="8" t="str">
+      <x:c r="B238" s="7" t="str">
         <x:v>Craniamon + Enbarrmon</x:v>
       </x:c>
-      <x:c r="C238" s="8" t="str">
+      <x:c r="C238" s="7" t="str">
         <x:v>Краниамон + Энбаррмон</x:v>
       </x:c>
-      <x:c r="D238" s="8" t="str">
+      <x:c r="D238" s="7" t="str">
         <x:v>Энбаррмон</x:v>
       </x:c>
-      <x:c r="E238" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F238" s="8" t="str">
+      <x:c r="E238" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F238" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Enbarrmon</x:v>
       </x:c>
-      <x:c r="G238" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H238" s="9" t="str">
+      <x:c r="G238" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H238" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="15" hidden="0" customHeight="1">
-      <x:c r="A239" s="7" t="str">
+      <x:c r="A239" s="6" t="str">
         <x:v>char_PARROTMON_BIG</x:v>
       </x:c>
-      <x:c r="B239" s="8" t="str">
+      <x:c r="B239" s="7" t="str">
         <x:v>Parrotmon</x:v>
       </x:c>
-      <x:c r="C239" s="8" t="str">
+      <x:c r="C239" s="7" t="str">
         <x:v>Пэрэтмон</x:v>
       </x:c>
-      <x:c r="D239" s="8" t="str">
+      <x:c r="D239" s="7" t="str">
         <x:v>Пэрротмон</x:v>
       </x:c>
-      <x:c r="E239" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F239" s="8" t="str">
+      <x:c r="E239" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F239" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Parrotmon</x:v>
       </x:c>
-      <x:c r="G239" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H239" s="9" t="str">
+      <x:c r="G239" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H239" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="15" hidden="0" customHeight="1">
-      <x:c r="A240" s="7" t="str">
+      <x:c r="A240" s="6" t="str">
         <x:v>char_PARROTMON_BIG_ADD</x:v>
       </x:c>
-      <x:c r="B240" s="8" t="str">
+      <x:c r="B240" s="7" t="str">
         <x:v>Parrotmon (Crested)</x:v>
       </x:c>
-      <x:c r="C240" s="8" t="str">
+      <x:c r="C240" s="7" t="str">
         <x:v>Пэрэтмон (Гребень)</x:v>
       </x:c>
-      <x:c r="D240" s="8" t="str">
+      <x:c r="D240" s="7" t="str">
         <x:v>Пэрротмон (гребень)</x:v>
       </x:c>
-      <x:c r="E240" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F240" s="8" t="str">
+      <x:c r="E240" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F240" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Parrotmon</x:v>
       </x:c>
-      <x:c r="G240" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H240" s="9" t="str">
+      <x:c r="G240" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H240" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="15" hidden="0" customHeight="1">
-      <x:c r="A241" s="7" t="str">
+      <x:c r="A241" s="6" t="str">
         <x:v>char_METALGREYMON_BIG_BL</x:v>
       </x:c>
-      <x:c r="B241" s="8" t="str">
+      <x:c r="B241" s="7" t="str">
         <x:v>MetalGreymon (Blue)</x:v>
       </x:c>
-      <x:c r="C241" s="8" t="str">
+      <x:c r="C241" s="7" t="str">
         <x:v>МеталлГреймон (Синий)</x:v>
       </x:c>
-      <x:c r="D241" s="8" t="str">
+      <x:c r="D241" s="7" t="str">
         <x:v>Металл Греймон (синий)</x:v>
       </x:c>
-      <x:c r="E241" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F241" s="8" t="str">
+      <x:c r="E241" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F241" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Metal_Greymon</x:v>
       </x:c>
-      <x:c r="G241" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H241" s="9" t="str">
+      <x:c r="G241" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H241" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="15" hidden="0" customHeight="1">
-      <x:c r="A242" s="7" t="str">
+      <x:c r="A242" s="6" t="str">
         <x:v>char_WHAMON_BIG</x:v>
       </x:c>
-      <x:c r="B242" s="8" t="str">
+      <x:c r="B242" s="7" t="str">
         <x:v>Whamon</x:v>
       </x:c>
-      <x:c r="C242" s="8" t="str">
+      <x:c r="C242" s="7" t="str">
         <x:v>Вамон</x:v>
       </x:c>
-      <x:c r="D242" s="8" t="str">
+      <x:c r="D242" s="7" t="str">
         <x:v>Уэмон</x:v>
       </x:c>
-      <x:c r="E242" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F242" s="8" t="str">
+      <x:c r="E242" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F242" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Whamon</x:v>
       </x:c>
-      <x:c r="G242" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H242" s="9" t="str">
+      <x:c r="G242" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H242" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="15" hidden="0" customHeight="1">
-      <x:c r="A243" s="7" t="str">
+      <x:c r="A243" s="6" t="str">
         <x:v>char_NEPTUNEMON_BIG</x:v>
       </x:c>
-      <x:c r="B243" s="8" t="str">
+      <x:c r="B243" s="7" t="str">
         <x:v>Neptunemon</x:v>
       </x:c>
-      <x:c r="C243" s="8" t="str">
+      <x:c r="C243" s="7" t="str">
         <x:v>Нептунемон</x:v>
       </x:c>
-      <x:c r="D243" s="8" t="str">
+      <x:c r="D243" s="7" t="str">
         <x:v>Нептунмон</x:v>
       </x:c>
-      <x:c r="E243" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F243" s="8" t="str">
+      <x:c r="E243" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F243" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Neptunemon</x:v>
       </x:c>
-      <x:c r="G243" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H243" s="9" t="str">
+      <x:c r="G243" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H243" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="15" hidden="0" customHeight="1">
-      <x:c r="A244" s="7" t="str">
+      <x:c r="A244" s="6" t="str">
         <x:v>char_OMEGAMON_BIG</x:v>
       </x:c>
-      <x:c r="B244" s="8" t="str">
+      <x:c r="B244" s="7" t="str">
         <x:v>Omnimon</x:v>
       </x:c>
-      <x:c r="C244" s="8" t="str">
+      <x:c r="C244" s="7" t="str">
         <x:v>Омнимон</x:v>
       </x:c>
-      <x:c r="D244" s="8" t="str">
+      <x:c r="D244" s="7" t="str">
         <x:v>Омегамон</x:v>
       </x:c>
-      <x:c r="E244" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F244" s="8" t="str">
+      <x:c r="E244" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F244" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Omegamon</x:v>
       </x:c>
-      <x:c r="G244" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H244" s="9" t="str">
+      <x:c r="G244" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H244" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="15" hidden="0" customHeight="1">
-      <x:c r="A245" s="7" t="str">
+      <x:c r="A245" s="6" t="str">
         <x:v>char_JUPITERMON_WRATHMODE_BIG</x:v>
       </x:c>
-      <x:c r="B245" s="8" t="str">
+      <x:c r="B245" s="7" t="str">
         <x:v>Jupitermon WM</x:v>
       </x:c>
-      <x:c r="C245" s="8" t="str">
+      <x:c r="C245" s="7" t="str">
         <x:v>Юпитермон WM</x:v>
       </x:c>
-      <x:c r="D245" s="8" t="str">
+      <x:c r="D245" s="7" t="str">
         <x:v>Юпитермон: Режим гнева</x:v>
       </x:c>
-      <x:c r="E245" s="8" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F245" s="8" t="str">
+      <x:c r="E245" s="7" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F245" s="7" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Jupitermon%3A_Wrath_Mode</x:v>
       </x:c>
-      <x:c r="G245" s="8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H245" s="9" t="str">
+      <x:c r="G245" s="7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H245" s="8" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="15" hidden="0" customHeight="1">
-      <x:c r="A246" s="10" t="str">
+      <x:c r="A246" s="9" t="str">
         <x:v>char_ORGEMON_BOSS</x:v>
       </x:c>
-      <x:c r="B246" s="11" t="str">
+      <x:c r="B246" s="10" t="str">
         <x:v>Ogremon</x:v>
       </x:c>
-      <x:c r="C246" s="11" t="str">
+      <x:c r="C246" s="10" t="str">
         <x:v>Огремон</x:v>
       </x:c>
-      <x:c r="D246" s="11" t="str">
+      <x:c r="D246" s="10" t="str">
         <x:v>Оргмон</x:v>
       </x:c>
-      <x:c r="E246" s="11" t="str">
-        <x:v>ru_digimon_fandom</x:v>
-      </x:c>
-      <x:c r="F246" s="11" t="str">
+      <x:c r="E246" s="10" t="str">
+        <x:v>ru_digimon_fandom</x:v>
+      </x:c>
+      <x:c r="F246" s="10" t="str">
         <x:v>https://digimon.fandom.com/ru/wiki/Orgemon</x:v>
       </x:c>
-      <x:c r="G246" s="11" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="H246" s="12" t="str">
+      <x:c r="G246" s="10" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="H246" s="11" t="str">
         <x:v>Changed to the selected Russian Digimon Wiki/Fandom form during the name localization pass.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2270b6196cfc4fe7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e3e8a5ad1a24d9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>